--- a/simple_game_test/filtered_users.xlsx
+++ b/simple_game_test/filtered_users.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL28"/>
+  <dimension ref="A1:AL35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3614,6 +3614,818 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>154</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>67effc2f296ab827d6128bf3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>9VO5CM</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>23</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>6</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>The study was engaging and good</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>45754.84783649952</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 19, 36, 30, 205100), datetime.datetime(2025, 4, 7, 19, 34, 53, 923900), datetime.datetime(2025, 4, 7, 19, 35, 20, 602200), datetime.datetime(2025, 4, 7, 19, 35, 41, 12100), datetime.datetime(2025, 4, 7, 19, 36, 7, 841900), datetime.datetime(2025, 4, 7, 19, 36, 44, 33600), datetime.datetime(2025, 4, 7, 19, 37, 22, 921400), datetime.datetime(2025, 4, 7, 19, 37, 23, 525100), datetime.datetime(2025, 4, 7, 19, 37, 46, 655700), datetime.datetime(2025, 4, 7, 19, 37, 56, 485900), datetime.datetime(2025, 4, 7, 19, 38, 34, 573800), datetime.datetime(2025, 4, 7, 19, 38, 58, 87100), datetime.datetime(2025, 4, 7, 19, 44, 24, 721000), datetime.datetime(2025, 4, 7, 19, 42, 23, 350100), datetime.datetime(2025, 4, 7, 19, 42, 42, 417100), datetime.datetime(2025, 4, 7, 19, 43, 12, 651400), datetime.datetime(2025, 4, 7, 19, 43, 20, 416400), datetime.datetime(2025, 4, 7, 19, 46, 1, 975400), datetime.datetime(2025, 4, 7, 19, 45, 34, 819900), datetime.datetime(2025, 4, 7, 19, 45, 59, 723300), datetime.datetime(2025, 4, 7, 19, 46, 22, 630200), datetime.datetime(2025, 4, 7, 19, 47, 1, 884600), datetime.datetime(2025, 4, 7, 19, 47, 14, 110200), datetime.datetime(2025, 4, 7, 19, 48, 17, 115300), datetime.datetime(2025, 4, 7, 19, 48, 1, 691000), datetime.datetime(2025, 4, 7, 19, 48, 43, 713200), datetime.datetime(2025, 4, 7, 19, 49, 3, 98400), datetime.datetime(2025, 4, 7, 19, 49, 50, 4800), datetime.datetime(2025, 4, 7, 19, 49, 43, 158500), datetime.datetime(2025, 4, 7, 19, 50, 29, 834900), datetime.datetime(2025, 4, 7, 19, 50, 58, 434000), datetime.datetime(2025, 4, 7, 19, 51, 6, 930300), datetime.datetime(2025, 4, 7, 19, 51, 18, 365000), datetime.datetime(2025, 4, 7, 19, 52, 9, 10700), datetime.datetime(2025, 4, 7, 19, 52, 1, 409000), datetime.datetime(2025, 4, 7, 19, 52, 25, 262600), datetime.datetime(2025, 4, 7, 19, 52, 37, 911600), datetime.datetime(2025, 4, 7, 19, 53, 21, 513200), datetime.datetime(2025, 4, 7, 19, 53, 47, 575700), datetime.datetime(2025, 4, 7, 19, 53, 42, 158300), datetime.datetime(2025, 4, 7, 19, 54, 2, 575300), datetime.datetime(2025, 4, 7, 19, 54, 19, 799100), datetime.datetime(2025, 4, 7, 19, 54, 30, 268200), datetime.datetime(2025, 4, 7, 19, 55, 26, 479100), datetime.datetime(2025, 4, 7, 19, 55, 11, 193300), datetime.datetime(2025, 4, 7, 19, 55, 31, 932700), datetime.datetime(2025, 4, 7, 19, 56, 22, 425800), datetime.datetime(2025, 4, 7, 19, 56, 15, 31800), datetime.datetime(2025, 4, 7, 19, 57, 18, 907800), datetime.datetime(2025, 4, 7, 19, 57, 10, 944400), datetime.datetime(2025, 4, 7, 19, 57, 54, 495600), datetime.datetime(2025, 4, 7, 19, 58, 55, 524500), datetime.datetime(2025, 4, 7, 19, 58, 38, 208000), datetime.datetime(2025, 4, 7, 19, 58, 56, 426900), datetime.datetime(2025, 4, 7, 19, 59, 26, 652400), datetime.datetime(2025, 4, 7, 19, 59, 46, 458600), datetime.datetime(2025, 4, 7, 20, 0, 6, 719000), datetime.datetime(2025, 4, 7, 20, 0, 44, 642600), datetime.datetime(2025, 4, 7, 20, 0, 32, 52000), datetime.datetime(2025, 4, 7, 20, 0, 42, 531000), datetime.datetime(2025, 4, 7, 20, 0, 55, 565200), datetime.datetime(2025, 4, 7, 20, 1, 9, 213000), datetime.datetime(2025, 4, 7, 20, 2, 42, 128100), datetime.datetime(2025, 4, 7, 20, 2, 42, 128100), datetime.datetime(2025, 4, 7, 20, 9, 4, 959000), datetime.datetime(2025, 4, 7, 20, 6, 35, 813700), datetime.datetime(2025, 4, 7, 20, 7, 23, 796600), datetime.datetime(2025, 4, 7, 20, 7, 26, 478800), datetime.datetime(2025, 4, 7, 20, 8, 28, 90000), datetime.datetime(2025, 4, 7, 20, 8, 9, 141000), datetime.datetime(2025, 4, 7, 20, 9, 9, 516900), datetime.datetime(2025, 4, 7, 20, 9, 2, 267600), datetime.datetime(2025, 4, 7, 20, 9, 54, 691100), datetime.datetime(2025, 4, 7, 20, 10, 18, 639100), datetime.datetime(2025, 4, 7, 20, 10, 38, 459700), datetime.datetime(2025, 4, 7, 20, 10, 42, 130200), datetime.datetime(2025, 4, 7, 20, 11, 35, 87900), datetime.datetime(2025, 4, 7, 20, 11, 24, 531700), datetime.datetime(2025, 4, 7, 20, 12, 6, 844900), datetime.datetime(2025, 4, 7, 20, 12, 11, 64600), datetime.datetime(2025, 4, 7, 20, 13, 22, 929100), datetime.datetime(2025, 4, 7, 20, 13, 9, 77900), datetime.datetime(2025, 4, 7, 20, 13, 57, 253500), datetime.datetime(2025, 4, 7, 20, 14, 12, 2600), datetime.datetime(2025, 4, 7, 20, 14, 16, 149400), datetime.datetime(2025, 4, 7, 20, 15, 12, 690500), datetime.datetime(2025, 4, 7, 20, 15, 13, 452900), datetime.datetime(2025, 4, 7, 20, 15, 32, 576100), datetime.datetime(2025, 4, 7, 20, 16, 19, 220700), datetime.datetime(2025, 4, 7, 20, 16, 28, 416300), datetime.datetime(2025, 4, 7, 20, 16, 37, 390100), datetime.datetime(2025, 4, 7, 20, 17, 23, 502500), datetime.datetime(2025, 4, 7, 20, 17, 45, 652800), datetime.datetime(2025, 4, 7, 20, 18, 21, 38000), datetime.datetime(2025, 4, 7, 20, 18, 45, 523500), datetime.datetime(2025, 4, 7, 20, 18, 42, 655500), datetime.datetime(2025, 4, 7, 20, 18, 57, 18000), datetime.datetime(2025, 4, 7, 20, 19, 6, 802800), datetime.datetime(2025, 4, 7, 20, 19, 23, 414200), datetime.datetime(2025, 4, 7, 20, 20, 4, 712100)]</t>
+        </is>
+      </c>
+      <c r="AE29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>155</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>66c90b4876ac27b40fa5fd52</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MY46M1</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>45754.82209433212</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>diagnostic test</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 19, 33, 58, 706500), datetime.datetime(2025, 4, 7, 19, 33, 37, 488700), datetime.datetime(2025, 4, 7, 19, 34, 38, 679400), datetime.datetime(2025, 4, 7, 19, 35, 11, 115700), datetime.datetime(2025, 4, 7, 19, 35, 48, 527000), datetime.datetime(2025, 4, 7, 19, 36, 31, 286000), datetime.datetime(2025, 4, 7, 19, 38, 22, 752800), datetime.datetime(2025, 4, 7, 19, 38, 14, 34300), datetime.datetime(2025, 4, 7, 19, 39, 39, 762700), datetime.datetime(2025, 4, 7, 19, 39, 46, 32500), datetime.datetime(2025, 4, 7, 19, 41, 6, 206100), datetime.datetime(2025, 4, 7, 19, 41, 37, 72800), datetime.datetime(2025, 4, 7, 19, 42, 5, 492400), datetime.datetime(2025, 4, 7, 19, 42, 55, 111300)]</t>
+        </is>
+      </c>
+      <c r="AE30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>156</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>67eff7a8455d7da8f34434a4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>E0BVC4</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>51</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>5</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>no comment</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>45754.84830539158</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 19, 32, 58, 648500), datetime.datetime(2025, 4, 7, 19, 32, 52, 692800), datetime.datetime(2025, 4, 7, 19, 33, 28, 293500), datetime.datetime(2025, 4, 7, 19, 33, 48, 675500), datetime.datetime(2025, 4, 7, 19, 34, 13, 314000), datetime.datetime(2025, 4, 7, 19, 39, 36, 93500), datetime.datetime(2025, 4, 7, 19, 37, 9, 895000), datetime.datetime(2025, 4, 7, 19, 37, 24, 466600), datetime.datetime(2025, 4, 7, 19, 37, 49, 764600), datetime.datetime(2025, 4, 7, 19, 37, 56, 412300), datetime.datetime(2025, 4, 7, 19, 45, 1, 237700), datetime.datetime(2025, 4, 7, 19, 41, 46, 267300), datetime.datetime(2025, 4, 7, 19, 41, 57, 901300), datetime.datetime(2025, 4, 7, 19, 42, 8, 88300), datetime.datetime(2025, 4, 7, 19, 46, 36, 544800), datetime.datetime(2025, 4, 7, 19, 44, 35, 74400), datetime.datetime(2025, 4, 7, 19, 44, 42, 652200), datetime.datetime(2025, 4, 7, 19, 44, 50, 315600), datetime.datetime(2025, 4, 7, 19, 50, 2, 548800), datetime.datetime(2025, 4, 7, 19, 47, 39, 786600), datetime.datetime(2025, 4, 7, 19, 48, 4, 510800), datetime.datetime(2025, 4, 7, 19, 48, 18, 677500), datetime.datetime(2025, 4, 7, 19, 48, 38, 421300), datetime.datetime(2025, 4, 7, 19, 49, 2, 625200), datetime.datetime(2025, 4, 7, 19, 49, 41, 576200), datetime.datetime(2025, 4, 7, 19, 49, 31, 159300), datetime.datetime(2025, 4, 7, 19, 50, 5, 318300), datetime.datetime(2025, 4, 7, 19, 50, 10, 841700), datetime.datetime(2025, 4, 7, 19, 50, 57, 855500), datetime.datetime(2025, 4, 7, 19, 50, 48, 710600), datetime.datetime(2025, 4, 7, 19, 52, 32, 456000), datetime.datetime(2025, 4, 7, 19, 52, 5, 5000), datetime.datetime(2025, 4, 7, 19, 52, 19, 580400), datetime.datetime(2025, 4, 7, 19, 52, 46, 971000), datetime.datetime(2025, 4, 7, 19, 52, 49, 968700), datetime.datetime(2025, 4, 7, 19, 53, 4, 281200), datetime.datetime(2025, 4, 7, 19, 54, 4, 396800), datetime.datetime(2025, 4, 7, 19, 53, 53, 662100), datetime.datetime(2025, 4, 7, 19, 54, 35, 11300), datetime.datetime(2025, 4, 7, 19, 54, 34, 875900), datetime.datetime(2025, 4, 7, 19, 55, 33, 227900), datetime.datetime(2025, 4, 7, 19, 55, 16, 826300), datetime.datetime(2025, 4, 7, 19, 55, 44, 897100), datetime.datetime(2025, 4, 7, 19, 55, 52, 787300), datetime.datetime(2025, 4, 7, 19, 56, 7, 11500), datetime.datetime(2025, 4, 7, 19, 56, 14, 942300), datetime.datetime(2025, 4, 7, 20, 0, 0, 755000), datetime.datetime(2025, 4, 7, 19, 58, 18, 187000), datetime.datetime(2025, 4, 7, 19, 58, 33, 203900), datetime.datetime(2025, 4, 7, 19, 58, 45, 606900), datetime.datetime(2025, 4, 7, 19, 59, 3, 139500), datetime.datetime(2025, 4, 7, 19, 59, 29, 156000), datetime.datetime(2025, 4, 7, 20, 1, 30, 17500), datetime.datetime(2025, 4, 7, 20, 1, 10, 79900), datetime.datetime(2025, 4, 7, 20, 1, 9, 51000), datetime.datetime(2025, 4, 7, 20, 1, 27, 174600), datetime.datetime(2025, 4, 7, 20, 1, 50, 200500), datetime.datetime(2025, 4, 7, 20, 4, 0, 514900), datetime.datetime(2025, 4, 7, 20, 4, 0, 514900), datetime.datetime(2025, 4, 7, 20, 6, 20, 48900), datetime.datetime(2025, 4, 7, 20, 6, 8, 719000), datetime.datetime(2025, 4, 7, 20, 6, 19, 472400), datetime.datetime(2025, 4, 7, 20, 6, 32, 306500), datetime.datetime(2025, 4, 7, 20, 9, 18, 396800), datetime.datetime(2025, 4, 7, 20, 8, 9, 448700), datetime.datetime(2025, 4, 7, 20, 8, 26, 947500), datetime.datetime(2025, 4, 7, 20, 8, 40, 322900), datetime.datetime(2025, 4, 7, 20, 10, 14, 976100), datetime.datetime(2025, 4, 7, 20, 9, 38, 930500), datetime.datetime(2025, 4, 7, 20, 9, 57, 656200), datetime.datetime(2025, 4, 7, 20, 10, 4, 663500), datetime.datetime(2025, 4, 7, 20, 10, 32, 267600), datetime.datetime(2025, 4, 7, 20, 10, 39, 924400), datetime.datetime(2025, 4, 7, 20, 13, 39, 786300), datetime.datetime(2025, 4, 7, 20, 12, 27, 756200), datetime.datetime(2025, 4, 7, 20, 13, 3, 131900), datetime.datetime(2025, 4, 7, 20, 12, 59, 105100), datetime.datetime(2025, 4, 7, 20, 13, 59, 436900), datetime.datetime(2025, 4, 7, 20, 14, 5, 579100), datetime.datetime(2025, 4, 7, 20, 14, 4, 989500), datetime.datetime(2025, 4, 7, 20, 15, 11, 722100), datetime.datetime(2025, 4, 7, 20, 15, 2, 359300), datetime.datetime(2025, 4, 7, 20, 15, 15, 964300), datetime.datetime(2025, 4, 7, 20, 16, 49, 548000), datetime.datetime(2025, 4, 7, 20, 16, 21, 292500), datetime.datetime(2025, 4, 7, 20, 16, 24, 451500), datetime.datetime(2025, 4, 7, 20, 17, 39, 206000), datetime.datetime(2025, 4, 7, 20, 17, 27, 624900), datetime.datetime(2025, 4, 7, 20, 17, 37, 541800), datetime.datetime(2025, 4, 7, 20, 19, 17, 165400), datetime.datetime(2025, 4, 7, 20, 18, 56, 420100), datetime.datetime(2025, 4, 7, 20, 19, 16, 625000), datetime.datetime(2025, 4, 7, 20, 19, 23, 778800), datetime.datetime(2025, 4, 7, 20, 19, 38, 486400), datetime.datetime(2025, 4, 7, 20, 21, 4, 744500)]</t>
+        </is>
+      </c>
+      <c r="AE31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>157</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>673ba77e4e24b2177b99fa75</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>WB9XND</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>41</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>5</v>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Nothing really. It was well explained</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>45754.90631810745</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 20, 39, 22, 713100), datetime.datetime(2025, 4, 7, 20, 39, 5, 301300), datetime.datetime(2025, 4, 7, 20, 40, 12, 888100), datetime.datetime(2025, 4, 7, 21, 46, 57, 201900), datetime.datetime(2025, 4, 7, 21, 14, 6, 797800), datetime.datetime(2025, 4, 7, 21, 14, 53, 719400), datetime.datetime(2025, 4, 7, 21, 15, 24, 530600), datetime.datetime(2025, 4, 7, 21, 16, 28, 566900), datetime.datetime(2025, 4, 7, 21, 17, 5, 657100), datetime.datetime(2025, 4, 7, 21, 17, 9, 50400), datetime.datetime(2025, 4, 7, 21, 17, 32, 114600), datetime.datetime(2025, 4, 7, 21, 17, 47, 54800), datetime.datetime(2025, 4, 7, 21, 17, 58, 758500), datetime.datetime(2025, 4, 7, 21, 18, 55, 144100), datetime.datetime(2025, 4, 7, 21, 18, 42, 445900), datetime.datetime(2025, 4, 7, 21, 19, 8, 673100), datetime.datetime(2025, 4, 7, 21, 19, 22, 554300), datetime.datetime(2025, 4, 7, 21, 19, 42, 367000), datetime.datetime(2025, 4, 7, 21, 20, 47, 8700), datetime.datetime(2025, 4, 7, 21, 20, 33, 674400), datetime.datetime(2025, 4, 7, 21, 21, 9, 661500), datetime.datetime(2025, 4, 7, 21, 21, 17, 355000), datetime.datetime(2025, 4, 7, 21, 22, 4, 379400), datetime.datetime(2025, 4, 7, 21, 22, 7, 471000), datetime.datetime(2025, 4, 7, 21, 23, 28, 433300), datetime.datetime(2025, 4, 7, 21, 23, 13, 343700), datetime.datetime(2025, 4, 7, 21, 23, 27, 890000), datetime.datetime(2025, 4, 7, 21, 23, 39, 567500), datetime.datetime(2025, 4, 7, 21, 23, 51, 739400), datetime.datetime(2025, 4, 7, 21, 27, 28, 813100), datetime.datetime(2025, 4, 7, 21, 27, 28, 813100), datetime.datetime(2025, 4, 7, 21, 29, 43, 438400), datetime.datetime(2025, 4, 7, 21, 30, 14, 40500), datetime.datetime(2025, 4, 7, 21, 30, 31, 737800), datetime.datetime(2025, 4, 7, 21, 31, 7, 880200), datetime.datetime(2025, 4, 7, 21, 32, 5, 904400), datetime.datetime(2025, 4, 7, 21, 32, 0, 270400), datetime.datetime(2025, 4, 7, 21, 32, 33, 641700), datetime.datetime(2025, 4, 7, 21, 33, 54, 53900), datetime.datetime(2025, 4, 7, 21, 33, 31, 966600), datetime.datetime(2025, 4, 7, 21, 34, 10, 786200), datetime.datetime(2025, 4, 7, 21, 34, 30, 827500), datetime.datetime(2025, 4, 7, 21, 34, 57, 102300), datetime.datetime(2025, 4, 7, 21, 35, 29, 639000), datetime.datetime(2025, 4, 7, 21, 35, 41, 925800), datetime.datetime(2025, 4, 7, 21, 36, 58, 509300), datetime.datetime(2025, 4, 7, 21, 36, 34, 332700), datetime.datetime(2025, 4, 7, 21, 36, 53, 43900), datetime.datetime(2025, 4, 7, 21, 37, 14, 529900), datetime.datetime(2025, 4, 7, 21, 37, 22, 800200), datetime.datetime(2025, 4, 7, 21, 37, 43, 440200), datetime.datetime(2025, 4, 7, 21, 38, 7, 128400), datetime.datetime(2025, 4, 7, 21, 39, 3, 418000), datetime.datetime(2025, 4, 7, 21, 38, 45, 593100), datetime.datetime(2025, 4, 7, 21, 38, 55, 285400), datetime.datetime(2025, 4, 7, 21, 39, 7, 913200), datetime.datetime(2025, 4, 7, 21, 39, 42, 668000), datetime.datetime(2025, 4, 7, 21, 39, 56, 937800), datetime.datetime(2025, 4, 7, 21, 40, 10, 169300), datetime.datetime(2025, 4, 7, 21, 41, 0, 218900), datetime.datetime(2025, 4, 7, 21, 40, 57, 96600), datetime.datetime(2025, 4, 7, 21, 41, 33, 583600), datetime.datetime(2025, 4, 7, 21, 41, 23, 304800), datetime.datetime(2025, 4, 7, 21, 41, 33, 656500), datetime.datetime(2025, 4, 7, 21, 41, 43, 6600), datetime.datetime(2025, 4, 7, 21, 42, 16, 212800), datetime.datetime(2025, 4, 7, 21, 44, 37, 410100)]</t>
+        </is>
+      </c>
+      <c r="AE32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>45</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="n">
+        <v>45</v>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>160</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>67f2a88a874ffbefd55213cf</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ZA1578</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>post practice</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>45754.90953296465</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 20, 47, 24, 578100), datetime.datetime(2025, 4, 7, 20, 47, 7, 487500), datetime.datetime(2025, 4, 7, 20, 47, 38, 713700), datetime.datetime(2025, 4, 7, 20, 48, 27, 645800), datetime.datetime(2025, 4, 7, 20, 48, 27, 310200), datetime.datetime(2025, 4, 7, 20, 49, 2, 549500), datetime.datetime(2025, 4, 7, 20, 48, 44, 943600), datetime.datetime(2025, 4, 7, 20, 49, 8, 242400), datetime.datetime(2025, 4, 7, 20, 52, 31, 258000), datetime.datetime(2025, 4, 7, 20, 51, 24, 967700), datetime.datetime(2025, 4, 7, 20, 51, 37, 22000), datetime.datetime(2025, 4, 7, 20, 51, 57, 700500), datetime.datetime(2025, 4, 7, 20, 52, 56, 949700), datetime.datetime(2025, 4, 7, 20, 52, 50, 109200), datetime.datetime(2025, 4, 7, 20, 53, 18, 137800), datetime.datetime(2025, 4, 7, 20, 53, 37, 877800), datetime.datetime(2025, 4, 7, 20, 54, 2, 129600), datetime.datetime(2025, 4, 7, 20, 54, 14, 343000), datetime.datetime(2025, 4, 7, 20, 55, 19, 536900), datetime.datetime(2025, 4, 7, 20, 55, 9, 459700), datetime.datetime(2025, 4, 7, 20, 55, 45, 58800), datetime.datetime(2025, 4, 7, 20, 57, 46, 507100), datetime.datetime(2025, 4, 7, 20, 57, 23, 500000), datetime.datetime(2025, 4, 7, 20, 57, 35, 112800), datetime.datetime(2025, 4, 7, 20, 58, 6, 905500), datetime.datetime(2025, 4, 7, 20, 58, 26, 172500), datetime.datetime(2025, 4, 7, 21, 2, 33, 166100), datetime.datetime(2025, 4, 7, 21, 0, 54, 623800), datetime.datetime(2025, 4, 7, 21, 2, 43, 839600), datetime.datetime(2025, 4, 7, 21, 2, 41, 272300), datetime.datetime(2025, 4, 7, 21, 2, 39, 737500), datetime.datetime(2025, 4, 7, 21, 3, 56, 922100), datetime.datetime(2025, 4, 7, 21, 3, 45, 363400), datetime.datetime(2025, 4, 7, 21, 4, 5, 213900), datetime.datetime(2025, 4, 7, 21, 4, 56, 302200), datetime.datetime(2025, 4, 7, 21, 5, 11, 711700), datetime.datetime(2025, 4, 7, 21, 6, 13, 270800), datetime.datetime(2025, 4, 7, 21, 6, 13, 759600), datetime.datetime(2025, 4, 7, 21, 7, 6, 634900), datetime.datetime(2025, 4, 7, 21, 7, 21, 286200), datetime.datetime(2025, 4, 7, 21, 8, 39, 834000), datetime.datetime(2025, 4, 7, 21, 8, 10, 445500), datetime.datetime(2025, 4, 7, 21, 8, 28, 717100), datetime.datetime(2025, 4, 7, 21, 9, 1, 549900), datetime.datetime(2025, 4, 7, 21, 9, 15, 613800), datetime.datetime(2025, 4, 7, 21, 9, 31, 896300), datetime.datetime(2025, 4, 7, 21, 9, 57, 888700), datetime.datetime(2025, 4, 7, 21, 15, 26, 637000), datetime.datetime(2025, 4, 7, 21, 13, 6, 940200), datetime.datetime(2025, 4, 7, 21, 13, 17, 971300), datetime.datetime(2025, 4, 7, 21, 13, 45, 933900), datetime.datetime(2025, 4, 7, 21, 14, 11, 761600), datetime.datetime(2025, 4, 7, 21, 14, 28, 747100), datetime.datetime(2025, 4, 7, 21, 15, 42, 386100), datetime.datetime(2025, 4, 7, 21, 15, 30, 169200), datetime.datetime(2025, 4, 7, 21, 15, 46, 458700), datetime.datetime(2025, 4, 7, 21, 16, 4, 34900), datetime.datetime(2025, 4, 7, 21, 16, 33, 595100), datetime.datetime(2025, 4, 7, 21, 16, 37, 712700), datetime.datetime(2025, 4, 7, 21, 17, 49, 296400), datetime.datetime(2025, 4, 7, 21, 17, 36, 147700), datetime.datetime(2025, 4, 7, 21, 17, 49, 669700), datetime.datetime(2025, 4, 7, 21, 18, 23, 257400), datetime.datetime(2025, 4, 7, 21, 18, 41, 539500), datetime.datetime(2025, 4, 7, 21, 19, 41, 598900), datetime.datetime(2025, 4, 7, 21, 21, 24, 801400), datetime.datetime(2025, 4, 7, 21, 20, 59, 171300), datetime.datetime(2025, 4, 7, 21, 21, 7, 615300), datetime.datetime(2025, 4, 7, 21, 21, 18, 911800), datetime.datetime(2025, 4, 7, 21, 21, 56, 799300), datetime.datetime(2025, 4, 7, 21, 24, 42, 846100), datetime.datetime(2025, 4, 7, 21, 24, 42, 846100), datetime.datetime(2025, 4, 7, 21, 30, 12, 882200), datetime.datetime(2025, 4, 7, 21, 27, 53, 764600), datetime.datetime(2025, 4, 7, 21, 28, 12, 740000), datetime.datetime(2025, 4, 7, 21, 29, 56, 514500), datetime.datetime(2025, 4, 7, 21, 31, 59, 819000), datetime.datetime(2025, 4, 7, 21, 31, 16, 299500), datetime.datetime(2025, 4, 7, 21, 32, 23, 505500), datetime.datetime(2025, 4, 7, 21, 34, 0, 573400), datetime.datetime(2025, 4, 7, 21, 33, 40, 791900), datetime.datetime(2025, 4, 7, 21, 35, 45, 593300), datetime.datetime(2025, 4, 7, 21, 38, 25, 414600), datetime.datetime(2025, 4, 7, 21, 37, 16, 515200), datetime.datetime(2025, 4, 7, 21, 38, 4, 853100), datetime.datetime(2025, 4, 7, 21, 38, 4, 853100)]</t>
+        </is>
+      </c>
+      <c r="AE33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>161</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>66b2a94c682fc730c408dbb1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>NVCWJF</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>35</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Waiting on a partner was frustrating and nearly resulted in me terminating my participation</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>45754.90586861606</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 20, 45, 36, 780800), datetime.datetime(2025, 4, 7, 20, 45, 18, 206600), datetime.datetime(2025, 4, 7, 20, 45, 46, 145400), datetime.datetime(2025, 4, 7, 20, 45, 58, 291600), datetime.datetime(2025, 4, 7, 20, 46, 10, 226200), datetime.datetime(2025, 4, 7, 20, 54, 48, 45100), datetime.datetime(2025, 4, 7, 20, 50, 45, 17800), datetime.datetime(2025, 4, 7, 20, 51, 21, 891700), datetime.datetime(2025, 4, 7, 20, 51, 23, 204800), datetime.datetime(2025, 4, 7, 20, 51, 39, 959200), datetime.datetime(2025, 4, 7, 20, 52, 58, 227700), datetime.datetime(2025, 4, 7, 20, 52, 45, 126000), datetime.datetime(2025, 4, 7, 20, 52, 53, 671100), datetime.datetime(2025, 4, 7, 20, 53, 4, 96100), datetime.datetime(2025, 4, 7, 20, 53, 30, 726200), datetime.datetime(2025, 4, 7, 20, 55, 34, 545300), datetime.datetime(2025, 4, 7, 20, 54, 46, 440600), datetime.datetime(2025, 4, 7, 20, 55, 5, 352200), datetime.datetime(2025, 4, 7, 20, 55, 11, 218400), datetime.datetime(2025, 4, 7, 20, 58, 5, 255000), datetime.datetime(2025, 4, 7, 20, 57, 5, 692600), datetime.datetime(2025, 4, 7, 20, 57, 36, 614000), datetime.datetime(2025, 4, 7, 20, 57, 46, 254300), datetime.datetime(2025, 4, 7, 20, 57, 54, 64600), datetime.datetime(2025, 4, 7, 21, 2, 34, 803800), datetime.datetime(2025, 4, 7, 21, 0, 41, 878100), datetime.datetime(2025, 4, 7, 21, 0, 44, 952100), datetime.datetime(2025, 4, 7, 21, 0, 54, 496600), datetime.datetime(2025, 4, 7, 21, 1, 5, 124000), datetime.datetime(2025, 4, 7, 21, 5, 16, 449300), datetime.datetime(2025, 4, 7, 21, 3, 33, 474200), datetime.datetime(2025, 4, 7, 21, 3, 59, 26500), datetime.datetime(2025, 4, 7, 21, 3, 58, 830600), datetime.datetime(2025, 4, 7, 21, 7, 3, 229500), datetime.datetime(2025, 4, 7, 21, 5, 47, 92200), datetime.datetime(2025, 4, 7, 21, 6, 6, 991900), datetime.datetime(2025, 4, 7, 21, 6, 12, 578000), datetime.datetime(2025, 4, 7, 21, 9, 4, 562300), datetime.datetime(2025, 4, 7, 21, 8, 1, 227700), datetime.datetime(2025, 4, 7, 21, 8, 18, 956800), datetime.datetime(2025, 4, 7, 21, 8, 34, 392400), datetime.datetime(2025, 4, 7, 21, 8, 52, 523100), datetime.datetime(2025, 4, 7, 21, 9, 2, 212000), datetime.datetime(2025, 4, 7, 21, 9, 13, 301100), datetime.datetime(2025, 4, 7, 21, 14, 13, 755300), datetime.datetime(2025, 4, 7, 21, 11, 54, 496900), datetime.datetime(2025, 4, 7, 21, 12, 7, 594700), datetime.datetime(2025, 4, 7, 21, 12, 25, 849500), datetime.datetime(2025, 4, 7, 21, 12, 36, 508700), datetime.datetime(2025, 4, 7, 21, 12, 47, 110100), datetime.datetime(2025, 4, 7, 21, 12, 54, 915100), datetime.datetime(2025, 4, 7, 21, 16, 46, 868000), datetime.datetime(2025, 4, 7, 21, 15, 3, 393700), datetime.datetime(2025, 4, 7, 21, 15, 19, 297200), datetime.datetime(2025, 4, 7, 21, 15, 33, 221600), datetime.datetime(2025, 4, 7, 21, 15, 54, 974300), datetime.datetime(2025, 4, 7, 21, 16, 0, 280800), datetime.datetime(2025, 4, 7, 21, 16, 11, 254300), datetime.datetime(2025, 4, 7, 21, 17, 57, 818500), datetime.datetime(2025, 4, 7, 21, 17, 17, 365700), datetime.datetime(2025, 4, 7, 21, 17, 34, 313200), datetime.datetime(2025, 4, 7, 21, 17, 45, 146900), datetime.datetime(2025, 4, 7, 21, 17, 50, 398100), datetime.datetime(2025, 4, 7, 21, 18, 22, 65200), datetime.datetime(2025, 4, 7, 21, 18, 21, 69700), datetime.datetime(2025, 4, 7, 21, 21, 52, 708100), datetime.datetime(2025, 4, 7, 21, 20, 27, 649700), datetime.datetime(2025, 4, 7, 21, 20, 29, 806200), datetime.datetime(2025, 4, 7, 21, 20, 41, 377400), datetime.datetime(2025, 4, 7, 21, 21, 0, 773500), datetime.datetime(2025, 4, 7, 21, 22, 9, 577000), datetime.datetime(2025, 4, 7, 21, 22, 9, 577000), datetime.datetime(2025, 4, 7, 21, 29, 1, 826200), datetime.datetime(2025, 4, 7, 21, 26, 42, 442300), datetime.datetime(2025, 4, 7, 21, 27, 19, 113700), datetime.datetime(2025, 4, 7, 21, 32, 30, 15900), datetime.datetime(2025, 4, 7, 21, 30, 6, 932800), datetime.datetime(2025, 4, 7, 21, 30, 22, 721800), datetime.datetime(2025, 4, 7, 21, 34, 3, 463300), datetime.datetime(2025, 4, 7, 21, 32, 28, 740000), datetime.datetime(2025, 4, 7, 21, 32, 45, 718900), datetime.datetime(2025, 4, 7, 21, 33, 11, 166800), datetime.datetime(2025, 4, 7, 21, 33, 33, 777900), datetime.datetime(2025, 4, 7, 21, 42, 34, 768700), datetime.datetime(2025, 4, 7, 21, 38, 24, 545900), datetime.datetime(2025, 4, 7, 21, 38, 27, 165500), datetime.datetime(2025, 4, 7, 21, 42, 2, 739300), datetime.datetime(2025, 4, 7, 21, 40, 45, 576000), datetime.datetime(2025, 4, 7, 21, 41, 59, 491500), datetime.datetime(2025, 4, 7, 21, 41, 47, 653400), datetime.datetime(2025, 4, 7, 21, 42, 52, 533600), datetime.datetime(2025, 4, 7, 21, 42, 33, 386400), datetime.datetime(2025, 4, 7, 21, 42, 43, 919400), datetime.datetime(2025, 4, 7, 21, 42, 56, 544400), datetime.datetime(2025, 4, 7, 21, 43, 10, 33900), datetime.datetime(2025, 4, 7, 21, 43, 43, 117500)]</t>
+        </is>
+      </c>
+      <c r="AE34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>162</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>67ee72bf64a45fade8b7b685</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>KMJQ9N</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>35</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>yes i understand game strategies</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>45754.90846418904</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 20, 47, 57, 568000), datetime.datetime(2025, 4, 7, 20, 47, 24, 718000), datetime.datetime(2025, 4, 7, 20, 49, 10, 22000), datetime.datetime(2025, 4, 7, 20, 49, 30, 737000), datetime.datetime(2025, 4, 7, 20, 49, 48, 261000), datetime.datetime(2025, 4, 7, 20, 51, 21, 650000), datetime.datetime(2025, 4, 7, 20, 50, 53, 42000), datetime.datetime(2025, 4, 7, 20, 51, 18, 23000), datetime.datetime(2025, 4, 7, 20, 51, 54, 300000), datetime.datetime(2025, 4, 7, 20, 52, 1, 686000), datetime.datetime(2025, 4, 7, 20, 52, 38, 301000), datetime.datetime(2025, 4, 7, 20, 52, 35, 861000), datetime.datetime(2025, 4, 7, 20, 53, 5, 53000), datetime.datetime(2025, 4, 7, 20, 53, 16, 466000), datetime.datetime(2025, 4, 7, 20, 53, 42, 429000), datetime.datetime(2025, 4, 7, 20, 56, 17, 787000), datetime.datetime(2025, 4, 7, 20, 55, 52, 421000), datetime.datetime(2025, 4, 7, 20, 56, 39, 706000), datetime.datetime(2025, 4, 7, 20, 57, 35, 556000), datetime.datetime(2025, 4, 7, 20, 57, 25, 206000), datetime.datetime(2025, 4, 7, 20, 59, 31, 13000), datetime.datetime(2025, 4, 7, 20, 59, 13, 801000), datetime.datetime(2025, 4, 7, 21, 0, 0, 106000), datetime.datetime(2025, 4, 7, 21, 0, 4, 120000), datetime.datetime(2025, 4, 7, 21, 1, 3, 924000), datetime.datetime(2025, 4, 7, 21, 1, 8, 871000), datetime.datetime(2025, 4, 7, 21, 2, 20, 314000), datetime.datetime(2025, 4, 7, 21, 2, 35, 924000), datetime.datetime(2025, 4, 7, 21, 2, 40, 831000), datetime.datetime(2025, 4, 7, 21, 3, 53, 949000), datetime.datetime(2025, 4, 7, 21, 3, 45, 218000), datetime.datetime(2025, 4, 7, 21, 4, 31, 35000), datetime.datetime(2025, 4, 7, 21, 4, 25, 687000), datetime.datetime(2025, 4, 7, 21, 6, 58, 192000), datetime.datetime(2025, 4, 7, 21, 6, 3, 306000), datetime.datetime(2025, 4, 7, 21, 6, 23, 246000), datetime.datetime(2025, 4, 7, 21, 6, 39, 795000), datetime.datetime(2025, 4, 7, 21, 9, 7, 761000), datetime.datetime(2025, 4, 7, 21, 8, 55, 653000), datetime.datetime(2025, 4, 7, 21, 9, 33, 954000), datetime.datetime(2025, 4, 7, 21, 9, 36, 978000), datetime.datetime(2025, 4, 7, 21, 10, 22, 899000), datetime.datetime(2025, 4, 7, 21, 10, 53, 219000), datetime.datetime(2025, 4, 7, 21, 11, 41, 839000), datetime.datetime(2025, 4, 7, 21, 12, 21, 643000), datetime.datetime(2025, 4, 7, 21, 12, 22, 813000), datetime.datetime(2025, 4, 7, 21, 13, 17, 457000), datetime.datetime(2025, 4, 7, 21, 13, 25, 361000), datetime.datetime(2025, 4, 7, 21, 14, 26, 288000), datetime.datetime(2025, 4, 7, 21, 14, 29, 7000), datetime.datetime(2025, 4, 7, 21, 15, 40, 254000), datetime.datetime(2025, 4, 7, 21, 15, 17, 43000), datetime.datetime(2025, 4, 7, 21, 15, 38, 302000), datetime.datetime(2025, 4, 7, 21, 15, 56, 17000), datetime.datetime(2025, 4, 7, 21, 16, 23, 590000), datetime.datetime(2025, 4, 7, 21, 16, 44, 795000), datetime.datetime(2025, 4, 7, 21, 17, 48, 286000), datetime.datetime(2025, 4, 7, 21, 17, 29, 656000), datetime.datetime(2025, 4, 7, 21, 18, 22, 418000), datetime.datetime(2025, 4, 7, 21, 18, 52, 356000), datetime.datetime(2025, 4, 7, 21, 19, 58, 99000), datetime.datetime(2025, 4, 7, 21, 19, 51, 208000), datetime.datetime(2025, 4, 7, 21, 20, 44, 237000), datetime.datetime(2025, 4, 7, 21, 20, 26, 182000), datetime.datetime(2025, 4, 7, 21, 20, 41, 989000), datetime.datetime(2025, 4, 7, 21, 21, 13, 494000), datetime.datetime(2025, 4, 7, 21, 21, 30, 611000), datetime.datetime(2025, 4, 7, 21, 26, 4, 29000), datetime.datetime(2025, 4, 7, 21, 26, 4, 29000), datetime.datetime(2025, 4, 7, 21, 26, 50, 936000), datetime.datetime(2025, 4, 7, 21, 26, 46, 474000), datetime.datetime(2025, 4, 7, 21, 27, 24, 593000), datetime.datetime(2025, 4, 7, 21, 32, 33, 183000), datetime.datetime(2025, 4, 7, 21, 30, 15, 589000), datetime.datetime(2025, 4, 7, 21, 31, 22, 182000), datetime.datetime(2025, 4, 7, 21, 31, 39, 888000), datetime.datetime(2025, 4, 7, 21, 33, 26, 376000), datetime.datetime(2025, 4, 7, 21, 33, 3, 307000), datetime.datetime(2025, 4, 7, 21, 33, 37, 351000), datetime.datetime(2025, 4, 7, 21, 33, 44, 87000), datetime.datetime(2025, 4, 7, 21, 34, 6, 810000), datetime.datetime(2025, 4, 7, 21, 34, 35, 486000), datetime.datetime(2025, 4, 7, 21, 42, 10, 614000), datetime.datetime(2025, 4, 7, 21, 39, 1, 95000), datetime.datetime(2025, 4, 7, 21, 42, 21, 39000), datetime.datetime(2025, 4, 7, 21, 41, 6, 321000), datetime.datetime(2025, 4, 7, 21, 42, 4, 827000), datetime.datetime(2025, 4, 7, 21, 42, 5, 535000), datetime.datetime(2025, 4, 7, 21, 42, 40, 78000), datetime.datetime(2025, 4, 7, 21, 42, 41, 723000), datetime.datetime(2025, 4, 7, 21, 43, 8, 579000), datetime.datetime(2025, 4, 7, 21, 43, 40, 371000), datetime.datetime(2025, 4, 7, 21, 43, 48, 480000), datetime.datetime(2025, 4, 7, 21, 47, 5, 933000)]</t>
+        </is>
+      </c>
+      <c r="AE35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/simple_game_test/filtered_users.xlsx
+++ b/simple_game_test/filtered_users.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL35"/>
+  <dimension ref="A1:AL68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4426,6 +4426,3520 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>163</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>67709d0088d93adec607305e</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>FTK3XE</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>42</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>45754.97941618193</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 22, 41, 17, 353700), datetime.datetime(2025, 4, 7, 22, 40, 40, 940500), datetime.datetime(2025, 4, 7, 22, 41, 10, 616500), datetime.datetime(2025, 4, 7, 22, 41, 41, 204500), datetime.datetime(2025, 4, 7, 22, 48, 0, 908000), datetime.datetime(2025, 4, 7, 22, 45, 19, 820500), datetime.datetime(2025, 4, 7, 22, 45, 45, 860400), datetime.datetime(2025, 4, 7, 22, 45, 53, 657900), datetime.datetime(2025, 4, 7, 22, 46, 41, 456200), datetime.datetime(2025, 4, 7, 22, 46, 43, 511300), datetime.datetime(2025, 4, 7, 22, 47, 17, 454600), datetime.datetime(2025, 4, 7, 22, 47, 39, 892100), datetime.datetime(2025, 4, 7, 22, 48, 12, 361100), datetime.datetime(2025, 4, 7, 22, 49, 44, 92900), datetime.datetime(2025, 4, 7, 22, 49, 14, 780700), datetime.datetime(2025, 4, 7, 22, 49, 40, 640600), datetime.datetime(2025, 4, 7, 22, 50, 22, 757200), datetime.datetime(2025, 4, 7, 22, 50, 47, 34500), datetime.datetime(2025, 4, 7, 22, 50, 42, 798400), datetime.datetime(2025, 4, 7, 22, 51, 18, 313000), datetime.datetime(2025, 4, 7, 22, 51, 36, 312000), datetime.datetime(2025, 4, 7, 22, 52, 6, 917000), datetime.datetime(2025, 4, 7, 22, 52, 10, 651400), datetime.datetime(2025, 4, 7, 22, 52, 53, 960100), datetime.datetime(2025, 4, 7, 22, 53, 9, 181100), datetime.datetime(2025, 4, 7, 22, 53, 52, 197300), datetime.datetime(2025, 4, 7, 22, 53, 56, 596100), datetime.datetime(2025, 4, 7, 22, 54, 14, 642800), datetime.datetime(2025, 4, 7, 22, 54, 26, 565900), datetime.datetime(2025, 4, 7, 22, 54, 52, 873200), datetime.datetime(2025, 4, 7, 22, 55, 27, 884100), datetime.datetime(2025, 4, 7, 22, 56, 4, 167800), datetime.datetime(2025, 4, 7, 22, 56, 56, 22600), datetime.datetime(2025, 4, 7, 22, 56, 45, 266500), datetime.datetime(2025, 4, 7, 22, 57, 15, 199200), datetime.datetime(2025, 4, 7, 22, 57, 42, 530400), datetime.datetime(2025, 4, 7, 22, 58, 17, 557700), datetime.datetime(2025, 4, 7, 22, 58, 34, 183300), datetime.datetime(2025, 4, 7, 22, 59, 31, 976800), datetime.datetime(2025, 4, 7, 22, 59, 31, 461100), datetime.datetime(2025, 4, 7, 23, 0, 39, 81500), datetime.datetime(2025, 4, 7, 23, 0, 25, 559900), datetime.datetime(2025, 4, 7, 23, 0, 45, 801300), datetime.datetime(2025, 4, 7, 23, 1, 9, 19100), datetime.datetime(2025, 4, 7, 23, 1, 27, 475600), datetime.datetime(2025, 4, 7, 23, 3, 14, 120000), datetime.datetime(2025, 4, 7, 23, 3, 14, 120000), datetime.datetime(2025, 4, 7, 23, 5, 16, 35700), datetime.datetime(2025, 4, 7, 23, 5, 11, 263400), datetime.datetime(2025, 4, 7, 23, 5, 31, 655900), datetime.datetime(2025, 4, 7, 23, 5, 44, 15500), datetime.datetime(2025, 4, 7, 23, 5, 59, 239900), datetime.datetime(2025, 4, 7, 23, 8, 16, 295400), datetime.datetime(2025, 4, 7, 23, 7, 23, 418700), datetime.datetime(2025, 4, 7, 23, 7, 39, 316700), datetime.datetime(2025, 4, 7, 23, 7, 49, 783200), datetime.datetime(2025, 4, 7, 23, 10, 22, 904700), datetime.datetime(2025, 4, 7, 23, 9, 23, 599600), datetime.datetime(2025, 4, 7, 23, 9, 37, 925300), datetime.datetime(2025, 4, 7, 23, 9, 46, 632000), datetime.datetime(2025, 4, 7, 23, 9, 57, 513100), datetime.datetime(2025, 4, 7, 23, 11, 29, 296400), datetime.datetime(2025, 4, 7, 23, 10, 56, 146400), datetime.datetime(2025, 4, 7, 23, 11, 12, 823500), datetime.datetime(2025, 4, 7, 23, 11, 21, 428600), datetime.datetime(2025, 4, 7, 23, 15, 18, 386800), datetime.datetime(2025, 4, 7, 23, 13, 47, 289900), datetime.datetime(2025, 4, 7, 23, 14, 10, 876500), datetime.datetime(2025, 4, 7, 23, 14, 20, 831800), datetime.datetime(2025, 4, 7, 23, 18, 21, 241900), datetime.datetime(2025, 4, 7, 23, 16, 36, 255700), datetime.datetime(2025, 4, 7, 23, 16, 44, 592400), datetime.datetime(2025, 4, 7, 23, 16, 55, 344200), datetime.datetime(2025, 4, 7, 23, 17, 4, 328100), datetime.datetime(2025, 4, 7, 23, 17, 28, 41100), datetime.datetime(2025, 4, 7, 23, 17, 32, 140300), datetime.datetime(2025, 4, 7, 23, 17, 47, 52500), datetime.datetime(2025, 4, 7, 23, 18, 7, 829200), datetime.datetime(2025, 4, 7, 23, 27, 26, 700200), datetime.datetime(2025, 4, 7, 23, 22, 57, 536400), datetime.datetime(2025, 4, 7, 23, 23, 7, 579000), datetime.datetime(2025, 4, 7, 23, 23, 37, 552500), datetime.datetime(2025, 4, 7, 23, 23, 44, 294000), datetime.datetime(2025, 4, 7, 23, 23, 54, 48300), datetime.datetime(2025, 4, 7, 23, 24, 20, 522100), datetime.datetime(2025, 4, 7, 23, 26, 9, 352900), datetime.datetime(2025, 4, 7, 23, 25, 22, 562200), datetime.datetime(2025, 4, 7, 23, 25, 50, 873200), datetime.datetime(2025, 4, 7, 23, 25, 57, 281400), datetime.datetime(2025, 4, 7, 23, 26, 24, 26500), datetime.datetime(2025, 4, 7, 23, 26, 26, 114100), datetime.datetime(2025, 4, 7, 23, 27, 48, 762800), datetime.datetime(2025, 4, 7, 23, 27, 42, 25600), datetime.datetime(2025, 4, 7, 23, 28, 41, 305600), datetime.datetime(2025, 4, 7, 23, 28, 18, 832600), datetime.datetime(2025, 4, 7, 23, 28, 31, 355100), datetime.datetime(2025, 4, 7, 23, 28, 40, 915200), datetime.datetime(2025, 4, 7, 23, 28, 51, 987100), datetime.datetime(2025, 4, 7, 23, 29, 28, 370800)]</t>
+        </is>
+      </c>
+      <c r="AE36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>47</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="n">
+        <v>47</v>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>164</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>65de3aa60d4695de8df8e49e</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>CT6O0F</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>45754.94062792322</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>165</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5cfff88a6775b90001e484f2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>DPND5I</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>removed_due_to_inactivity</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>45754.94712584196</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 22, 44, 12, 481200), datetime.datetime(2025, 4, 7, 22, 44, 58, 560100)]</t>
+        </is>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>47</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="n">
+        <v>47</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>166</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>65555ad794df5e3308b4b09a</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>NXZTSR</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>49</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>[4]</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>I think it is a little confusing but I always understood the strategy eventually. The instructions helped a lot.</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>45754.97958817779</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA39" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 22, 39, 48, 743200), datetime.datetime(2025, 4, 7, 22, 40, 26, 668400), datetime.datetime(2025, 4, 7, 22, 40, 47, 747200), datetime.datetime(2025, 4, 7, 22, 41, 9, 879000), datetime.datetime(2025, 4, 7, 22, 48, 9, 835500), datetime.datetime(2025, 4, 7, 22, 45, 0, 854100), datetime.datetime(2025, 4, 7, 22, 45, 27, 482900), datetime.datetime(2025, 4, 7, 22, 47, 10, 924200), datetime.datetime(2025, 4, 7, 22, 46, 44, 103400), datetime.datetime(2025, 4, 7, 22, 47, 15, 841800), datetime.datetime(2025, 4, 7, 22, 48, 8, 327100), datetime.datetime(2025, 4, 7, 22, 48, 11, 345300), datetime.datetime(2025, 4, 7, 22, 48, 22, 216000), datetime.datetime(2025, 4, 7, 22, 49, 9, 61900), datetime.datetime(2025, 4, 7, 22, 48, 59, 200900), datetime.datetime(2025, 4, 7, 22, 49, 21, 765300), datetime.datetime(2025, 4, 7, 22, 49, 43, 461200), datetime.datetime(2025, 4, 7, 22, 51, 6, 922400), datetime.datetime(2025, 4, 7, 22, 50, 39, 513500), datetime.datetime(2025, 4, 7, 22, 51, 4, 253700), datetime.datetime(2025, 4, 7, 22, 51, 16, 570100), datetime.datetime(2025, 4, 7, 22, 51, 31, 365800), datetime.datetime(2025, 4, 7, 22, 51, 40, 992200), datetime.datetime(2025, 4, 7, 22, 53, 14, 56100), datetime.datetime(2025, 4, 7, 22, 52, 49, 167600), datetime.datetime(2025, 4, 7, 22, 53, 3, 480400), datetime.datetime(2025, 4, 7, 22, 53, 40, 438700), datetime.datetime(2025, 4, 7, 22, 53, 47, 349400), datetime.datetime(2025, 4, 7, 22, 54, 9, 193600), datetime.datetime(2025, 4, 7, 22, 54, 23, 550000), datetime.datetime(2025, 4, 7, 22, 54, 37, 291700), datetime.datetime(2025, 4, 7, 22, 56, 37, 267700), datetime.datetime(2025, 4, 7, 22, 56, 0, 169800), datetime.datetime(2025, 4, 7, 22, 56, 27, 152500), datetime.datetime(2025, 4, 7, 22, 56, 39, 626200), datetime.datetime(2025, 4, 7, 22, 59, 3, 839800), datetime.datetime(2025, 4, 7, 22, 58, 23, 893300), datetime.datetime(2025, 4, 7, 22, 58, 33, 114800), datetime.datetime(2025, 4, 7, 22, 59, 38, 97100), datetime.datetime(2025, 4, 7, 22, 59, 50, 182400), datetime.datetime(2025, 4, 7, 23, 0, 41, 186800), datetime.datetime(2025, 4, 7, 23, 0, 35, 881200), datetime.datetime(2025, 4, 7, 23, 0, 53, 498600), datetime.datetime(2025, 4, 7, 23, 1, 3, 473800), datetime.datetime(2025, 4, 7, 23, 1, 19, 744300), datetime.datetime(2025, 4, 7, 23, 2, 50, 786400), datetime.datetime(2025, 4, 7, 23, 2, 50, 786400), datetime.datetime(2025, 4, 7, 23, 5, 21, 199100), datetime.datetime(2025, 4, 7, 23, 4, 41, 885100), datetime.datetime(2025, 4, 7, 23, 5, 17, 349600), datetime.datetime(2025, 4, 7, 23, 6, 47, 340700), datetime.datetime(2025, 4, 7, 23, 6, 24, 596300), datetime.datetime(2025, 4, 7, 23, 6, 55, 715300), datetime.datetime(2025, 4, 7, 23, 7, 27, 320100), datetime.datetime(2025, 4, 7, 23, 7, 40, 588000), datetime.datetime(2025, 4, 7, 23, 7, 45, 742800), datetime.datetime(2025, 4, 7, 23, 8, 27, 590000), datetime.datetime(2025, 4, 7, 23, 9, 6, 571500), datetime.datetime(2025, 4, 7, 23, 9, 23, 661300), datetime.datetime(2025, 4, 7, 23, 9, 34, 296200), datetime.datetime(2025, 4, 7, 23, 10, 17, 322200), datetime.datetime(2025, 4, 7, 23, 10, 29, 560800), datetime.datetime(2025, 4, 7, 23, 11, 20, 238000), datetime.datetime(2025, 4, 7, 23, 11, 32, 44300), datetime.datetime(2025, 4, 7, 23, 12, 9, 72900), datetime.datetime(2025, 4, 7, 23, 12, 12, 898900), datetime.datetime(2025, 4, 7, 23, 12, 31, 931000), datetime.datetime(2025, 4, 7, 23, 13, 12, 638300), datetime.datetime(2025, 4, 7, 23, 13, 49, 55600), datetime.datetime(2025, 4, 7, 23, 13, 43, 963000), datetime.datetime(2025, 4, 7, 23, 14, 31, 338700), datetime.datetime(2025, 4, 7, 23, 15, 16, 76700), datetime.datetime(2025, 4, 7, 23, 17, 38, 635200), datetime.datetime(2025, 4, 7, 23, 17, 40, 375100), datetime.datetime(2025, 4, 7, 23, 18, 4, 989500), datetime.datetime(2025, 4, 7, 23, 17, 55, 58000), datetime.datetime(2025, 4, 7, 23, 18, 8, 895600), datetime.datetime(2025, 4, 7, 23, 18, 57, 990900), datetime.datetime(2025, 4, 7, 23, 18, 59, 246900), datetime.datetime(2025, 4, 7, 23, 20, 38, 504000), datetime.datetime(2025, 4, 7, 23, 20, 16, 389800), datetime.datetime(2025, 4, 7, 23, 23, 48, 554600), datetime.datetime(2025, 4, 7, 23, 23, 33, 159300), datetime.datetime(2025, 4, 7, 23, 23, 25, 480800), datetime.datetime(2025, 4, 7, 23, 23, 40, 858500), datetime.datetime(2025, 4, 7, 23, 23, 52, 127000), datetime.datetime(2025, 4, 7, 23, 24, 11, 424700), datetime.datetime(2025, 4, 7, 23, 24, 24, 281200), datetime.datetime(2025, 4, 7, 23, 24, 53, 417700), datetime.datetime(2025, 4, 7, 23, 25, 30, 846900), datetime.datetime(2025, 4, 7, 23, 25, 32, 983600), datetime.datetime(2025, 4, 7, 23, 25, 49, 367000), datetime.datetime(2025, 4, 7, 23, 25, 56, 535400), datetime.datetime(2025, 4, 7, 23, 26, 27, 626400), datetime.datetime(2025, 4, 7, 23, 26, 44, 786100), datetime.datetime(2025, 4, 7, 23, 27, 51, 894500), datetime.datetime(2025, 4, 7, 23, 27, 48, 283500), datetime.datetime(2025, 4, 7, 23, 28, 22, 794200), datetime.datetime(2025, 4, 7, 23, 28, 19, 731900), datetime.datetime(2025, 4, 7, 23, 28, 29, 797900), datetime.datetime(2025, 4, 7, 23, 28, 43, 843500), datetime.datetime(2025, 4, 7, 23, 28, 54, 596100), datetime.datetime(2025, 4, 7, 23, 29, 28, 313600)]</t>
+        </is>
+      </c>
+      <c r="AE39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>167</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>67a95540dda6841d514b9c17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>SMPDGZ</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>post practice</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>45754.98047436514</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>diagnostic feedback</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 23, 18, 49, 780300), datetime.datetime(2025, 4, 7, 23, 18, 14, 935100), datetime.datetime(2025, 4, 7, 23, 19, 5, 469500), datetime.datetime(2025, 4, 7, 23, 19, 38, 17200), datetime.datetime(2025, 4, 7, 23, 20, 22, 923500), datetime.datetime(2025, 4, 7, 23, 20, 15, 490700), datetime.datetime(2025, 4, 7, 23, 20, 50, 804300), datetime.datetime(2025, 4, 7, 23, 20, 52, 690000), datetime.datetime(2025, 4, 7, 23, 23, 42, 527000), datetime.datetime(2025, 4, 7, 23, 23, 11, 999800), datetime.datetime(2025, 4, 7, 23, 24, 12, 272400), datetime.datetime(2025, 4, 7, 23, 23, 49, 142700), datetime.datetime(2025, 4, 7, 23, 24, 59, 799000), datetime.datetime(2025, 4, 7, 23, 25, 17, 548100), datetime.datetime(2025, 4, 7, 23, 25, 16, 96800), datetime.datetime(2025, 4, 7, 23, 25, 36, 23300), datetime.datetime(2025, 4, 7, 23, 25, 53, 365100), datetime.datetime(2025, 4, 7, 23, 25, 59, 94700), datetime.datetime(2025, 4, 7, 23, 29, 6, 978600), datetime.datetime(2025, 4, 7, 23, 27, 55, 520600), datetime.datetime(2025, 4, 7, 23, 28, 12, 979500), datetime.datetime(2025, 4, 7, 23, 28, 12, 979500)]</t>
+        </is>
+      </c>
+      <c r="AE40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>49</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="n">
+        <v>49</v>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>168</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>67662a2073c335e033cd9e0e</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>CZ61KL</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>45755.01086164892</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>diagnostic feedback</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 7, 23, 17, 9, 393800), datetime.datetime(2025, 4, 7, 23, 17, 11, 902100), datetime.datetime(2025, 4, 7, 23, 17, 5, 518300), datetime.datetime(2025, 4, 7, 23, 17, 18, 387200), datetime.datetime(2025, 4, 7, 23, 18, 0, 426700), datetime.datetime(2025, 4, 7, 23, 18, 27, 468100), datetime.datetime(2025, 4, 7, 23, 21, 32, 333500), datetime.datetime(2025, 4, 7, 23, 20, 30, 849200), datetime.datetime(2025, 4, 7, 23, 21, 7, 712600), datetime.datetime(2025, 4, 7, 23, 21, 15, 692500), datetime.datetime(2025, 4, 7, 23, 22, 56, 741200), datetime.datetime(2025, 4, 7, 23, 22, 28, 667200), datetime.datetime(2025, 4, 7, 23, 23, 29, 795700), datetime.datetime(2025, 4, 7, 23, 23, 25, 155100), datetime.datetime(2025, 4, 7, 23, 23, 47, 954200), datetime.datetime(2025, 4, 7, 23, 23, 59, 354400), datetime.datetime(2025, 4, 7, 23, 26, 14, 632500), datetime.datetime(2025, 4, 7, 23, 25, 32, 946300), datetime.datetime(2025, 4, 7, 23, 25, 49, 84000), datetime.datetime(2025, 4, 7, 23, 26, 3, 911800), datetime.datetime(2025, 4, 7, 23, 26, 12, 195400), datetime.datetime(2025, 4, 7, 23, 29, 1, 696300), datetime.datetime(2025, 4, 7, 23, 27, 50, 302900), datetime.datetime(2025, 4, 7, 23, 28, 30, 618800), datetime.datetime(2025, 4, 7, 23, 28, 39, 514600), datetime.datetime(2025, 4, 7, 23, 29, 4, 821400), datetime.datetime(2025, 4, 7, 23, 33, 10, 770700), datetime.datetime(2025, 4, 7, 23, 31, 32, 679400), datetime.datetime(2025, 4, 7, 23, 33, 24, 488300), datetime.datetime(2025, 4, 7, 23, 33, 25, 774700), datetime.datetime(2025, 4, 7, 23, 33, 41, 585500), datetime.datetime(2025, 4, 7, 23, 33, 54, 630300), datetime.datetime(2025, 4, 7, 23, 34, 5, 764000), datetime.datetime(2025, 4, 7, 23, 34, 56, 449300), datetime.datetime(2025, 4, 7, 23, 34, 49, 674700), datetime.datetime(2025, 4, 7, 23, 35, 46, 304500), datetime.datetime(2025, 4, 7, 23, 36, 13, 152300), datetime.datetime(2025, 4, 7, 23, 36, 13, 677300), datetime.datetime(2025, 4, 7, 23, 37, 56, 49800), datetime.datetime(2025, 4, 7, 23, 37, 35, 652600), datetime.datetime(2025, 4, 7, 23, 38, 45, 680900), datetime.datetime(2025, 4, 7, 23, 38, 39, 880300), datetime.datetime(2025, 4, 7, 23, 39, 40, 447100), datetime.datetime(2025, 4, 7, 23, 39, 28, 613900), datetime.datetime(2025, 4, 7, 23, 39, 39, 71900), datetime.datetime(2025, 4, 7, 23, 40, 15, 85100), datetime.datetime(2025, 4, 7, 23, 40, 16, 818300), datetime.datetime(2025, 4, 7, 23, 41, 31, 358200), datetime.datetime(2025, 4, 7, 23, 41, 31, 358200), datetime.datetime(2025, 4, 7, 23, 45, 47, 707900), datetime.datetime(2025, 4, 7, 23, 45, 57, 104000), datetime.datetime(2025, 4, 7, 23, 46, 3, 469000), datetime.datetime(2025, 4, 7, 23, 46, 8, 312600), datetime.datetime(2025, 4, 7, 23, 46, 24, 771000), datetime.datetime(2025, 4, 7, 23, 46, 44, 317400), datetime.datetime(2025, 4, 7, 23, 47, 45, 148500), datetime.datetime(2025, 4, 7, 23, 47, 33, 227100), datetime.datetime(2025, 4, 7, 23, 49, 8, 131100), datetime.datetime(2025, 4, 7, 23, 48, 33, 55500), datetime.datetime(2025, 4, 7, 23, 48, 45, 733200), datetime.datetime(2025, 4, 7, 23, 48, 55, 775700), datetime.datetime(2025, 4, 8, 0, 3, 18, 617800), datetime.datetime(2025, 4, 7, 23, 56, 29, 637900), datetime.datetime(2025, 4, 7, 23, 56, 35, 707800), datetime.datetime(2025, 4, 7, 23, 56, 50, 881800), datetime.datetime(2025, 4, 7, 23, 57, 13, 433100), datetime.datetime(2025, 4, 7, 23, 57, 26, 446100), datetime.datetime(2025, 4, 7, 23, 58, 3, 276700), datetime.datetime(2025, 4, 7, 23, 58, 4, 558300), datetime.datetime(2025, 4, 7, 23, 58, 13, 483300), datetime.datetime(2025, 4, 7, 23, 58, 36, 211200), datetime.datetime(2025, 4, 7, 23, 58, 46, 590600), datetime.datetime(2025, 4, 7, 23, 58, 59, 417800), datetime.datetime(2025, 4, 7, 23, 59, 53, 124300), datetime.datetime(2025, 4, 7, 23, 59, 39, 349400), datetime.datetime(2025, 4, 8, 0, 0, 6, 283200), datetime.datetime(2025, 4, 8, 0, 1, 18, 148700), datetime.datetime(2025, 4, 8, 0, 1, 16, 285300)]</t>
+        </is>
+      </c>
+      <c r="AE41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>49</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="n">
+        <v>49</v>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>169</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>6519ce2a3291465da90a7b62</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>NR4WB3</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>45754.95571070151</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>170</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>67558a78aa571bda11e0a217</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>PV0PV0</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>45754.99691191199</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>diagnostic test</t>
+        </is>
+      </c>
+      <c r="AA43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 8, 0, 16, 59, 633200), datetime.datetime(2025, 4, 8, 0, 16, 57, 587700), datetime.datetime(2025, 4, 8, 0, 18, 41, 735300), datetime.datetime(2025, 4, 8, 0, 18, 13, 970500), datetime.datetime(2025, 4, 8, 0, 22, 34, 590100), datetime.datetime(2025, 4, 8, 0, 20, 56, 616300), datetime.datetime(2025, 4, 8, 0, 21, 50, 520400), datetime.datetime(2025, 4, 8, 0, 21, 59, 883300), datetime.datetime(2025, 4, 8, 0, 22, 49, 715700), datetime.datetime(2025, 4, 8, 0, 22, 43, 367800), datetime.datetime(2025, 4, 8, 0, 24, 5, 473900), datetime.datetime(2025, 4, 8, 0, 24, 0, 163200), datetime.datetime(2025, 4, 8, 0, 24, 20, 613800), datetime.datetime(2025, 4, 8, 0, 24, 31, 368500), datetime.datetime(2025, 4, 8, 0, 26, 19, 98200), datetime.datetime(2025, 4, 8, 0, 25, 49, 578600), datetime.datetime(2025, 4, 8, 0, 26, 47, 521100), datetime.datetime(2025, 4, 8, 0, 26, 55, 881800), datetime.datetime(2025, 4, 8, 0, 27, 37, 114500), datetime.datetime(2025, 4, 8, 0, 27, 35, 405800), datetime.datetime(2025, 4, 8, 0, 28, 41, 842200), datetime.datetime(2025, 4, 8, 0, 29, 6, 524100), datetime.datetime(2025, 4, 8, 0, 29, 21, 230100), datetime.datetime(2025, 4, 8, 0, 29, 48, 311600), datetime.datetime(2025, 4, 8, 0, 29, 56, 773800), datetime.datetime(2025, 4, 8, 0, 32, 16, 156200), datetime.datetime(2025, 4, 8, 0, 31, 43, 316100), datetime.datetime(2025, 4, 8, 0, 31, 47, 723900), datetime.datetime(2025, 4, 8, 0, 32, 43, 612700), datetime.datetime(2025, 4, 8, 0, 32, 42, 13200), datetime.datetime(2025, 4, 8, 0, 33, 3, 486600), datetime.datetime(2025, 4, 8, 0, 33, 24, 899200), datetime.datetime(2025, 4, 8, 0, 33, 48, 227000), datetime.datetime(2025, 4, 8, 0, 34, 41, 140800), datetime.datetime(2025, 4, 8, 0, 35, 30, 69400), datetime.datetime(2025, 4, 8, 0, 35, 30, 561000), datetime.datetime(2025, 4, 8, 0, 35, 54, 16500), datetime.datetime(2025, 4, 8, 0, 36, 23, 532200), datetime.datetime(2025, 4, 8, 0, 36, 35, 762500), datetime.datetime(2025, 4, 8, 0, 36, 44, 326400), datetime.datetime(2025, 4, 8, 0, 37, 41, 98300), datetime.datetime(2025, 4, 8, 0, 37, 48, 127200), datetime.datetime(2025, 4, 8, 0, 38, 6, 373600), datetime.datetime(2025, 4, 8, 0, 38, 55, 793900), datetime.datetime(2025, 4, 8, 0, 39, 14, 700100), datetime.datetime(2025, 4, 8, 0, 39, 54, 422000), datetime.datetime(2025, 4, 8, 0, 39, 54, 302300), datetime.datetime(2025, 4, 8, 0, 40, 2, 519100), datetime.datetime(2025, 4, 8, 0, 40, 28, 887400), datetime.datetime(2025, 4, 8, 0, 40, 47, 549300), datetime.datetime(2025, 4, 8, 0, 41, 14, 988700), datetime.datetime(2025, 4, 8, 0, 41, 14, 988700), datetime.datetime(2025, 4, 8, 0, 48, 6, 507000), datetime.datetime(2025, 4, 8, 0, 45, 16, 529000), datetime.datetime(2025, 4, 8, 0, 45, 34, 612200), datetime.datetime(2025, 4, 8, 0, 45, 39, 313500), datetime.datetime(2025, 4, 8, 0, 45, 49, 701800), datetime.datetime(2025, 4, 8, 0, 46, 7, 692000), datetime.datetime(2025, 4, 8, 0, 49, 8, 406000), datetime.datetime(2025, 4, 8, 0, 50, 1, 861700), datetime.datetime(2025, 4, 8, 0, 50, 22, 601800), datetime.datetime(2025, 4, 8, 0, 50, 55, 917300)]</t>
+        </is>
+      </c>
+      <c r="AE43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>49</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="n">
+        <v>49</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>171</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>67f02e4aa6132647f0172d46</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>DICJ8K</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>45754.96634300919</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>172</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5e571601a5b2230d6d2cb29e</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>CH02SX</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>45754.99126908887</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>173</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>67efefb887fe06ac1e551c3c</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ULV8AJ</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>45755.05982530466</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>174</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>67f2a908ade3b552f3fbfbcc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>QO5QW1</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>45755.21918525758</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>diagnostic feedback</t>
+        </is>
+      </c>
+      <c r="AA47" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 8, 1, 42, 44, 573800), datetime.datetime(2025, 4, 8, 1, 42, 38, 696700), datetime.datetime(2025, 4, 8, 1, 44, 19, 923400), datetime.datetime(2025, 4, 8, 1, 45, 1, 17500), datetime.datetime(2025, 4, 8, 1, 45, 51, 176500), datetime.datetime(2025, 4, 8, 1, 46, 8, 310100), datetime.datetime(2025, 4, 8, 1, 47, 37, 124000), datetime.datetime(2025, 4, 8, 1, 47, 14, 424300), datetime.datetime(2025, 4, 8, 1, 48, 12, 851300), datetime.datetime(2025, 4, 8, 1, 48, 17, 888800), datetime.datetime(2025, 4, 8, 1, 48, 47, 563600), datetime.datetime(2025, 4, 8, 1, 49, 10, 498200), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800), datetime.datetime(2025, 4, 8, 1, 55, 29, 77800)]</t>
+        </is>
+      </c>
+      <c r="AE47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>175</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5fa347426528964fed84cb3d</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2WPCXN</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>45755.08355850044</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>diagnostic feedback</t>
+        </is>
+      </c>
+      <c r="AA48" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 8, 1, 41, 9, 627900), datetime.datetime(2025, 4, 8, 1, 42, 5, 85200), datetime.datetime(2025, 4, 8, 1, 42, 17, 697800), datetime.datetime(2025, 4, 8, 1, 46, 18, 740500), datetime.datetime(2025, 4, 8, 1, 44, 51, 822800), datetime.datetime(2025, 4, 8, 1, 46, 43, 874700), datetime.datetime(2025, 4, 8, 1, 49, 42, 120800), datetime.datetime(2025, 4, 8, 1, 49, 34, 357200), datetime.datetime(2025, 4, 8, 1, 49, 58, 548300), datetime.datetime(2025, 4, 8, 1, 51, 20, 5300), datetime.datetime(2025, 4, 8, 1, 51, 15, 649400), datetime.datetime(2025, 4, 8, 1, 52, 15, 239800), datetime.datetime(2025, 4, 8, 1, 52, 15, 239800), datetime.datetime(2025, 4, 8, 1, 52, 15, 239800), datetime.datetime(2025, 4, 8, 1, 52, 15, 239800), datetime.datetime(2025, 4, 8, 1, 52, 15, 239800)]</t>
+        </is>
+      </c>
+      <c r="AE48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>176</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>6755e9c458096939d31dd317</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>U9Z6BI</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>45755.07970082702</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>diagnostic feedback</t>
+        </is>
+      </c>
+      <c r="AA49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 8, 1, 37, 40, 920900), datetime.datetime(2025, 4, 8, 1, 37, 29, 706700), datetime.datetime(2025, 4, 8, 1, 37, 52, 6700), datetime.datetime(2025, 4, 8, 1, 38, 7, 35400), datetime.datetime(2025, 4, 8, 1, 38, 8, 322400), datetime.datetime(2025, 4, 8, 1, 38, 16, 55300), datetime.datetime(2025, 4, 8, 1, 38, 16, 55300), datetime.datetime(2025, 4, 8, 1, 38, 16, 55300), datetime.datetime(2025, 4, 8, 1, 54, 10, 409200), datetime.datetime(2025, 4, 8, 1, 46, 38, 723900), datetime.datetime(2025, 4, 8, 1, 46, 52, 464800), datetime.datetime(2025, 4, 8, 1, 47, 8, 228200), datetime.datetime(2025, 4, 8, 1, 47, 11, 690300), datetime.datetime(2025, 4, 8, 1, 47, 11, 690300), datetime.datetime(2025, 4, 8, 1, 47, 11, 690300), datetime.datetime(2025, 4, 8, 1, 47, 11, 690300), datetime.datetime(2025, 4, 8, 1, 47, 11, 690300), datetime.datetime(2025, 4, 8, 1, 47, 11, 690300), datetime.datetime(2025, 4, 8, 1, 47, 11, 690300), datetime.datetime(2025, 4, 8, 1, 47, 11, 690300), datetime.datetime(2025, 4, 8, 1, 47, 11, 690300), datetime.datetime(2025, 4, 8, 1, 47, 11, 690300), datetime.datetime(2025, 4, 8, 1, 47, 11, 690300)]</t>
+        </is>
+      </c>
+      <c r="AE49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>178</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5a9bf9bd89de8200013f0f28</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>DDXHM6</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>33</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>45756.4599539831</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA50" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 10, 24, 13, 502700), datetime.datetime(2025, 4, 9, 10, 23, 42, 473400), datetime.datetime(2025, 4, 9, 10, 24, 18, 441900), datetime.datetime(2025, 4, 9, 10, 24, 30, 232400), datetime.datetime(2025, 4, 9, 10, 25, 31, 245600), datetime.datetime(2025, 4, 9, 10, 25, 18, 990900), datetime.datetime(2025, 4, 9, 10, 25, 53, 863300), datetime.datetime(2025, 4, 9, 10, 25, 58, 621100), datetime.datetime(2025, 4, 9, 10, 27, 10, 657000), datetime.datetime(2025, 4, 9, 10, 26, 54, 282000), datetime.datetime(2025, 4, 9, 10, 27, 15, 540400), datetime.datetime(2025, 4, 9, 10, 27, 23, 545800), datetime.datetime(2025, 4, 9, 10, 27, 46, 725800), datetime.datetime(2025, 4, 9, 10, 29, 57, 750600), datetime.datetime(2025, 4, 9, 10, 29, 4, 880700), datetime.datetime(2025, 4, 9, 10, 29, 27, 903100), datetime.datetime(2025, 4, 9, 10, 29, 50, 778000), datetime.datetime(2025, 4, 9, 10, 31, 30, 43800), datetime.datetime(2025, 4, 9, 10, 30, 52, 754200), datetime.datetime(2025, 4, 9, 10, 31, 47, 145000), datetime.datetime(2025, 4, 9, 10, 31, 36, 416800), datetime.datetime(2025, 4, 9, 10, 32, 21, 614000), datetime.datetime(2025, 4, 9, 10, 32, 22, 202600), datetime.datetime(2025, 4, 9, 10, 33, 56, 789500), datetime.datetime(2025, 4, 9, 10, 33, 38, 828200), datetime.datetime(2025, 4, 9, 10, 34, 28, 850300), datetime.datetime(2025, 4, 9, 10, 34, 22, 955600), datetime.datetime(2025, 4, 9, 10, 35, 34, 942500), datetime.datetime(2025, 4, 9, 10, 35, 14, 674600), datetime.datetime(2025, 4, 9, 10, 36, 0, 548300), datetime.datetime(2025, 4, 9, 10, 35, 50, 906200), datetime.datetime(2025, 4, 9, 10, 36, 9, 125800), datetime.datetime(2025, 4, 9, 10, 36, 17, 905800), datetime.datetime(2025, 4, 9, 10, 36, 37, 655400), datetime.datetime(2025, 4, 9, 10, 37, 36, 543500), datetime.datetime(2025, 4, 9, 10, 37, 36, 543500), datetime.datetime(2025, 4, 9, 10, 41, 19, 728200), datetime.datetime(2025, 4, 9, 10, 40, 1, 985100), datetime.datetime(2025, 4, 9, 10, 40, 13, 270900), datetime.datetime(2025, 4, 9, 10, 40, 21, 778100), datetime.datetime(2025, 4, 9, 10, 40, 31, 707300), datetime.datetime(2025, 4, 9, 10, 40, 49, 140800), datetime.datetime(2025, 4, 9, 10, 42, 34, 593000), datetime.datetime(2025, 4, 9, 10, 41, 57, 995000), datetime.datetime(2025, 4, 9, 10, 42, 4, 424400), datetime.datetime(2025, 4, 9, 10, 42, 13, 751000), datetime.datetime(2025, 4, 9, 10, 42, 41, 786700), datetime.datetime(2025, 4, 9, 10, 46, 29, 727900), datetime.datetime(2025, 4, 9, 10, 44, 50, 406400), datetime.datetime(2025, 4, 9, 10, 45, 7, 962600), datetime.datetime(2025, 4, 9, 10, 45, 27, 507400), datetime.datetime(2025, 4, 9, 10, 47, 8, 949100), datetime.datetime(2025, 4, 9, 10, 46, 30, 678500), datetime.datetime(2025, 4, 9, 10, 46, 42, 429700), datetime.datetime(2025, 4, 9, 10, 47, 1, 484200), datetime.datetime(2025, 4, 9, 10, 48, 39, 642700), datetime.datetime(2025, 4, 9, 10, 48, 21, 888800), datetime.datetime(2025, 4, 9, 10, 48, 32, 69100), datetime.datetime(2025, 4, 9, 10, 48, 34, 851800), datetime.datetime(2025, 4, 9, 10, 49, 20, 357000), datetime.datetime(2025, 4, 9, 10, 49, 25, 573500), datetime.datetime(2025, 4, 9, 10, 50, 54, 60800), datetime.datetime(2025, 4, 9, 10, 50, 21, 705800), datetime.datetime(2025, 4, 9, 10, 50, 45, 619900), datetime.datetime(2025, 4, 9, 10, 50, 54, 722700), datetime.datetime(2025, 4, 9, 10, 51, 7, 966500), datetime.datetime(2025, 4, 9, 10, 51, 13, 180700), datetime.datetime(2025, 4, 9, 10, 51, 52, 242700), datetime.datetime(2025, 4, 9, 10, 54, 10, 648500), datetime.datetime(2025, 4, 9, 10, 53, 8, 873800), datetime.datetime(2025, 4, 9, 10, 53, 20, 137700), datetime.datetime(2025, 4, 9, 10, 53, 44, 491500), datetime.datetime(2025, 4, 9, 10, 53, 47, 300000), datetime.datetime(2025, 4, 9, 10, 53, 56, 475900), datetime.datetime(2025, 4, 9, 10, 54, 4, 952300), datetime.datetime(2025, 4, 9, 10, 54, 33, 578100), datetime.datetime(2025, 4, 9, 10, 55, 59, 601200), datetime.datetime(2025, 4, 9, 10, 55, 23, 956800), datetime.datetime(2025, 4, 9, 10, 55, 34, 930500), datetime.datetime(2025, 4, 9, 10, 55, 54, 102300), datetime.datetime(2025, 4, 9, 10, 56, 1, 948900), datetime.datetime(2025, 4, 9, 10, 56, 22, 19100), datetime.datetime(2025, 4, 9, 10, 56, 35, 908400), datetime.datetime(2025, 4, 9, 11, 2, 4, 269500), datetime.datetime(2025, 4, 9, 10, 59, 34, 146300), datetime.datetime(2025, 4, 9, 10, 59, 42, 148300), datetime.datetime(2025, 4, 9, 10, 59, 58, 14800), datetime.datetime(2025, 4, 9, 11, 0, 48, 704100), datetime.datetime(2025, 4, 9, 11, 0, 40, 596800), datetime.datetime(2025, 4, 9, 11, 0, 47, 914000), datetime.datetime(2025, 4, 9, 11, 0, 53, 390200), datetime.datetime(2025, 4, 9, 11, 1, 5, 573000), datetime.datetime(2025, 4, 9, 11, 1, 46, 224600)]</t>
+        </is>
+      </c>
+      <c r="AE50" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>51</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="n">
+        <v>51</v>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>179</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>66e3e2de126b39b731a37762</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76H8ZE</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>45756.4326456593</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>51</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="n">
+        <v>51</v>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>180</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>62d06d1b651d6922f62fab9b</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>I6DXEO</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>29</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>It was a little confusing to understand chip and its strategy.</t>
+        </is>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>45756.47065885197</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA52" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 10, 23, 43, 540000), datetime.datetime(2025, 4, 9, 10, 23, 31, 388700), datetime.datetime(2025, 4, 9, 10, 24, 6, 309700), datetime.datetime(2025, 4, 9, 10, 24, 21, 683200), datetime.datetime(2025, 4, 9, 10, 26, 42, 668700), datetime.datetime(2025, 4, 9, 10, 26, 5, 625300), datetime.datetime(2025, 4, 9, 10, 26, 21, 465500), datetime.datetime(2025, 4, 9, 10, 26, 32, 965700), datetime.datetime(2025, 4, 9, 10, 27, 27, 240200), datetime.datetime(2025, 4, 9, 10, 27, 20, 135100), datetime.datetime(2025, 4, 9, 10, 28, 19, 978200), datetime.datetime(2025, 4, 9, 10, 28, 19, 940100), datetime.datetime(2025, 4, 9, 10, 28, 33, 613700), datetime.datetime(2025, 4, 9, 10, 28, 47, 885300), datetime.datetime(2025, 4, 9, 10, 29, 40, 52000), datetime.datetime(2025, 4, 9, 10, 29, 34, 67700), datetime.datetime(2025, 4, 9, 10, 30, 2, 778900), datetime.datetime(2025, 4, 9, 10, 30, 4, 183100), datetime.datetime(2025, 4, 9, 10, 30, 23, 685500), datetime.datetime(2025, 4, 9, 10, 30, 36, 223800), datetime.datetime(2025, 4, 9, 10, 31, 6, 511300), datetime.datetime(2025, 4, 9, 10, 31, 15, 761200), datetime.datetime(2025, 4, 9, 10, 31, 16, 480600), datetime.datetime(2025, 4, 9, 10, 31, 50, 310300), datetime.datetime(2025, 4, 9, 10, 31, 53, 913300), datetime.datetime(2025, 4, 9, 10, 31, 59, 114000), datetime.datetime(2025, 4, 9, 10, 32, 34, 668500), datetime.datetime(2025, 4, 9, 10, 32, 42, 78000), datetime.datetime(2025, 4, 9, 10, 33, 26, 4200), datetime.datetime(2025, 4, 9, 10, 33, 33, 620000), datetime.datetime(2025, 4, 9, 10, 33, 32, 495200), datetime.datetime(2025, 4, 9, 10, 34, 55, 395600), datetime.datetime(2025, 4, 9, 10, 34, 47, 529200), datetime.datetime(2025, 4, 9, 10, 34, 51, 824200), datetime.datetime(2025, 4, 9, 10, 35, 34, 779100), datetime.datetime(2025, 4, 9, 10, 35, 39, 285800), datetime.datetime(2025, 4, 9, 10, 36, 19, 665500), datetime.datetime(2025, 4, 9, 10, 36, 34, 739200), datetime.datetime(2025, 4, 9, 10, 36, 43, 577800), datetime.datetime(2025, 4, 9, 10, 37, 22, 433300), datetime.datetime(2025, 4, 9, 10, 37, 23, 287100), datetime.datetime(2025, 4, 9, 10, 38, 42, 692500), datetime.datetime(2025, 4, 9, 10, 38, 42, 692500), datetime.datetime(2025, 4, 9, 10, 40, 30, 523100), datetime.datetime(2025, 4, 9, 10, 40, 38, 817600), datetime.datetime(2025, 4, 9, 10, 41, 3, 763100), datetime.datetime(2025, 4, 9, 10, 41, 4, 231300), datetime.datetime(2025, 4, 9, 10, 41, 28, 628400), datetime.datetime(2025, 4, 9, 10, 43, 22, 754700), datetime.datetime(2025, 4, 9, 10, 44, 41, 897900), datetime.datetime(2025, 4, 9, 10, 43, 55, 821900), datetime.datetime(2025, 4, 9, 10, 44, 2, 604000), datetime.datetime(2025, 4, 9, 10, 44, 15, 74400), datetime.datetime(2025, 4, 9, 10, 44, 33, 591500), datetime.datetime(2025, 4, 9, 10, 45, 27, 905100), datetime.datetime(2025, 4, 9, 10, 45, 30, 254200), datetime.datetime(2025, 4, 9, 10, 45, 42, 754600), datetime.datetime(2025, 4, 9, 10, 45, 52, 634500), datetime.datetime(2025, 4, 9, 10, 46, 2, 141200), datetime.datetime(2025, 4, 9, 10, 47, 3, 803000), datetime.datetime(2025, 4, 9, 10, 46, 56, 961900), datetime.datetime(2025, 4, 9, 10, 47, 8, 777800), datetime.datetime(2025, 4, 9, 10, 47, 21, 859800), datetime.datetime(2025, 4, 9, 10, 47, 29, 243000), datetime.datetime(2025, 4, 9, 10, 48, 12, 714200), datetime.datetime(2025, 4, 9, 10, 48, 23, 470500), datetime.datetime(2025, 4, 9, 10, 48, 38, 662600), datetime.datetime(2025, 4, 9, 10, 48, 48, 579800), datetime.datetime(2025, 4, 9, 10, 49, 49, 219300), datetime.datetime(2025, 4, 9, 10, 49, 48, 495100), datetime.datetime(2025, 4, 9, 10, 51, 13, 819500), datetime.datetime(2025, 4, 9, 10, 51, 41, 458200), datetime.datetime(2025, 4, 9, 10, 51, 33, 1000), datetime.datetime(2025, 4, 9, 10, 51, 50, 535600), datetime.datetime(2025, 4, 9, 10, 51, 58, 847200), datetime.datetime(2025, 4, 9, 10, 52, 10, 206400), datetime.datetime(2025, 4, 9, 10, 52, 30, 701700), datetime.datetime(2025, 4, 9, 10, 53, 47, 310300), datetime.datetime(2025, 4, 9, 10, 53, 20, 746700), datetime.datetime(2025, 4, 9, 10, 53, 30, 350400), datetime.datetime(2025, 4, 9, 10, 53, 48, 502100), datetime.datetime(2025, 4, 9, 10, 53, 54, 768300), datetime.datetime(2025, 4, 9, 10, 54, 13, 579100), datetime.datetime(2025, 4, 9, 10, 54, 22, 984000), datetime.datetime(2025, 4, 9, 10, 54, 52, 326400), datetime.datetime(2025, 4, 9, 10, 58, 12, 13900), datetime.datetime(2025, 4, 9, 10, 56, 35, 896800), datetime.datetime(2025, 4, 9, 10, 56, 46, 679900), datetime.datetime(2025, 4, 9, 10, 56, 55, 435400), datetime.datetime(2025, 4, 9, 10, 57, 12, 964800), datetime.datetime(2025, 4, 9, 10, 57, 31, 726200), datetime.datetime(2025, 4, 9, 10, 59, 48, 97100), datetime.datetime(2025, 4, 9, 10, 58, 57, 958900), datetime.datetime(2025, 4, 9, 10, 59, 4, 254500), datetime.datetime(2025, 4, 9, 11, 0, 0, 279900), datetime.datetime(2025, 4, 9, 10, 59, 55, 379200), datetime.datetime(2025, 4, 9, 11, 0, 4, 81100), datetime.datetime(2025, 4, 9, 11, 0, 20, 590100), datetime.datetime(2025, 4, 9, 11, 1, 15, 578500), datetime.datetime(2025, 4, 9, 11, 0, 54, 604400), datetime.datetime(2025, 4, 9, 11, 1, 1, 881600), datetime.datetime(2025, 4, 9, 11, 1, 13, 359100), datetime.datetime(2025, 4, 9, 11, 1, 25, 642200), datetime.datetime(2025, 4, 9, 11, 2, 23, 262100)]</t>
+        </is>
+      </c>
+      <c r="AE52" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>51</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="n">
+        <v>51</v>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>181</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5f160514e2a4062d2a0ded58</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>9AZ8H1</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>45756.45125990139</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>52</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="n">
+        <v>52</v>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>182</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>66bcce7233ce3b6b5aaecd5e</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ALID9U</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>54</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I would have liked more time </t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>45756.50358172585</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA54" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 11, 17, 59, 795000), datetime.datetime(2025, 4, 9, 11, 17, 45, 594000), datetime.datetime(2025, 4, 9, 11, 18, 41, 268700), datetime.datetime(2025, 4, 9, 11, 19, 10, 797000), datetime.datetime(2025, 4, 9, 11, 19, 29, 37500), datetime.datetime(2025, 4, 9, 11, 20, 11, 408900), datetime.datetime(2025, 4, 9, 11, 21, 8, 471200), datetime.datetime(2025, 4, 9, 11, 21, 11, 503100), datetime.datetime(2025, 4, 9, 11, 21, 50, 191700), datetime.datetime(2025, 4, 9, 11, 22, 8, 472200), datetime.datetime(2025, 4, 9, 11, 22, 22, 570800), datetime.datetime(2025, 4, 9, 11, 23, 27, 359100), datetime.datetime(2025, 4, 9, 11, 24, 7, 975300), datetime.datetime(2025, 4, 9, 11, 24, 12, 139700), datetime.datetime(2025, 4, 9, 11, 24, 25, 591900), datetime.datetime(2025, 4, 9, 11, 25, 17, 775800), datetime.datetime(2025, 4, 9, 11, 25, 28, 750200), datetime.datetime(2025, 4, 9, 11, 25, 40, 902100), datetime.datetime(2025, 4, 9, 11, 26, 47, 708900), datetime.datetime(2025, 4, 9, 11, 26, 41, 756900), datetime.datetime(2025, 4, 9, 11, 26, 55, 234600), datetime.datetime(2025, 4, 9, 11, 28, 21, 199600), datetime.datetime(2025, 4, 9, 11, 28, 4, 377300), datetime.datetime(2025, 4, 9, 11, 28, 13, 283800), datetime.datetime(2025, 4, 9, 11, 30, 0, 486200), datetime.datetime(2025, 4, 9, 11, 29, 37, 923000), datetime.datetime(2025, 4, 9, 11, 29, 48, 836300), datetime.datetime(2025, 4, 9, 11, 30, 7, 946500), datetime.datetime(2025, 4, 9, 11, 30, 24, 735800), datetime.datetime(2025, 4, 9, 11, 30, 30, 150800), datetime.datetime(2025, 4, 9, 11, 30, 52, 272700), datetime.datetime(2025, 4, 9, 11, 30, 59, 195100), datetime.datetime(2025, 4, 9, 11, 31, 16, 607200), datetime.datetime(2025, 4, 9, 11, 31, 25, 789300), datetime.datetime(2025, 4, 9, 11, 31, 53, 492900), datetime.datetime(2025, 4, 9, 11, 34, 6, 379400), datetime.datetime(2025, 4, 9, 11, 33, 28, 978600), datetime.datetime(2025, 4, 9, 11, 33, 42, 696300), datetime.datetime(2025, 4, 9, 11, 34, 3, 510200), datetime.datetime(2025, 4, 9, 11, 34, 17, 706000), datetime.datetime(2025, 4, 9, 11, 34, 23, 977900), datetime.datetime(2025, 4, 9, 11, 34, 45, 203500), datetime.datetime(2025, 4, 9, 11, 35, 0, 548400), datetime.datetime(2025, 4, 9, 11, 35, 8, 781600), datetime.datetime(2025, 4, 9, 11, 35, 16, 272900), datetime.datetime(2025, 4, 9, 11, 35, 36, 97600), datetime.datetime(2025, 4, 9, 11, 35, 49, 363900), datetime.datetime(2025, 4, 9, 11, 38, 25, 646000), datetime.datetime(2025, 4, 9, 11, 37, 32, 540700), datetime.datetime(2025, 4, 9, 11, 37, 46, 563400), datetime.datetime(2025, 4, 9, 11, 37, 56, 932200), datetime.datetime(2025, 4, 9, 11, 38, 12, 40000), datetime.datetime(2025, 4, 9, 11, 40, 9, 82100), datetime.datetime(2025, 4, 9, 11, 39, 31, 140700), datetime.datetime(2025, 4, 9, 11, 39, 39, 855100), datetime.datetime(2025, 4, 9, 11, 40, 2, 343000), datetime.datetime(2025, 4, 9, 11, 40, 15, 61900), datetime.datetime(2025, 4, 9, 11, 40, 19, 41500), datetime.datetime(2025, 4, 9, 11, 41, 56, 998600), datetime.datetime(2025, 4, 9, 11, 41, 35, 872400), datetime.datetime(2025, 4, 9, 11, 41, 47, 322000), datetime.datetime(2025, 4, 9, 11, 41, 58, 459300), datetime.datetime(2025, 4, 9, 11, 42, 14, 747300), datetime.datetime(2025, 4, 9, 11, 44, 8, 162800), datetime.datetime(2025, 4, 9, 11, 44, 8, 162800), datetime.datetime(2025, 4, 9, 11, 48, 28, 24400), datetime.datetime(2025, 4, 9, 11, 47, 17, 546000), datetime.datetime(2025, 4, 9, 11, 47, 34, 64600), datetime.datetime(2025, 4, 9, 11, 47, 45, 737700), datetime.datetime(2025, 4, 9, 11, 49, 57, 877000), datetime.datetime(2025, 4, 9, 11, 49, 8, 430700), datetime.datetime(2025, 4, 9, 11, 49, 39, 792400), datetime.datetime(2025, 4, 9, 11, 51, 17, 466500), datetime.datetime(2025, 4, 9, 11, 50, 54, 713000), datetime.datetime(2025, 4, 9, 11, 51, 14, 180600), datetime.datetime(2025, 4, 9, 11, 51, 29, 286800), datetime.datetime(2025, 4, 9, 11, 51, 34, 437200), datetime.datetime(2025, 4, 9, 11, 52, 25, 22100), datetime.datetime(2025, 4, 9, 11, 52, 25, 851600), datetime.datetime(2025, 4, 9, 11, 52, 44, 671000), datetime.datetime(2025, 4, 9, 11, 52, 49, 468700), datetime.datetime(2025, 4, 9, 11, 53, 7, 281200), datetime.datetime(2025, 4, 9, 11, 53, 12, 948700), datetime.datetime(2025, 4, 9, 11, 54, 8, 215500), datetime.datetime(2025, 4, 9, 11, 54, 10, 791600), datetime.datetime(2025, 4, 9, 11, 54, 25, 871400), datetime.datetime(2025, 4, 9, 11, 54, 45, 250000), datetime.datetime(2025, 4, 9, 11, 54, 46, 809700), datetime.datetime(2025, 4, 9, 11, 56, 24, 411200), datetime.datetime(2025, 4, 9, 11, 56, 12, 626600), datetime.datetime(2025, 4, 9, 11, 56, 12, 832500), datetime.datetime(2025, 4, 9, 11, 57, 0, 872500), datetime.datetime(2025, 4, 9, 11, 57, 5, 41200), datetime.datetime(2025, 4, 9, 11, 57, 13, 639800), datetime.datetime(2025, 4, 9, 11, 57, 21, 164600), datetime.datetime(2025, 4, 9, 11, 57, 40, 111800), datetime.datetime(2025, 4, 9, 11, 57, 46, 738100), datetime.datetime(2025, 4, 9, 11, 59, 38, 128800), datetime.datetime(2025, 4, 9, 11, 59, 4, 959300), datetime.datetime(2025, 4, 9, 11, 59, 18, 67000), datetime.datetime(2025, 4, 9, 11, 59, 24, 729700), datetime.datetime(2025, 4, 9, 11, 59, 44, 168600), datetime.datetime(2025, 4, 9, 11, 59, 48, 518700), datetime.datetime(2025, 4, 9, 12, 2, 21, 139600), datetime.datetime(2025, 4, 9, 12, 1, 31, 95500), datetime.datetime(2025, 4, 9, 12, 2, 16, 945700), datetime.datetime(2025, 4, 9, 12, 2, 12, 975800), datetime.datetime(2025, 4, 9, 12, 2, 23, 927300), datetime.datetime(2025, 4, 9, 12, 2, 52, 941600), datetime.datetime(2025, 4, 9, 12, 3, 2, 805200), datetime.datetime(2025, 4, 9, 12, 4, 26, 355100)]</t>
+        </is>
+      </c>
+      <c r="AE54" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>52</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="n">
+        <v>52</v>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>183</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5d70dd0b28805f001aaf9a94</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>IOFHTY</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>45756.48805555292</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>184</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>59cb95053306be000195be2e</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>MGMW5S</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>32</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>2</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>45756.50279456765</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA56" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 11, 18, 30, 297200), datetime.datetime(2025, 4, 9, 11, 18, 15, 878900), datetime.datetime(2025, 4, 9, 11, 18, 34, 542700), datetime.datetime(2025, 4, 9, 11, 18, 49, 570600), datetime.datetime(2025, 4, 9, 11, 19, 0, 896700), datetime.datetime(2025, 4, 9, 11, 19, 32, 386000), datetime.datetime(2025, 4, 9, 11, 21, 16, 936200), datetime.datetime(2025, 4, 9, 11, 20, 39, 662000), datetime.datetime(2025, 4, 9, 11, 20, 51, 710900), datetime.datetime(2025, 4, 9, 11, 21, 13, 525900), datetime.datetime(2025, 4, 9, 11, 21, 23, 619300), datetime.datetime(2025, 4, 9, 11, 21, 49, 738300), datetime.datetime(2025, 4, 9, 11, 25, 17, 350200), datetime.datetime(2025, 4, 9, 11, 24, 17, 897200), datetime.datetime(2025, 4, 9, 11, 25, 16, 295500), datetime.datetime(2025, 4, 9, 11, 24, 54, 458100), datetime.datetime(2025, 4, 9, 11, 27, 3, 381000), datetime.datetime(2025, 4, 9, 11, 26, 29, 736000), datetime.datetime(2025, 4, 9, 11, 26, 51, 633200), datetime.datetime(2025, 4, 9, 11, 27, 0, 423500), datetime.datetime(2025, 4, 9, 11, 27, 54, 751600), datetime.datetime(2025, 4, 9, 11, 27, 45, 250300), datetime.datetime(2025, 4, 9, 11, 28, 9, 392300), datetime.datetime(2025, 4, 9, 11, 30, 5, 639100), datetime.datetime(2025, 4, 9, 11, 29, 30, 481700), datetime.datetime(2025, 4, 9, 11, 29, 39, 580600), datetime.datetime(2025, 4, 9, 11, 29, 52, 519700), datetime.datetime(2025, 4, 9, 11, 30, 13, 159600), datetime.datetime(2025, 4, 9, 11, 30, 26, 279900), datetime.datetime(2025, 4, 9, 11, 30, 51, 845500), datetime.datetime(2025, 4, 9, 11, 31, 6, 766000), datetime.datetime(2025, 4, 9, 11, 31, 13, 538800), datetime.datetime(2025, 4, 9, 11, 31, 32, 499500), datetime.datetime(2025, 4, 9, 11, 31, 33, 798300), datetime.datetime(2025, 4, 9, 11, 32, 1, 906400), datetime.datetime(2025, 4, 9, 11, 33, 51, 876300), datetime.datetime(2025, 4, 9, 11, 33, 7, 107100), datetime.datetime(2025, 4, 9, 11, 33, 18, 283500), datetime.datetime(2025, 4, 9, 11, 33, 27, 191600), datetime.datetime(2025, 4, 9, 11, 33, 49, 611200), datetime.datetime(2025, 4, 9, 11, 34, 1, 773800), datetime.datetime(2025, 4, 9, 11, 34, 19, 462700), datetime.datetime(2025, 4, 9, 11, 34, 41, 463400), datetime.datetime(2025, 4, 9, 11, 34, 55, 898100), datetime.datetime(2025, 4, 9, 11, 39, 12, 22000), datetime.datetime(2025, 4, 9, 11, 37, 25, 334800), datetime.datetime(2025, 4, 9, 11, 37, 35, 346200), datetime.datetime(2025, 4, 9, 11, 37, 45, 732200), datetime.datetime(2025, 4, 9, 11, 37, 57, 512800), datetime.datetime(2025, 4, 9, 11, 39, 58, 801100), datetime.datetime(2025, 4, 9, 11, 39, 33, 446600), datetime.datetime(2025, 4, 9, 11, 39, 47, 24200), datetime.datetime(2025, 4, 9, 11, 39, 56, 9900), datetime.datetime(2025, 4, 9, 11, 40, 6, 204900), datetime.datetime(2025, 4, 9, 11, 40, 11, 71400), datetime.datetime(2025, 4, 9, 11, 42, 3, 325800), datetime.datetime(2025, 4, 9, 11, 41, 32, 813600), datetime.datetime(2025, 4, 9, 11, 41, 46, 273600), datetime.datetime(2025, 4, 9, 11, 42, 5, 363200), datetime.datetime(2025, 4, 9, 11, 42, 13, 108700), datetime.datetime(2025, 4, 9, 11, 44, 14, 267500), datetime.datetime(2025, 4, 9, 11, 44, 14, 267500), datetime.datetime(2025, 4, 9, 11, 47, 49, 992500), datetime.datetime(2025, 4, 9, 11, 46, 40, 464500), datetime.datetime(2025, 4, 9, 11, 47, 26, 7800), datetime.datetime(2025, 4, 9, 11, 47, 26, 528900), datetime.datetime(2025, 4, 9, 11, 50, 19, 769500), datetime.datetime(2025, 4, 9, 11, 49, 12, 953200), datetime.datetime(2025, 4, 9, 11, 49, 32, 604500), datetime.datetime(2025, 4, 9, 11, 50, 58, 245300), datetime.datetime(2025, 4, 9, 11, 50, 24, 219400), datetime.datetime(2025, 4, 9, 11, 50, 47, 954300), datetime.datetime(2025, 4, 9, 11, 51, 2, 639100), datetime.datetime(2025, 4, 9, 11, 51, 16, 926500), datetime.datetime(2025, 4, 9, 11, 51, 29, 179500), datetime.datetime(2025, 4, 9, 11, 52, 24, 564700), datetime.datetime(2025, 4, 9, 11, 52, 10, 885200), datetime.datetime(2025, 4, 9, 11, 52, 31, 881800), datetime.datetime(2025, 4, 9, 11, 52, 40, 487800), datetime.datetime(2025, 4, 9, 11, 52, 57, 700800), datetime.datetime(2025, 4, 9, 11, 53, 11, 877100), datetime.datetime(2025, 4, 9, 11, 53, 48, 626900), datetime.datetime(2025, 4, 9, 11, 53, 58, 764000), datetime.datetime(2025, 4, 9, 11, 54, 8, 417200), datetime.datetime(2025, 4, 9, 11, 54, 23, 288500), datetime.datetime(2025, 4, 9, 11, 55, 12, 418600), datetime.datetime(2025, 4, 9, 11, 55, 16, 482800), datetime.datetime(2025, 4, 9, 11, 55, 45, 876800), datetime.datetime(2025, 4, 9, 11, 55, 47, 904200), datetime.datetime(2025, 4, 9, 11, 57, 16, 351400), datetime.datetime(2025, 4, 9, 11, 57, 0, 219200), datetime.datetime(2025, 4, 9, 11, 57, 15, 960200), datetime.datetime(2025, 4, 9, 11, 57, 29, 755500), datetime.datetime(2025, 4, 9, 11, 57, 59, 590300), datetime.datetime(2025, 4, 9, 11, 58, 36, 364900), datetime.datetime(2025, 4, 9, 11, 59, 5, 97800), datetime.datetime(2025, 4, 9, 11, 58, 54, 18900), datetime.datetime(2025, 4, 9, 11, 59, 21, 584700), datetime.datetime(2025, 4, 9, 12, 0, 3, 208200), datetime.datetime(2025, 4, 9, 12, 0, 11, 503500), datetime.datetime(2025, 4, 9, 12, 1, 58, 5700), datetime.datetime(2025, 4, 9, 12, 1, 29, 338000), datetime.datetime(2025, 4, 9, 12, 2, 17, 719800), datetime.datetime(2025, 4, 9, 12, 2, 9, 290500), datetime.datetime(2025, 4, 9, 12, 2, 18, 721100), datetime.datetime(2025, 4, 9, 12, 2, 39, 22800), datetime.datetime(2025, 4, 9, 12, 2, 45, 533900), datetime.datetime(2025, 4, 9, 12, 3, 37, 193400)]</t>
+        </is>
+      </c>
+      <c r="AE56" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>52</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="n">
+        <v>52</v>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>185</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>65639bc09216e3f40fcd1d4b</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>C8D51F</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>48</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>2</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Showing the points gained and lost during the game would've been helpful in figuring out what gains and loses points. I didn't feel frustrated, and it was a laid back game.</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>45756.50453526588</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA57" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 11, 18, 10, 119300), datetime.datetime(2025, 4, 9, 11, 17, 47, 831300), datetime.datetime(2025, 4, 9, 11, 18, 16, 570400), datetime.datetime(2025, 4, 9, 11, 18, 27, 838100), datetime.datetime(2025, 4, 9, 11, 18, 48, 194000), datetime.datetime(2025, 4, 9, 11, 21, 41, 278000), datetime.datetime(2025, 4, 9, 11, 20, 35, 548800), datetime.datetime(2025, 4, 9, 11, 20, 54, 93300), datetime.datetime(2025, 4, 9, 11, 21, 3, 126600), datetime.datetime(2025, 4, 9, 11, 21, 26, 213000), datetime.datetime(2025, 4, 9, 11, 25, 40, 941100), datetime.datetime(2025, 4, 9, 11, 24, 18, 912000), datetime.datetime(2025, 4, 9, 11, 25, 23, 477500), datetime.datetime(2025, 4, 9, 11, 25, 10, 217000), datetime.datetime(2025, 4, 9, 11, 26, 52, 905200), datetime.datetime(2025, 4, 9, 11, 26, 27, 774800), datetime.datetime(2025, 4, 9, 11, 26, 46, 927600), datetime.datetime(2025, 4, 9, 11, 28, 9, 794100), datetime.datetime(2025, 4, 9, 11, 27, 56, 842400), datetime.datetime(2025, 4, 9, 11, 28, 18, 871700), datetime.datetime(2025, 4, 9, 11, 30, 3, 527600), datetime.datetime(2025, 4, 9, 11, 29, 31, 574300), datetime.datetime(2025, 4, 9, 11, 29, 47, 264700), datetime.datetime(2025, 4, 9, 11, 30, 1, 686900), datetime.datetime(2025, 4, 9, 11, 30, 25, 598100), datetime.datetime(2025, 4, 9, 11, 30, 46, 449700), datetime.datetime(2025, 4, 9, 11, 31, 15, 400100), datetime.datetime(2025, 4, 9, 11, 31, 21, 961500), datetime.datetime(2025, 4, 9, 11, 31, 48, 405200), datetime.datetime(2025, 4, 9, 11, 32, 18, 774900), datetime.datetime(2025, 4, 9, 11, 34, 0, 974700), datetime.datetime(2025, 4, 9, 11, 33, 27, 599300), datetime.datetime(2025, 4, 9, 11, 33, 41, 77700), datetime.datetime(2025, 4, 9, 11, 33, 54, 575800), datetime.datetime(2025, 4, 9, 11, 34, 25, 949700), datetime.datetime(2025, 4, 9, 11, 34, 36, 489400), datetime.datetime(2025, 4, 9, 11, 34, 50, 289100), datetime.datetime(2025, 4, 9, 11, 35, 20, 762700), datetime.datetime(2025, 4, 9, 11, 36, 4, 526600), datetime.datetime(2025, 4, 9, 11, 36, 13, 228900), datetime.datetime(2025, 4, 9, 11, 36, 37, 744200), datetime.datetime(2025, 4, 9, 11, 37, 33, 986700), datetime.datetime(2025, 4, 9, 11, 37, 33, 269700), datetime.datetime(2025, 4, 9, 11, 37, 54, 106900), datetime.datetime(2025, 4, 9, 11, 38, 0, 401900), datetime.datetime(2025, 4, 9, 11, 38, 15, 84400), datetime.datetime(2025, 4, 9, 11, 38, 29, 469600), datetime.datetime(2025, 4, 9, 11, 39, 40, 369300), datetime.datetime(2025, 4, 9, 11, 39, 28, 80600), datetime.datetime(2025, 4, 9, 11, 39, 40, 787900), datetime.datetime(2025, 4, 9, 11, 39, 59, 855900), datetime.datetime(2025, 4, 9, 11, 40, 9, 182300), datetime.datetime(2025, 4, 9, 11, 40, 20, 835000), datetime.datetime(2025, 4, 9, 11, 40, 33, 247600), datetime.datetime(2025, 4, 9, 11, 42, 18, 265800), datetime.datetime(2025, 4, 9, 11, 41, 58, 993400), datetime.datetime(2025, 4, 9, 11, 42, 18, 381100), datetime.datetime(2025, 4, 9, 11, 42, 28, 838200), datetime.datetime(2025, 4, 9, 11, 42, 49, 712000), datetime.datetime(2025, 4, 9, 11, 44, 18, 923800), datetime.datetime(2025, 4, 9, 11, 44, 18, 923800), datetime.datetime(2025, 4, 9, 11, 47, 15, 749400), datetime.datetime(2025, 4, 9, 11, 46, 59, 65600), datetime.datetime(2025, 4, 9, 11, 47, 41, 988600), datetime.datetime(2025, 4, 9, 11, 48, 59, 154900), datetime.datetime(2025, 4, 9, 11, 49, 5, 286800), datetime.datetime(2025, 4, 9, 11, 49, 2, 75300), datetime.datetime(2025, 4, 9, 11, 49, 31, 127800), datetime.datetime(2025, 4, 9, 11, 49, 36, 577800), datetime.datetime(2025, 4, 9, 11, 50, 58, 433000), datetime.datetime(2025, 4, 9, 11, 50, 35, 139700), datetime.datetime(2025, 4, 9, 11, 51, 0, 173000), datetime.datetime(2025, 4, 9, 11, 51, 21, 600900), datetime.datetime(2025, 4, 9, 11, 52, 43, 46300), datetime.datetime(2025, 4, 9, 11, 52, 33, 152600), datetime.datetime(2025, 4, 9, 11, 53, 4, 470700), datetime.datetime(2025, 4, 9, 11, 53, 14, 112700), datetime.datetime(2025, 4, 9, 11, 54, 5, 445200), datetime.datetime(2025, 4, 9, 11, 54, 5, 880000), datetime.datetime(2025, 4, 9, 11, 54, 21, 810900), datetime.datetime(2025, 4, 9, 11, 54, 28, 558800), datetime.datetime(2025, 4, 9, 11, 54, 49, 711500), datetime.datetime(2025, 4, 9, 11, 54, 59, 458300), datetime.datetime(2025, 4, 9, 11, 56, 5, 984800), datetime.datetime(2025, 4, 9, 11, 56, 7, 410000), datetime.datetime(2025, 4, 9, 11, 57, 5, 124200), datetime.datetime(2025, 4, 9, 11, 56, 45, 920000), datetime.datetime(2025, 4, 9, 11, 57, 27, 489300), datetime.datetime(2025, 4, 9, 11, 57, 28, 877700), datetime.datetime(2025, 4, 9, 12, 1, 18, 228600), datetime.datetime(2025, 4, 9, 12, 0, 9, 923200), datetime.datetime(2025, 4, 9, 12, 0, 38, 180900), datetime.datetime(2025, 4, 9, 12, 0, 41, 619100), datetime.datetime(2025, 4, 9, 12, 1, 27, 933600), datetime.datetime(2025, 4, 9, 12, 1, 33, 244900), datetime.datetime(2025, 4, 9, 12, 2, 10, 460800), datetime.datetime(2025, 4, 9, 12, 2, 12, 465900), datetime.datetime(2025, 4, 9, 12, 2, 27, 838200), datetime.datetime(2025, 4, 9, 12, 2, 35, 410800), datetime.datetime(2025, 4, 9, 12, 2, 51, 969800), datetime.datetime(2025, 4, 9, 12, 4, 44, 687500)]</t>
+        </is>
+      </c>
+      <c r="AE57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>52</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="n">
+        <v>52</v>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>186</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>67db400e73eb8cf711f262a8</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>P91FDP</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>21</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>4</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>That was interesting and confusing! I had fun. I wish Chip was more clear about what we were doing.</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>45756.55077518692</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA58" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 12, 20, 26, 27000), datetime.datetime(2025, 4, 9, 12, 20, 6, 700400), datetime.datetime(2025, 4, 9, 12, 20, 47, 830200), datetime.datetime(2025, 4, 9, 12, 21, 6, 354800), datetime.datetime(2025, 4, 9, 12, 21, 33, 121500), datetime.datetime(2025, 4, 9, 12, 27, 48, 371400), datetime.datetime(2025, 4, 9, 12, 25, 17, 590300), datetime.datetime(2025, 4, 9, 12, 25, 32, 874400), datetime.datetime(2025, 4, 9, 12, 25, 39, 816200), datetime.datetime(2025, 4, 9, 12, 25, 51, 611700), datetime.datetime(2025, 4, 9, 12, 26, 39, 947600), datetime.datetime(2025, 4, 9, 12, 26, 29, 647000), datetime.datetime(2025, 4, 9, 12, 27, 4, 76200), datetime.datetime(2025, 4, 9, 12, 27, 6, 641600), datetime.datetime(2025, 4, 9, 12, 27, 31, 365400), datetime.datetime(2025, 4, 9, 12, 27, 56, 443600), datetime.datetime(2025, 4, 9, 12, 29, 1, 821900), datetime.datetime(2025, 4, 9, 12, 28, 46, 143700), datetime.datetime(2025, 4, 9, 12, 29, 4, 690900), datetime.datetime(2025, 4, 9, 12, 29, 15, 833700), datetime.datetime(2025, 4, 9, 12, 30, 0, 310500), datetime.datetime(2025, 4, 9, 12, 30, 0, 593200), datetime.datetime(2025, 4, 9, 12, 32, 36, 346600), datetime.datetime(2025, 4, 9, 12, 31, 51, 936800), datetime.datetime(2025, 4, 9, 12, 32, 52, 120200), datetime.datetime(2025, 4, 9, 12, 32, 37, 864800), datetime.datetime(2025, 4, 9, 12, 32, 59, 436200), datetime.datetime(2025, 4, 9, 12, 33, 18, 271600), datetime.datetime(2025, 4, 9, 12, 33, 32, 124300), datetime.datetime(2025, 4, 9, 12, 33, 42, 456900), datetime.datetime(2025, 4, 9, 12, 34, 6, 273600), datetime.datetime(2025, 4, 9, 12, 35, 34, 364600), datetime.datetime(2025, 4, 9, 12, 35, 5, 913700), datetime.datetime(2025, 4, 9, 12, 35, 14, 46700), datetime.datetime(2025, 4, 9, 12, 35, 44, 435300), datetime.datetime(2025, 4, 9, 12, 35, 45, 602900), datetime.datetime(2025, 4, 9, 12, 36, 17, 319800), datetime.datetime(2025, 4, 9, 12, 36, 29, 98900), datetime.datetime(2025, 4, 9, 12, 37, 26, 890900), datetime.datetime(2025, 4, 9, 12, 37, 12, 155800), datetime.datetime(2025, 4, 9, 12, 37, 18, 230600), datetime.datetime(2025, 4, 9, 12, 37, 37, 140900), datetime.datetime(2025, 4, 9, 12, 37, 49, 981600), datetime.datetime(2025, 4, 9, 12, 38, 10, 317400), datetime.datetime(2025, 4, 9, 12, 38, 25, 866400), datetime.datetime(2025, 4, 9, 12, 39, 23, 404900), datetime.datetime(2025, 4, 9, 12, 39, 4, 132600), datetime.datetime(2025, 4, 9, 12, 39, 12, 790400), datetime.datetime(2025, 4, 9, 12, 39, 34, 444100), datetime.datetime(2025, 4, 9, 12, 39, 48, 271700), datetime.datetime(2025, 4, 9, 12, 40, 27, 413700), datetime.datetime(2025, 4, 9, 12, 40, 30, 228500), datetime.datetime(2025, 4, 9, 12, 41, 33, 279800), datetime.datetime(2025, 4, 9, 12, 41, 31, 632300), datetime.datetime(2025, 4, 9, 12, 41, 43, 693600), datetime.datetime(2025, 4, 9, 12, 41, 54, 809200), datetime.datetime(2025, 4, 9, 12, 42, 17, 583400), datetime.datetime(2025, 4, 9, 12, 44, 34, 26500), datetime.datetime(2025, 4, 9, 12, 44, 34, 26500), datetime.datetime(2025, 4, 9, 12, 47, 46, 283000), datetime.datetime(2025, 4, 9, 12, 47, 18, 644200), datetime.datetime(2025, 4, 9, 12, 47, 39, 69100), datetime.datetime(2025, 4, 9, 12, 47, 44, 58200), datetime.datetime(2025, 4, 9, 12, 48, 28, 429400), datetime.datetime(2025, 4, 9, 12, 48, 25, 218900), datetime.datetime(2025, 4, 9, 12, 49, 4, 647800), datetime.datetime(2025, 4, 9, 12, 49, 5, 333000), datetime.datetime(2025, 4, 9, 12, 49, 21, 355700), datetime.datetime(2025, 4, 9, 12, 49, 30, 433800), datetime.datetime(2025, 4, 9, 12, 50, 18, 660100), datetime.datetime(2025, 4, 9, 12, 50, 11, 324900), datetime.datetime(2025, 4, 9, 12, 50, 58, 572200), datetime.datetime(2025, 4, 9, 12, 51, 3, 955300), datetime.datetime(2025, 4, 9, 12, 51, 58, 366000), datetime.datetime(2025, 4, 9, 12, 52, 6, 692200), datetime.datetime(2025, 4, 9, 12, 52, 8, 188600), datetime.datetime(2025, 4, 9, 12, 53, 12, 810300), datetime.datetime(2025, 4, 9, 12, 53, 0, 966500), datetime.datetime(2025, 4, 9, 12, 53, 45, 758300), datetime.datetime(2025, 4, 9, 12, 53, 41, 13400), datetime.datetime(2025, 4, 9, 12, 54, 4, 796300), datetime.datetime(2025, 4, 9, 12, 54, 11, 861300), datetime.datetime(2025, 4, 9, 12, 54, 32, 107300), datetime.datetime(2025, 4, 9, 12, 54, 36, 449600), datetime.datetime(2025, 4, 9, 12, 56, 17, 187000), datetime.datetime(2025, 4, 9, 12, 56, 5, 713300), datetime.datetime(2025, 4, 9, 12, 57, 54, 999100), datetime.datetime(2025, 4, 9, 12, 59, 37, 448000), datetime.datetime(2025, 4, 9, 12, 59, 38, 967300), datetime.datetime(2025, 4, 9, 13, 0, 23, 831800), datetime.datetime(2025, 4, 9, 13, 1, 29, 759800), datetime.datetime(2025, 4, 9, 13, 1, 19, 656700), datetime.datetime(2025, 4, 9, 13, 2, 3, 716900), datetime.datetime(2025, 4, 9, 13, 2, 5, 567500), datetime.datetime(2025, 4, 9, 13, 3, 1, 411000)]</t>
+        </is>
+      </c>
+      <c r="AE58" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="n">
+        <v>54</v>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>187</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>66ec8f7ce843d25227820f97</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>WGAPC8</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>45756.51206342669</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="AA59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 11, 58, 11, 960400), datetime.datetime(2025, 4, 9, 11, 57, 38, 490800), datetime.datetime(2025, 4, 9, 11, 58, 16, 29300), datetime.datetime(2025, 4, 9, 12, 2, 41, 291700), datetime.datetime(2025, 4, 9, 12, 0, 44, 930500), datetime.datetime(2025, 4, 9, 12, 1, 33, 78600), datetime.datetime(2025, 4, 9, 12, 1, 36, 326000), datetime.datetime(2025, 4, 9, 12, 3, 2, 625000), datetime.datetime(2025, 4, 9, 12, 3, 6, 465300), datetime.datetime(2025, 4, 9, 12, 3, 39, 139100), datetime.datetime(2025, 4, 9, 12, 3, 52, 514400), datetime.datetime(2025, 4, 9, 12, 4, 6, 281200), datetime.datetime(2025, 4, 9, 12, 5, 31, 779800), datetime.datetime(2025, 4, 9, 12, 5, 7, 699000), datetime.datetime(2025, 4, 9, 12, 5, 41, 160300), datetime.datetime(2025, 4, 9, 12, 5, 48, 525500), datetime.datetime(2025, 4, 9, 12, 6, 9, 827900), datetime.datetime(2025, 4, 9, 12, 6, 18, 879400), datetime.datetime(2025, 4, 9, 12, 7, 56, 679400), datetime.datetime(2025, 4, 9, 12, 7, 27, 746500), datetime.datetime(2025, 4, 9, 12, 7, 43, 74500), datetime.datetime(2025, 4, 9, 12, 8, 8, 958100), datetime.datetime(2025, 4, 9, 12, 11, 14, 59000), datetime.datetime(2025, 4, 9, 12, 10, 2, 330300), datetime.datetime(2025, 4, 9, 12, 11, 1, 60000), datetime.datetime(2025, 4, 9, 12, 10, 40, 562000), datetime.datetime(2025, 4, 9, 12, 10, 58, 13000), datetime.datetime(2025, 4, 9, 12, 11, 5, 607500), datetime.datetime(2025, 4, 9, 12, 13, 36, 874300), datetime.datetime(2025, 4, 9, 12, 12, 37, 562000), datetime.datetime(2025, 4, 9, 12, 13, 1, 948000), datetime.datetime(2025, 4, 9, 12, 13, 15, 511300)]</t>
+        </is>
+      </c>
+      <c r="AE59" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>53</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="n">
+        <v>53</v>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>188</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>6757069f8e2b810b4fabd66b</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>TIZ4CF</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>46</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>2</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>45756.52794104454</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA60" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 11, 59, 19, 459700), datetime.datetime(2025, 4, 9, 11, 58, 58, 834300), datetime.datetime(2025, 4, 9, 11, 59, 54, 759800), datetime.datetime(2025, 4, 9, 11, 59, 52, 139700), datetime.datetime(2025, 4, 9, 12, 0, 49, 357200), datetime.datetime(2025, 4, 9, 12, 1, 1, 974200), datetime.datetime(2025, 4, 9, 12, 1, 37, 84900), datetime.datetime(2025, 4, 9, 12, 3, 16, 352700), datetime.datetime(2025, 4, 9, 12, 2, 49, 973600), datetime.datetime(2025, 4, 9, 12, 3, 44, 210400), datetime.datetime(2025, 4, 9, 12, 3, 41, 59600), datetime.datetime(2025, 4, 9, 12, 4, 7, 566100), datetime.datetime(2025, 4, 9, 12, 4, 21, 705200), datetime.datetime(2025, 4, 9, 12, 5, 53, 999900), datetime.datetime(2025, 4, 9, 12, 5, 29, 537600), datetime.datetime(2025, 4, 9, 12, 6, 2, 213700), datetime.datetime(2025, 4, 9, 12, 6, 24, 915900), datetime.datetime(2025, 4, 9, 12, 6, 30, 677300), datetime.datetime(2025, 4, 9, 12, 8, 11, 924300), datetime.datetime(2025, 4, 9, 12, 7, 55, 79600), datetime.datetime(2025, 4, 9, 12, 8, 15, 946600), datetime.datetime(2025, 4, 9, 12, 8, 16, 615500), datetime.datetime(2025, 4, 9, 12, 8, 54, 563200), datetime.datetime(2025, 4, 9, 12, 8, 59, 310500), datetime.datetime(2025, 4, 9, 12, 10, 21, 344000), datetime.datetime(2025, 4, 9, 12, 10, 0, 999400), datetime.datetime(2025, 4, 9, 12, 10, 34, 718700), datetime.datetime(2025, 4, 9, 12, 10, 45, 243800), datetime.datetime(2025, 4, 9, 12, 14, 24, 349500), datetime.datetime(2025, 4, 9, 12, 12, 59, 733700), datetime.datetime(2025, 4, 9, 12, 13, 39, 94300), datetime.datetime(2025, 4, 9, 12, 13, 29, 461900), datetime.datetime(2025, 4, 9, 12, 13, 50, 887100), datetime.datetime(2025, 4, 9, 12, 17, 23, 852700), datetime.datetime(2025, 4, 9, 12, 15, 51, 481100), datetime.datetime(2025, 4, 9, 12, 16, 14, 620800), datetime.datetime(2025, 4, 9, 12, 16, 17, 937100), datetime.datetime(2025, 4, 9, 12, 16, 50, 750800), datetime.datetime(2025, 4, 9, 12, 16, 52, 286100), datetime.datetime(2025, 4, 9, 12, 22, 15, 911000), datetime.datetime(2025, 4, 9, 12, 20, 21, 677200), datetime.datetime(2025, 4, 9, 12, 21, 28, 327900), datetime.datetime(2025, 4, 9, 12, 21, 12, 274500), datetime.datetime(2025, 4, 9, 12, 21, 19, 151000), datetime.datetime(2025, 4, 9, 12, 22, 4, 494400), datetime.datetime(2025, 4, 9, 12, 22, 6, 872000), datetime.datetime(2025, 4, 9, 12, 23, 40, 277400), datetime.datetime(2025, 4, 9, 12, 23, 40, 277400), datetime.datetime(2025, 4, 9, 12, 25, 40, 178900), datetime.datetime(2025, 4, 9, 12, 25, 37, 58000), datetime.datetime(2025, 4, 9, 12, 25, 57, 747400), datetime.datetime(2025, 4, 9, 12, 25, 53, 745200), datetime.datetime(2025, 4, 9, 12, 26, 20, 410600), datetime.datetime(2025, 4, 9, 12, 26, 32, 511400), datetime.datetime(2025, 4, 9, 12, 27, 0, 370700), datetime.datetime(2025, 4, 9, 12, 27, 7, 881700), datetime.datetime(2025, 4, 9, 12, 27, 33, 693000), datetime.datetime(2025, 4, 9, 12, 27, 29, 346800), datetime.datetime(2025, 4, 9, 12, 28, 1, 205800), datetime.datetime(2025, 4, 9, 12, 28, 46, 883000), datetime.datetime(2025, 4, 9, 12, 28, 47, 143100), datetime.datetime(2025, 4, 9, 12, 28, 57, 694300), datetime.datetime(2025, 4, 9, 12, 29, 25, 319600), datetime.datetime(2025, 4, 9, 12, 30, 24, 558200), datetime.datetime(2025, 4, 9, 12, 30, 19, 617400), datetime.datetime(2025, 4, 9, 12, 31, 16, 173800), datetime.datetime(2025, 4, 9, 12, 31, 20, 285800), datetime.datetime(2025, 4, 9, 12, 31, 21, 142200), datetime.datetime(2025, 4, 9, 12, 32, 12, 738200), datetime.datetime(2025, 4, 9, 12, 32, 14, 679200), datetime.datetime(2025, 4, 9, 12, 32, 45, 219600), datetime.datetime(2025, 4, 9, 12, 33, 36, 389600), datetime.datetime(2025, 4, 9, 12, 33, 23, 922200), datetime.datetime(2025, 4, 9, 12, 33, 37, 106300), datetime.datetime(2025, 4, 9, 12, 34, 8, 290600), datetime.datetime(2025, 4, 9, 12, 34, 6, 894100), datetime.datetime(2025, 4, 9, 12, 34, 18, 957700), datetime.datetime(2025, 4, 9, 12, 35, 1, 2000), datetime.datetime(2025, 4, 9, 12, 36, 4, 309700), datetime.datetime(2025, 4, 9, 12, 35, 46, 52900), datetime.datetime(2025, 4, 9, 12, 35, 58, 468100), datetime.datetime(2025, 4, 9, 12, 36, 5, 109900), datetime.datetime(2025, 4, 9, 12, 36, 30, 528400), datetime.datetime(2025, 4, 9, 12, 36, 57, 598100), datetime.datetime(2025, 4, 9, 12, 37, 5, 265400), datetime.datetime(2025, 4, 9, 12, 37, 49, 302200), datetime.datetime(2025, 4, 9, 12, 37, 33, 360300), datetime.datetime(2025, 4, 9, 12, 37, 54, 284800), datetime.datetime(2025, 4, 9, 12, 38, 0, 27300), datetime.datetime(2025, 4, 9, 12, 38, 16, 64600), datetime.datetime(2025, 4, 9, 12, 39, 49, 680000)]</t>
+        </is>
+      </c>
+      <c r="AE60" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>53</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="n">
+        <v>53</v>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>189</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>57308d1530a5560010ecbc1a</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>PRKOW9</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>45756.51312384167</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>diagnostic test</t>
+        </is>
+      </c>
+      <c r="AA61" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 11, 57, 40, 862200), datetime.datetime(2025, 4, 9, 11, 57, 25, 284000), datetime.datetime(2025, 4, 9, 11, 58, 56, 687200), datetime.datetime(2025, 4, 9, 11, 58, 48, 417800), datetime.datetime(2025, 4, 9, 12, 1, 50, 725900), datetime.datetime(2025, 4, 9, 12, 0, 48, 897800), datetime.datetime(2025, 4, 9, 12, 1, 49, 747000), datetime.datetime(2025, 4, 9, 12, 1, 43, 906100), datetime.datetime(2025, 4, 9, 12, 2, 44, 223300), datetime.datetime(2025, 4, 9, 12, 2, 33, 289500), datetime.datetime(2025, 4, 9, 12, 3, 58, 300100), datetime.datetime(2025, 4, 9, 12, 4, 36, 263200), datetime.datetime(2025, 4, 9, 12, 5, 14, 415400), datetime.datetime(2025, 4, 9, 12, 5, 5, 559200), datetime.datetime(2025, 4, 9, 12, 6, 1, 870300), datetime.datetime(2025, 4, 9, 12, 6, 3, 47700), datetime.datetime(2025, 4, 9, 12, 6, 53, 980400), datetime.datetime(2025, 4, 9, 12, 7, 29, 963700), datetime.datetime(2025, 4, 9, 12, 7, 25, 224600), datetime.datetime(2025, 4, 9, 12, 8, 28, 18600), datetime.datetime(2025, 4, 9, 12, 8, 22, 441600), datetime.datetime(2025, 4, 9, 12, 9, 3, 147000), datetime.datetime(2025, 4, 9, 12, 9, 15, 873500), datetime.datetime(2025, 4, 9, 12, 10, 4, 965100), datetime.datetime(2025, 4, 9, 12, 10, 13, 737100), datetime.datetime(2025, 4, 9, 12, 10, 51, 921300), datetime.datetime(2025, 4, 9, 12, 11, 2, 82500), datetime.datetime(2025, 4, 9, 12, 12, 10, 751000), datetime.datetime(2025, 4, 9, 12, 12, 5, 114400), datetime.datetime(2025, 4, 9, 12, 13, 5, 764800), datetime.datetime(2025, 4, 9, 12, 12, 54, 320700), datetime.datetime(2025, 4, 9, 12, 13, 48, 395600), datetime.datetime(2025, 4, 9, 12, 13, 45, 251100), datetime.datetime(2025, 4, 9, 12, 15, 24, 295600), datetime.datetime(2025, 4, 9, 12, 16, 2, 521800), datetime.datetime(2025, 4, 9, 12, 15, 39, 940700), datetime.datetime(2025, 4, 9, 12, 16, 18, 470500), datetime.datetime(2025, 4, 9, 12, 16, 30, 111300)]</t>
+        </is>
+      </c>
+      <c r="AE61" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>53</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="n">
+        <v>53</v>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>190</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5b6b2c3156558d0001678ffc</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>KIZBSZ</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>45756.50976943546</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="n">
+        <v>54</v>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>191</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>667d404c940badc47d80d670</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>UPP3TD</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>post practice</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>45756.51665771312</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="AA63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>['mouse']</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 12, 19, 39, 129000)]</t>
+        </is>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="n">
+        <v>54</v>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>192</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5a7226d9f660ae0001a9a547</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>LRVBUO</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>26</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>45756.54232305499</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA64" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 12, 22, 40, 873400), datetime.datetime(2025, 4, 9, 12, 22, 43, 286500), datetime.datetime(2025, 4, 9, 12, 22, 45, 574200), datetime.datetime(2025, 4, 9, 12, 23, 31, 368600), datetime.datetime(2025, 4, 9, 12, 23, 26, 905800), datetime.datetime(2025, 4, 9, 12, 24, 0, 904300), datetime.datetime(2025, 4, 9, 12, 25, 59, 137400), datetime.datetime(2025, 4, 9, 12, 25, 31, 773600), datetime.datetime(2025, 4, 9, 12, 25, 40, 407400), datetime.datetime(2025, 4, 9, 12, 25, 55, 519000), datetime.datetime(2025, 4, 9, 12, 26, 43, 770200), datetime.datetime(2025, 4, 9, 12, 26, 51, 270500), datetime.datetime(2025, 4, 9, 12, 26, 49, 948500), datetime.datetime(2025, 4, 9, 12, 26, 58, 51700), datetime.datetime(2025, 4, 9, 12, 27, 9, 900600), datetime.datetime(2025, 4, 9, 12, 27, 18, 368800), datetime.datetime(2025, 4, 9, 12, 29, 23, 220800), datetime.datetime(2025, 4, 9, 12, 28, 42, 49300), datetime.datetime(2025, 4, 9, 12, 28, 47, 585500), datetime.datetime(2025, 4, 9, 12, 28, 54, 35600), datetime.datetime(2025, 4, 9, 12, 31, 41, 118500), datetime.datetime(2025, 4, 9, 12, 30, 33, 334200), datetime.datetime(2025, 4, 9, 12, 33, 56, 770700), datetime.datetime(2025, 4, 9, 12, 32, 34, 400), datetime.datetime(2025, 4, 9, 12, 33, 26, 632400), datetime.datetime(2025, 4, 9, 12, 33, 14, 516000), datetime.datetime(2025, 4, 9, 12, 33, 39, 137800), datetime.datetime(2025, 4, 9, 12, 33, 45, 515700), datetime.datetime(2025, 4, 9, 12, 33, 51, 834700), datetime.datetime(2025, 4, 9, 12, 34, 29, 866900), datetime.datetime(2025, 4, 9, 12, 35, 21, 198000), datetime.datetime(2025, 4, 9, 12, 35, 2, 303600), datetime.datetime(2025, 4, 9, 12, 35, 7, 569200), datetime.datetime(2025, 4, 9, 12, 35, 22, 666700), datetime.datetime(2025, 4, 9, 12, 35, 22, 134100), datetime.datetime(2025, 4, 9, 12, 35, 40, 416700), datetime.datetime(2025, 4, 9, 12, 35, 56, 468100), datetime.datetime(2025, 4, 9, 12, 37, 59, 618700), datetime.datetime(2025, 4, 9, 12, 37, 11, 5300), datetime.datetime(2025, 4, 9, 12, 37, 12, 594200), datetime.datetime(2025, 4, 9, 12, 37, 23, 829000), datetime.datetime(2025, 4, 9, 12, 37, 35, 182900), datetime.datetime(2025, 4, 9, 12, 37, 44, 800800), datetime.datetime(2025, 4, 9, 12, 40, 13, 972100), datetime.datetime(2025, 4, 9, 12, 39, 6, 985500), datetime.datetime(2025, 4, 9, 12, 39, 9, 686600), datetime.datetime(2025, 4, 9, 12, 39, 21, 217600), datetime.datetime(2025, 4, 9, 12, 39, 30, 334200), datetime.datetime(2025, 4, 9, 12, 39, 39, 151700), datetime.datetime(2025, 4, 9, 12, 42, 7, 709700), datetime.datetime(2025, 4, 9, 12, 41, 16, 35000), datetime.datetime(2025, 4, 9, 12, 41, 15, 470200), datetime.datetime(2025, 4, 9, 12, 41, 28, 20600), datetime.datetime(2025, 4, 9, 12, 41, 39, 755500), datetime.datetime(2025, 4, 9, 12, 42, 54, 519100), datetime.datetime(2025, 4, 9, 12, 42, 54, 519100), datetime.datetime(2025, 4, 9, 12, 49, 42, 696300), datetime.datetime(2025, 4, 9, 12, 48, 9, 638900), datetime.datetime(2025, 4, 9, 12, 47, 46, 855000), datetime.datetime(2025, 4, 9, 12, 48, 37, 737900), datetime.datetime(2025, 4, 9, 12, 48, 22, 954800), datetime.datetime(2025, 4, 9, 12, 49, 6, 673300), datetime.datetime(2025, 4, 9, 12, 49, 2, 971600), datetime.datetime(2025, 4, 9, 12, 49, 12, 123000), datetime.datetime(2025, 4, 9, 12, 49, 20, 654000), datetime.datetime(2025, 4, 9, 12, 50, 17, 156300), datetime.datetime(2025, 4, 9, 12, 49, 58, 973000), datetime.datetime(2025, 4, 9, 12, 50, 11, 238400), datetime.datetime(2025, 4, 9, 12, 50, 23, 18100), datetime.datetime(2025, 4, 9, 12, 52, 18, 973700), datetime.datetime(2025, 4, 9, 12, 51, 41, 771000), datetime.datetime(2025, 4, 9, 12, 53, 39, 390200), datetime.datetime(2025, 4, 9, 12, 52, 56, 85600), datetime.datetime(2025, 4, 9, 12, 53, 49, 719600), datetime.datetime(2025, 4, 9, 12, 53, 37, 853500), datetime.datetime(2025, 4, 9, 12, 53, 48, 274700), datetime.datetime(2025, 4, 9, 12, 53, 56, 988600), datetime.datetime(2025, 4, 9, 12, 54, 2, 573900), datetime.datetime(2025, 4, 9, 12, 56, 3, 773500), datetime.datetime(2025, 4, 9, 12, 55, 16, 854600), datetime.datetime(2025, 4, 9, 12, 55, 26, 873300), datetime.datetime(2025, 4, 9, 12, 55, 42, 921000), datetime.datetime(2025, 4, 9, 12, 55, 51, 885900), datetime.datetime(2025, 4, 9, 13, 2, 56, 845600), datetime.datetime(2025, 4, 9, 12, 59, 33, 637100), datetime.datetime(2025, 4, 9, 12, 59, 42, 905600), datetime.datetime(2025, 4, 9, 12, 59, 52, 19300), datetime.datetime(2025, 4, 9, 13, 0, 0, 685500), datetime.datetime(2025, 4, 9, 13, 0, 40, 70600)]</t>
+        </is>
+      </c>
+      <c r="AE64" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>54</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="n">
+        <v>54</v>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>193</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>64135e3d9cd5e3f16290d29c</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>KV9033</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>26</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>4</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>I wish Chip could have not confuse me with sometimes using the purple squares and then other times not using the purple square at all. No, other feedback.</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>45756.57473741535</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA65" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'r', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 12, 51, 10, 636400), datetime.datetime(2025, 4, 9, 12, 51, 33, 930700), datetime.datetime(2025, 4, 9, 12, 52, 11, 644700), datetime.datetime(2025, 4, 9, 12, 52, 55, 507200), datetime.datetime(2025, 4, 9, 12, 59, 51, 52200), datetime.datetime(2025, 4, 9, 12, 56, 43, 580200), datetime.datetime(2025, 4, 9, 12, 57, 6, 241300), datetime.datetime(2025, 4, 9, 12, 57, 52, 600900), datetime.datetime(2025, 4, 9, 12, 58, 6, 225000), datetime.datetime(2025, 4, 9, 13, 0, 8, 222700), datetime.datetime(2025, 4, 9, 12, 59, 33, 231300), datetime.datetime(2025, 4, 9, 13, 0, 1, 974600), datetime.datetime(2025, 4, 9, 13, 0, 31, 747500), datetime.datetime(2025, 4, 9, 13, 3, 15, 412000), datetime.datetime(2025, 4, 9, 13, 2, 27, 760100), datetime.datetime(2025, 4, 9, 13, 2, 46, 32000), datetime.datetime(2025, 4, 9, 13, 3, 16, 430700), datetime.datetime(2025, 4, 9, 13, 3, 57, 26700), datetime.datetime(2025, 4, 9, 13, 5, 12, 264200), datetime.datetime(2025, 4, 9, 13, 6, 1, 487200), datetime.datetime(2025, 4, 9, 13, 6, 37, 406500), datetime.datetime(2025, 4, 9, 13, 6, 49, 216500), datetime.datetime(2025, 4, 9, 13, 7, 49, 792100), datetime.datetime(2025, 4, 9, 13, 8, 0, 302900), datetime.datetime(2025, 4, 9, 13, 9, 48, 997900), datetime.datetime(2025, 4, 9, 13, 9, 20, 147700), datetime.datetime(2025, 4, 9, 13, 10, 19, 478500), datetime.datetime(2025, 4, 9, 13, 10, 22, 760500), datetime.datetime(2025, 4, 9, 13, 10, 35, 257000), datetime.datetime(2025, 4, 9, 13, 11, 4, 515700), datetime.datetime(2025, 4, 9, 13, 11, 15, 992900), datetime.datetime(2025, 4, 9, 13, 12, 59, 751500), datetime.datetime(2025, 4, 9, 13, 12, 59, 751500), datetime.datetime(2025, 4, 9, 13, 18, 53, 875000), datetime.datetime(2025, 4, 9, 13, 18, 38, 190500), datetime.datetime(2025, 4, 9, 13, 18, 56, 242300), datetime.datetime(2025, 4, 9, 13, 19, 9, 110900), datetime.datetime(2025, 4, 9, 13, 19, 22, 824600), datetime.datetime(2025, 4, 9, 13, 20, 51, 108300), datetime.datetime(2025, 4, 9, 13, 20, 25, 56700), datetime.datetime(2025, 4, 9, 13, 20, 35, 534100), datetime.datetime(2025, 4, 9, 13, 20, 54, 32000), datetime.datetime(2025, 4, 9, 13, 24, 21, 902000), datetime.datetime(2025, 4, 9, 13, 22, 51, 654200), datetime.datetime(2025, 4, 9, 13, 23, 1, 250800), datetime.datetime(2025, 4, 9, 13, 23, 14, 490700), datetime.datetime(2025, 4, 9, 13, 27, 39, 740300), datetime.datetime(2025, 4, 9, 13, 25, 41, 781500), datetime.datetime(2025, 4, 9, 13, 25, 58, 954700), datetime.datetime(2025, 4, 9, 13, 26, 36, 647400), datetime.datetime(2025, 4, 9, 13, 28, 17, 81100), datetime.datetime(2025, 4, 9, 13, 27, 48, 886600), datetime.datetime(2025, 4, 9, 13, 28, 48, 360800), datetime.datetime(2025, 4, 9, 13, 29, 1, 224200), datetime.datetime(2025, 4, 9, 13, 30, 11, 840700), datetime.datetime(2025, 4, 9, 13, 29, 50, 384500), datetime.datetime(2025, 4, 9, 13, 31, 56, 299100), datetime.datetime(2025, 4, 9, 13, 31, 7, 308900), datetime.datetime(2025, 4, 9, 13, 32, 52, 258300), datetime.datetime(2025, 4, 9, 13, 32, 39, 917400), datetime.datetime(2025, 4, 9, 13, 32, 44, 49300), datetime.datetime(2025, 4, 9, 13, 32, 55, 532300), datetime.datetime(2025, 4, 9, 13, 33, 13, 864300), datetime.datetime(2025, 4, 9, 13, 33, 28, 982500), datetime.datetime(2025, 4, 9, 13, 33, 45, 292400), datetime.datetime(2025, 4, 9, 13, 35, 1, 49700), datetime.datetime(2025, 4, 9, 13, 34, 32, 640800), datetime.datetime(2025, 4, 9, 13, 34, 46, 25000), datetime.datetime(2025, 4, 9, 13, 35, 7, 638300), datetime.datetime(2025, 4, 9, 13, 35, 20, 677200), datetime.datetime(2025, 4, 9, 13, 35, 32, 716900), datetime.datetime(2025, 4, 9, 13, 35, 52, 10500), datetime.datetime(2025, 4, 9, 13, 37, 16, 434200), datetime.datetime(2025, 4, 9, 13, 37, 4, 368600), datetime.datetime(2025, 4, 9, 13, 37, 8, 297200), datetime.datetime(2025, 4, 9, 13, 37, 22, 382900), datetime.datetime(2025, 4, 9, 13, 37, 39, 671000), datetime.datetime(2025, 4, 9, 13, 37, 50, 291000), datetime.datetime(2025, 4, 9, 13, 39, 4, 354700), datetime.datetime(2025, 4, 9, 13, 38, 40, 953700), datetime.datetime(2025, 4, 9, 13, 38, 47, 732500), datetime.datetime(2025, 4, 9, 13, 39, 4, 640200), datetime.datetime(2025, 4, 9, 13, 40, 21, 928700), datetime.datetime(2025, 4, 9, 13, 40, 1, 706700), datetime.datetime(2025, 4, 9, 13, 41, 10, 139300), datetime.datetime(2025, 4, 9, 13, 41, 7, 570600), datetime.datetime(2025, 4, 9, 13, 41, 23, 726700), datetime.datetime(2025, 4, 9, 13, 41, 29, 874700), datetime.datetime(2025, 4, 9, 13, 41, 41, 450800), datetime.datetime(2025, 4, 9, 13, 43, 27, 349500)]</t>
+        </is>
+      </c>
+      <c r="AE65" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>194</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>616ce5db307058da351fd1e5</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>KT0JU6</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" t="n">
+        <v>38</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>2</v>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Firstly, I'd like to say that at times It seemed I was being told to go through the purple when it made sense to, other times I was being told to completely avoid the purple.  It seemed to go on forever.</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>45756.57234169988</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA66" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 12, 54, 35, 153600), datetime.datetime(2025, 4, 9, 12, 55, 8, 998700), datetime.datetime(2025, 4, 9, 12, 56, 44, 145500), datetime.datetime(2025, 4, 9, 12, 57, 2, 78200), datetime.datetime(2025, 4, 9, 12, 57, 2, 458500), datetime.datetime(2025, 4, 9, 12, 58, 17, 577700), datetime.datetime(2025, 4, 9, 12, 59, 14, 448600), datetime.datetime(2025, 4, 9, 13, 0, 57, 549600), datetime.datetime(2025, 4, 9, 13, 0, 17, 511700), datetime.datetime(2025, 4, 9, 13, 0, 49, 851100), datetime.datetime(2025, 4, 9, 13, 1, 35, 368300), datetime.datetime(2025, 4, 9, 13, 3, 28, 373400), datetime.datetime(2025, 4, 9, 13, 3, 3, 160700), datetime.datetime(2025, 4, 9, 13, 3, 51, 545300), datetime.datetime(2025, 4, 9, 13, 4, 1, 732000), datetime.datetime(2025, 4, 9, 13, 6, 18, 38200), datetime.datetime(2025, 4, 9, 13, 5, 50, 413400), datetime.datetime(2025, 4, 9, 13, 9, 32, 994400), datetime.datetime(2025, 4, 9, 13, 8, 31, 412200), datetime.datetime(2025, 4, 9, 13, 9, 17, 410400), datetime.datetime(2025, 4, 9, 13, 9, 27, 364000), datetime.datetime(2025, 4, 9, 13, 10, 31, 741300), datetime.datetime(2025, 4, 9, 13, 10, 25, 871600), datetime.datetime(2025, 4, 9, 13, 10, 37, 735300), datetime.datetime(2025, 4, 9, 13, 11, 12, 604900), datetime.datetime(2025, 4, 9, 13, 11, 18, 647800), datetime.datetime(2025, 4, 9, 13, 13, 25, 318100), datetime.datetime(2025, 4, 9, 13, 13, 25, 318100), datetime.datetime(2025, 4, 9, 13, 22, 2, 456400), datetime.datetime(2025, 4, 9, 13, 19, 9, 773800), datetime.datetime(2025, 4, 9, 13, 19, 26, 430300), datetime.datetime(2025, 4, 9, 13, 19, 40, 67300), datetime.datetime(2025, 4, 9, 13, 19, 51, 304000), datetime.datetime(2025, 4, 9, 13, 21, 12, 596700), datetime.datetime(2025, 4, 9, 13, 21, 8, 8900), datetime.datetime(2025, 4, 9, 13, 21, 20, 664500), datetime.datetime(2025, 4, 9, 13, 21, 40, 629000), datetime.datetime(2025, 4, 9, 13, 22, 25, 315500), datetime.datetime(2025, 4, 9, 13, 23, 36, 37100), datetime.datetime(2025, 4, 9, 13, 23, 21, 634700), datetime.datetime(2025, 4, 9, 13, 23, 50, 2500), datetime.datetime(2025, 4, 9, 13, 23, 54, 191000), datetime.datetime(2025, 4, 9, 13, 24, 17, 319200), datetime.datetime(2025, 4, 9, 13, 24, 24, 552600), datetime.datetime(2025, 4, 9, 13, 26, 26, 176500), datetime.datetime(2025, 4, 9, 13, 26, 3, 807000), datetime.datetime(2025, 4, 9, 13, 26, 13, 817200), datetime.datetime(2025, 4, 9, 13, 26, 25, 266900), datetime.datetime(2025, 4, 9, 13, 26, 42, 704500), datetime.datetime(2025, 4, 9, 13, 26, 46, 600200), datetime.datetime(2025, 4, 9, 13, 28, 25, 813200), datetime.datetime(2025, 4, 9, 13, 28, 7, 809200), datetime.datetime(2025, 4, 9, 13, 28, 27, 304900), datetime.datetime(2025, 4, 9, 13, 28, 34, 606400), datetime.datetime(2025, 4, 9, 13, 29, 48, 80900), datetime.datetime(2025, 4, 9, 13, 29, 32, 85600), datetime.datetime(2025, 4, 9, 13, 29, 46, 612800), datetime.datetime(2025, 4, 9, 13, 29, 58, 290000), datetime.datetime(2025, 4, 9, 13, 33, 27, 97700), datetime.datetime(2025, 4, 9, 13, 32, 0, 734900), datetime.datetime(2025, 4, 9, 13, 32, 10, 622900), datetime.datetime(2025, 4, 9, 13, 32, 40, 107300), datetime.datetime(2025, 4, 9, 13, 33, 11, 438800), datetime.datetime(2025, 4, 9, 13, 33, 11, 331200), datetime.datetime(2025, 4, 9, 13, 33, 44, 89000), datetime.datetime(2025, 4, 9, 13, 35, 0, 606000), datetime.datetime(2025, 4, 9, 13, 34, 32, 308700), datetime.datetime(2025, 4, 9, 13, 34, 40, 798700), datetime.datetime(2025, 4, 9, 13, 34, 58, 542300), datetime.datetime(2025, 4, 9, 13, 35, 3, 197300), datetime.datetime(2025, 4, 9, 13, 35, 50, 65800), datetime.datetime(2025, 4, 9, 13, 35, 45, 244800), datetime.datetime(2025, 4, 9, 13, 36, 10, 202200), datetime.datetime(2025, 4, 9, 13, 36, 47, 270900), datetime.datetime(2025, 4, 9, 13, 36, 46, 270300), datetime.datetime(2025, 4, 9, 13, 36, 50, 822400), datetime.datetime(2025, 4, 9, 13, 37, 12, 642600), datetime.datetime(2025, 4, 9, 13, 37, 15, 406700), datetime.datetime(2025, 4, 9, 13, 37, 27, 39500), datetime.datetime(2025, 4, 9, 13, 37, 44, 244200), datetime.datetime(2025, 4, 9, 13, 38, 46, 302900), datetime.datetime(2025, 4, 9, 13, 38, 28, 22200), datetime.datetime(2025, 4, 9, 13, 38, 41, 776300), datetime.datetime(2025, 4, 9, 13, 38, 52, 727100), datetime.datetime(2025, 4, 9, 13, 39, 13, 17200), datetime.datetime(2025, 4, 9, 13, 39, 23, 586700), datetime.datetime(2025, 4, 9, 13, 41, 30, 495700), datetime.datetime(2025, 4, 9, 13, 40, 40, 616900), datetime.datetime(2025, 4, 9, 13, 41, 16, 936100), datetime.datetime(2025, 4, 9, 13, 41, 16, 536800), datetime.datetime(2025, 4, 9, 13, 41, 28, 673900), datetime.datetime(2025, 4, 9, 13, 42, 18, 843600)]</t>
+        </is>
+      </c>
+      <c r="AE66" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>195</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>676aa9c4bde30e11da44f128</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>3EI4KO</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>33</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>2</v>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>45756.57145902239</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA67" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 9, 12, 50, 31, 958300), datetime.datetime(2025, 4, 9, 12, 51, 20, 397500), datetime.datetime(2025, 4, 9, 12, 51, 56, 52600), datetime.datetime(2025, 4, 9, 12, 52, 33, 120600), datetime.datetime(2025, 4, 9, 13, 0, 9, 670100), datetime.datetime(2025, 4, 9, 12, 56, 37, 633300), datetime.datetime(2025, 4, 9, 12, 57, 0, 305300), datetime.datetime(2025, 4, 9, 12, 57, 12, 870900), datetime.datetime(2025, 4, 9, 13, 1, 19, 740800), datetime.datetime(2025, 4, 9, 12, 59, 52, 751000), datetime.datetime(2025, 4, 9, 13, 0, 5, 708400), datetime.datetime(2025, 4, 9, 13, 0, 19, 846000), datetime.datetime(2025, 4, 9, 13, 3, 9, 1800), datetime.datetime(2025, 4, 9, 13, 2, 12, 174200), datetime.datetime(2025, 4, 9, 13, 2, 21, 172900), datetime.datetime(2025, 4, 9, 13, 2, 42, 538100), datetime.datetime(2025, 4, 9, 13, 2, 57, 138000), datetime.datetime(2025, 4, 9, 13, 3, 22, 934800), datetime.datetime(2025, 4, 9, 13, 6, 43, 340300), datetime.datetime(2025, 4, 9, 13, 5, 30, 117200), datetime.datetime(2025, 4, 9, 13, 5, 45, 447300), datetime.datetime(2025, 4, 9, 13, 8, 15, 7600), datetime.datetime(2025, 4, 9, 13, 7, 16, 106900), datetime.datetime(2025, 4, 9, 13, 9, 52, 799800), datetime.datetime(2025, 4, 9, 13, 8, 58, 465700), datetime.datetime(2025, 4, 9, 13, 10, 7, 454100), datetime.datetime(2025, 4, 9, 13, 9, 55, 449400), datetime.datetime(2025, 4, 9, 13, 10, 5, 451200), datetime.datetime(2025, 4, 9, 13, 10, 58, 132400), datetime.datetime(2025, 4, 9, 13, 10, 52, 362700), datetime.datetime(2025, 4, 9, 13, 12, 7, 443500), datetime.datetime(2025, 4, 9, 13, 12, 7, 443500), datetime.datetime(2025, 4, 9, 13, 22, 2, 929400), datetime.datetime(2025, 4, 9, 13, 18, 19, 344400), datetime.datetime(2025, 4, 9, 13, 18, 26, 277100), datetime.datetime(2025, 4, 9, 13, 18, 37, 742200), datetime.datetime(2025, 4, 9, 13, 20, 16, 974200), datetime.datetime(2025, 4, 9, 13, 20, 55, 985500), datetime.datetime(2025, 4, 9, 13, 21, 41, 248700), datetime.datetime(2025, 4, 9, 13, 21, 43, 116200), datetime.datetime(2025, 4, 9, 13, 21, 39, 482900), datetime.datetime(2025, 4, 9, 13, 22, 0, 96900), datetime.datetime(2025, 4, 9, 13, 22, 11, 263700), datetime.datetime(2025, 4, 9, 13, 23, 31, 857200), datetime.datetime(2025, 4, 9, 13, 23, 18, 204600), datetime.datetime(2025, 4, 9, 13, 24, 31, 538500), datetime.datetime(2025, 4, 9, 13, 24, 24, 800700), datetime.datetime(2025, 4, 9, 13, 25, 26, 659000), datetime.datetime(2025, 4, 9, 13, 25, 47, 389300), datetime.datetime(2025, 4, 9, 13, 25, 45, 171100), datetime.datetime(2025, 4, 9, 13, 25, 55, 435900), datetime.datetime(2025, 4, 9, 13, 26, 5, 376700), datetime.datetime(2025, 4, 9, 13, 26, 34, 327700), datetime.datetime(2025, 4, 9, 13, 28, 11, 846300), datetime.datetime(2025, 4, 9, 13, 27, 38, 447800), datetime.datetime(2025, 4, 9, 13, 27, 49, 580200), datetime.datetime(2025, 4, 9, 13, 28, 24, 997200), datetime.datetime(2025, 4, 9, 13, 28, 26, 257700), datetime.datetime(2025, 4, 9, 13, 29, 51, 604700), datetime.datetime(2025, 4, 9, 13, 29, 27, 214600), datetime.datetime(2025, 4, 9, 13, 29, 47, 558800), datetime.datetime(2025, 4, 9, 13, 29, 55, 589100), datetime.datetime(2025, 4, 9, 13, 33, 33, 97000), datetime.datetime(2025, 4, 9, 13, 32, 3, 1600), datetime.datetime(2025, 4, 9, 13, 32, 21, 302300), datetime.datetime(2025, 4, 9, 13, 32, 52, 151800), datetime.datetime(2025, 4, 9, 13, 32, 55, 202600), datetime.datetime(2025, 4, 9, 13, 33, 13, 481600), datetime.datetime(2025, 4, 9, 13, 34, 0, 282600), datetime.datetime(2025, 4, 9, 13, 34, 46, 277400), datetime.datetime(2025, 4, 9, 13, 34, 34, 478200), datetime.datetime(2025, 4, 9, 13, 34, 43, 241600), datetime.datetime(2025, 4, 9, 13, 35, 3, 728700), datetime.datetime(2025, 4, 9, 13, 35, 11, 896300), datetime.datetime(2025, 4, 9, 13, 35, 20, 711600), datetime.datetime(2025, 4, 9, 13, 35, 38, 122200), datetime.datetime(2025, 4, 9, 13, 35, 55, 623900), datetime.datetime(2025, 4, 9, 13, 37, 0, 683200), datetime.datetime(2025, 4, 9, 13, 36, 40, 689100), datetime.datetime(2025, 4, 9, 13, 36, 51, 319300), datetime.datetime(2025, 4, 9, 13, 37, 8, 25300), datetime.datetime(2025, 4, 9, 13, 37, 26, 590600), datetime.datetime(2025, 4, 9, 13, 37, 56, 145300), datetime.datetime(2025, 4, 9, 13, 38, 36, 447100), datetime.datetime(2025, 4, 9, 13, 38, 21, 467600), datetime.datetime(2025, 4, 9, 13, 38, 28, 239800), datetime.datetime(2025, 4, 9, 13, 38, 44, 497100), datetime.datetime(2025, 4, 9, 13, 39, 21, 246100), datetime.datetime(2025, 4, 9, 13, 39, 29, 690600), datetime.datetime(2025, 4, 9, 13, 39, 34, 840900), datetime.datetime(2025, 4, 9, 13, 40, 50, 257900), datetime.datetime(2025, 4, 9, 13, 40, 32, 555400), datetime.datetime(2025, 4, 9, 13, 40, 35, 723400), datetime.datetime(2025, 4, 9, 13, 40, 43, 643800), datetime.datetime(2025, 4, 9, 13, 41, 5, 710300), datetime.datetime(2025, 4, 9, 13, 41, 45, 79200)]</t>
+        </is>
+      </c>
+      <c r="AE67" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>196</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>6156fef09d1ab07148870099</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0FCRK0</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>45756.5521197761</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>56</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="n">
+        <v>56</v>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/simple_game_test/filtered_users.xlsx
+++ b/simple_game_test/filtered_users.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL68"/>
+  <dimension ref="A1:AM78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,10 +623,17 @@
           <t>experimental_condition</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>domain_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>89</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -721,18 +728,27 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>24</v>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>90</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -827,18 +843,27 @@
         <v>2</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="n">
-        <v>24</v>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>91</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -943,18 +968,27 @@
         <v>1</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="n">
-        <v>24</v>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>98</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1063,18 +1097,27 @@
         <v>2</v>
       </c>
       <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
-        <v>27</v>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>99</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1183,18 +1226,27 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="n">
-        <v>27</v>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>100</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1289,18 +1341,27 @@
         <v>1</v>
       </c>
       <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="n">
-        <v>27</v>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>101</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1409,18 +1470,27 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="n">
-        <v>28</v>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>102</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1529,18 +1599,27 @@
         <v>1</v>
       </c>
       <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="n">
-        <v>28</v>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>103</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1649,18 +1728,27 @@
         <v>2</v>
       </c>
       <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="n">
-        <v>28</v>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>104</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1755,18 +1843,27 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="n">
-        <v>29</v>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>105</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1861,18 +1958,27 @@
         <v>1</v>
       </c>
       <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="n">
-        <v>29</v>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>106</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1951,10 +2057,13 @@
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>107</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2063,18 +2172,27 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="n">
-        <v>31</v>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>108</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2169,18 +2287,27 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="n">
-        <v>32</v>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>109</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2275,18 +2402,27 @@
         <v>2</v>
       </c>
       <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="n">
-        <v>30</v>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>110</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2395,18 +2531,27 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="n">
-        <v>30</v>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>111</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2501,18 +2646,27 @@
         <v>2</v>
       </c>
       <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="n">
-        <v>29</v>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>112</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2621,18 +2775,27 @@
         <v>1</v>
       </c>
       <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="n">
-        <v>32</v>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>113</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2741,18 +2904,27 @@
         <v>1</v>
       </c>
       <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="n">
-        <v>31</v>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>114</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2861,18 +3033,27 @@
         <v>1</v>
       </c>
       <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="n">
-        <v>30</v>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>115</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2967,18 +3148,27 @@
         <v>1</v>
       </c>
       <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="n">
-        <v>33</v>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>116</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3073,18 +3263,27 @@
         <v>2</v>
       </c>
       <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="n">
-        <v>31</v>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>117</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3193,18 +3392,27 @@
         <v>2</v>
       </c>
       <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="n">
-        <v>32</v>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>118</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3299,18 +3507,27 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="n">
-        <v>33</v>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>119</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3405,18 +3622,27 @@
         <v>2</v>
       </c>
       <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="n">
-        <v>33</v>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>120</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3505,18 +3731,27 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="n">
-        <v>34</v>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>121</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3605,18 +3840,27 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="n">
-        <v>34</v>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>154</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3725,18 +3969,27 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="n">
-        <v>44</v>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>155</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3831,18 +4084,27 @@
         <v>2</v>
       </c>
       <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="n">
-        <v>44</v>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>156</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3951,18 +4213,27 @@
         <v>1</v>
       </c>
       <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="n">
-        <v>44</v>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>157</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4071,18 +4342,27 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="n">
-        <v>45</v>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>160</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4177,18 +4457,27 @@
         <v>1</v>
       </c>
       <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="n">
-        <v>46</v>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>161</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4297,18 +4586,27 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="n">
-        <v>46</v>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>162</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4417,18 +4715,27 @@
         <v>2</v>
       </c>
       <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="n">
-        <v>46</v>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>163</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4533,18 +4840,27 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="n">
-        <v>47</v>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>164</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4623,10 +4939,13 @@
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>165</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4721,18 +5040,27 @@
         <v>2</v>
       </c>
       <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="n">
-        <v>47</v>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>166</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4841,18 +5169,27 @@
         <v>1</v>
       </c>
       <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="n">
-        <v>47</v>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>167</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4947,18 +5284,27 @@
         <v>2</v>
       </c>
       <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="n">
-        <v>49</v>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>168</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5053,18 +5399,27 @@
         <v>1</v>
       </c>
       <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="n">
-        <v>49</v>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>169</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5153,18 +5508,27 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="n">
-        <v>48</v>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>170</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5259,18 +5623,27 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="n">
-        <v>49</v>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>171</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5349,10 +5722,13 @@
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>172</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5431,10 +5807,13 @@
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>173</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5513,10 +5892,13 @@
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>174</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5611,18 +5993,27 @@
         <v>1</v>
       </c>
       <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="n">
-        <v>50</v>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>175</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5717,18 +6108,27 @@
         <v>2</v>
       </c>
       <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="n">
-        <v>50</v>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>176</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -5823,18 +6223,27 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="n">
-        <v>50</v>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>178</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -5939,18 +6348,27 @@
         <v>0</v>
       </c>
       <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="n">
-        <v>51</v>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>179</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6039,18 +6457,27 @@
         <v>1</v>
       </c>
       <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="n">
-        <v>51</v>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>180</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6159,18 +6586,27 @@
         <v>2</v>
       </c>
       <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="n">
-        <v>51</v>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>181</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6259,18 +6695,27 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="n">
-        <v>52</v>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>182</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6379,18 +6824,27 @@
         <v>1</v>
       </c>
       <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="n">
-        <v>52</v>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>183</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -6469,10 +6923,13 @@
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>184</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6577,18 +7034,27 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="n">
-        <v>52</v>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>185</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -6697,18 +7163,27 @@
         <v>2</v>
       </c>
       <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="n">
-        <v>52</v>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>186</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -6817,18 +7292,27 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="inlineStr"/>
-      <c r="AK58" t="n">
-        <v>54</v>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>187</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -6923,18 +7407,27 @@
         <v>1</v>
       </c>
       <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="n">
-        <v>53</v>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>188</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -7043,18 +7536,27 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="n">
-        <v>53</v>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>189</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -7149,18 +7651,27 @@
         <v>2</v>
       </c>
       <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="n">
-        <v>53</v>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>190</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -7249,18 +7760,27 @@
         <v>1</v>
       </c>
       <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="n">
-        <v>54</v>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>191</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -7355,18 +7875,27 @@
         <v>1</v>
       </c>
       <c r="AJ63" t="inlineStr"/>
-      <c r="AK63" t="n">
-        <v>54</v>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>192</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -7475,18 +8004,27 @@
         <v>2</v>
       </c>
       <c r="AJ64" t="inlineStr"/>
-      <c r="AK64" t="n">
-        <v>54</v>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>sb-at</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>193</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -7595,18 +8133,27 @@
         <v>2</v>
       </c>
       <c r="AJ65" t="inlineStr"/>
-      <c r="AK65" t="n">
-        <v>55</v>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>194</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -7715,18 +8262,27 @@
         <v>0</v>
       </c>
       <c r="AJ66" t="inlineStr"/>
-      <c r="AK66" t="n">
-        <v>55</v>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>195</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -7831,18 +8387,27 @@
         <v>1</v>
       </c>
       <c r="AJ67" t="inlineStr"/>
-      <c r="AK67" t="n">
-        <v>55</v>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
           <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>196</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -7931,12 +8496,1205 @@
         <v>0</v>
       </c>
       <c r="AJ68" t="inlineStr"/>
-      <c r="AK68" t="n">
-        <v>56</v>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
           <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>67e879fe11e09af6fae79aaf</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>UL9ZRR</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>45757.13247747928</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>67f573c0a4c92853e134bec9</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>D51U96</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>45757.11224104754</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>diagnostic feedback</t>
+        </is>
+      </c>
+      <c r="AA70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 10, 2, 16, 42, 101900), datetime.datetime(2025, 4, 10, 2, 16, 23, 708800), datetime.datetime(2025, 4, 10, 2, 17, 15, 105900), datetime.datetime(2025, 4, 10, 2, 17, 47, 158600), datetime.datetime(2025, 4, 10, 2, 25, 41, 832500), datetime.datetime(2025, 4, 10, 2, 21, 58, 696200), datetime.datetime(2025, 4, 10, 2, 22, 29, 126300), datetime.datetime(2025, 4, 10, 2, 22, 43, 715600), datetime.datetime(2025, 4, 10, 2, 29, 32, 682300), datetime.datetime(2025, 4, 10, 2, 27, 1, 621600), datetime.datetime(2025, 4, 10, 2, 27, 31, 263600), datetime.datetime(2025, 4, 10, 2, 27, 53, 996200), datetime.datetime(2025, 4, 10, 2, 28, 15, 888800), datetime.datetime(2025, 4, 10, 2, 28, 29, 330500), datetime.datetime(2025, 4, 10, 2, 32, 54, 959100), datetime.datetime(2025, 4, 10, 2, 31, 18, 6900), datetime.datetime(2025, 4, 10, 2, 32, 9, 154800), datetime.datetime(2025, 4, 10, 2, 32, 47, 562900), datetime.datetime(2025, 4, 10, 2, 32, 53, 229500), datetime.datetime(2025, 4, 10, 2, 33, 1, 7800), datetime.datetime(2025, 4, 10, 2, 34, 55, 892700), datetime.datetime(2025, 4, 10, 2, 35, 2, 40200), datetime.datetime(2025, 4, 10, 2, 35, 19, 589700), datetime.datetime(2025, 4, 10, 2, 35, 27, 830000), datetime.datetime(2025, 4, 10, 2, 37, 3, 186900), datetime.datetime(2025, 4, 10, 2, 37, 11, 174900), datetime.datetime(2025, 4, 10, 2, 37, 7, 442000), datetime.datetime(2025, 4, 10, 2, 37, 25, 88800), datetime.datetime(2025, 4, 10, 2, 38, 34, 889200), datetime.datetime(2025, 4, 10, 2, 38, 22, 441200), datetime.datetime(2025, 4, 10, 2, 38, 44, 56500), datetime.datetime(2025, 4, 10, 2, 39, 24, 87500), datetime.datetime(2025, 4, 10, 2, 39, 37, 106000), datetime.datetime(2025, 4, 10, 2, 41, 50, 631800), datetime.datetime(2025, 4, 10, 2, 41, 5, 828700), datetime.datetime(2025, 4, 10, 2, 41, 16, 150600)]</t>
+        </is>
+      </c>
+      <c r="AE70" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>57</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>67f67e86d2314e24293f3d2c</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>IHUBDM</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>25</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>4</v>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>I have no feedback.</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="n">
+        <v>45757.15735712661</v>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA71" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'AudioVolumeUp', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 10, 2, 23, 49, 550400), datetime.datetime(2025, 4, 10, 2, 23, 22, 230000), datetime.datetime(2025, 4, 10, 2, 25, 41, 947500), datetime.datetime(2025, 4, 10, 2, 25, 7, 208800), datetime.datetime(2025, 4, 10, 2, 25, 22, 545000), datetime.datetime(2025, 4, 10, 2, 25, 29, 420800), datetime.datetime(2025, 4, 10, 2, 45, 45, 99900), datetime.datetime(2025, 4, 10, 2, 35, 59, 733300), datetime.datetime(2025, 4, 10, 2, 36, 13, 377500), datetime.datetime(2025, 4, 10, 2, 36, 27, 210000), datetime.datetime(2025, 4, 10, 2, 36, 56, 284900), datetime.datetime(2025, 4, 10, 2, 37, 8, 31900), datetime.datetime(2025, 4, 10, 2, 56, 6, 775200), datetime.datetime(2025, 4, 10, 2, 47, 1, 543400), datetime.datetime(2025, 4, 10, 2, 47, 23, 181300), datetime.datetime(2025, 4, 10, 2, 47, 30, 820400), datetime.datetime(2025, 4, 10, 2, 53, 10, 391200), datetime.datetime(2025, 4, 10, 2, 50, 34, 545100), datetime.datetime(2025, 4, 10, 2, 50, 47, 859800), datetime.datetime(2025, 4, 10, 2, 50, 57, 217600), datetime.datetime(2025, 4, 10, 2, 56, 15, 249900), datetime.datetime(2025, 4, 10, 2, 54, 4, 934000), datetime.datetime(2025, 4, 10, 2, 58, 56, 243700), datetime.datetime(2025, 4, 10, 2, 56, 59, 49700), datetime.datetime(2025, 4, 10, 2, 57, 21, 37300), datetime.datetime(2025, 4, 10, 2, 57, 28, 682100), datetime.datetime(2025, 4, 10, 2, 57, 43, 319900), datetime.datetime(2025, 4, 10, 2, 58, 1, 916700), datetime.datetime(2025, 4, 10, 2, 58, 26, 778000), datetime.datetime(2025, 4, 10, 2, 59, 8, 980400), datetime.datetime(2025, 4, 10, 2, 59, 12, 15100), datetime.datetime(2025, 4, 10, 2, 59, 39, 18000), datetime.datetime(2025, 4, 10, 3, 14, 56, 286000), datetime.datetime(2025, 4, 10, 3, 8, 9, 974800), datetime.datetime(2025, 4, 10, 3, 9, 57, 468800), datetime.datetime(2025, 4, 10, 3, 10, 3, 746200), datetime.datetime(2025, 4, 10, 3, 10, 5, 470000), datetime.datetime(2025, 4, 10, 3, 11, 5, 806500), datetime.datetime(2025, 4, 10, 3, 10, 53, 744500), datetime.datetime(2025, 4, 10, 3, 11, 56, 512400), datetime.datetime(2025, 4, 10, 3, 12, 44, 206800), datetime.datetime(2025, 4, 10, 3, 12, 55, 328200), datetime.datetime(2025, 4, 10, 3, 13, 0, 45400), datetime.datetime(2025, 4, 10, 3, 13, 13, 958600), datetime.datetime(2025, 4, 10, 3, 13, 22, 170700), datetime.datetime(2025, 4, 10, 3, 14, 38, 412800), datetime.datetime(2025, 4, 10, 3, 14, 38, 412800), datetime.datetime(2025, 4, 10, 3, 24, 20, 256700), datetime.datetime(2025, 4, 10, 3, 20, 18, 875800), datetime.datetime(2025, 4, 10, 3, 21, 5, 89100), datetime.datetime(2025, 4, 10, 3, 20, 59, 956600), datetime.datetime(2025, 4, 10, 3, 29, 4, 793600), datetime.datetime(2025, 4, 10, 3, 25, 20, 394900), datetime.datetime(2025, 4, 10, 3, 26, 0, 166000), datetime.datetime(2025, 4, 10, 3, 26, 1, 178600), datetime.datetime(2025, 4, 10, 3, 31, 16, 937100), datetime.datetime(2025, 4, 10, 3, 29, 42, 655600), datetime.datetime(2025, 4, 10, 3, 29, 57, 794000), datetime.datetime(2025, 4, 10, 3, 30, 15, 280100), datetime.datetime(2025, 4, 10, 3, 30, 41, 733900), datetime.datetime(2025, 4, 10, 3, 34, 47, 906000), datetime.datetime(2025, 4, 10, 3, 33, 9, 647800), datetime.datetime(2025, 4, 10, 3, 33, 57, 720600), datetime.datetime(2025, 4, 10, 3, 34, 4, 223800), datetime.datetime(2025, 4, 10, 3, 34, 22, 92900), datetime.datetime(2025, 4, 10, 3, 36, 28, 831400), datetime.datetime(2025, 4, 10, 3, 35, 54, 312100), datetime.datetime(2025, 4, 10, 3, 36, 16, 844100), datetime.datetime(2025, 4, 10, 3, 38, 22, 348700), datetime.datetime(2025, 4, 10, 3, 37, 51, 502900), datetime.datetime(2025, 4, 10, 3, 38, 35, 226100), datetime.datetime(2025, 4, 10, 3, 38, 53, 367400), datetime.datetime(2025, 4, 10, 3, 39, 7, 914000), datetime.datetime(2025, 4, 10, 3, 39, 11, 585700), datetime.datetime(2025, 4, 10, 3, 39, 56, 239800), datetime.datetime(2025, 4, 10, 3, 40, 1, 765100), datetime.datetime(2025, 4, 10, 3, 40, 15, 293500), datetime.datetime(2025, 4, 10, 3, 41, 14, 116800), datetime.datetime(2025, 4, 10, 3, 41, 12, 947200), datetime.datetime(2025, 4, 10, 3, 42, 40, 587700), datetime.datetime(2025, 4, 10, 3, 42, 24, 516800), datetime.datetime(2025, 4, 10, 3, 42, 33, 457000), datetime.datetime(2025, 4, 10, 3, 43, 29, 945700), datetime.datetime(2025, 4, 10, 3, 43, 53, 832600), datetime.datetime(2025, 4, 10, 3, 45, 20, 232300)]</t>
+        </is>
+      </c>
+      <c r="AE71" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>58</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>67ec48793ebbd294ff4730c5</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>YMEWA7</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>45757.15007667374</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA72" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'r', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 10, 2, 32, 37, 840600), datetime.datetime(2025, 4, 10, 2, 31, 38, 221900), datetime.datetime(2025, 4, 10, 2, 32, 56, 659100), datetime.datetime(2025, 4, 10, 2, 33, 42, 171000), datetime.datetime(2025, 4, 10, 2, 34, 39, 667500), datetime.datetime(2025, 4, 10, 2, 35, 2, 688400), datetime.datetime(2025, 4, 10, 2, 36, 17, 984700), datetime.datetime(2025, 4, 10, 2, 36, 37, 136800), datetime.datetime(2025, 4, 10, 2, 39, 41, 655200), datetime.datetime(2025, 4, 10, 2, 39, 26, 380500), datetime.datetime(2025, 4, 10, 2, 39, 53, 777600), datetime.datetime(2025, 4, 10, 2, 41, 18, 462900), datetime.datetime(2025, 4, 10, 2, 41, 55, 68300), datetime.datetime(2025, 4, 10, 2, 42, 9, 609200), datetime.datetime(2025, 4, 10, 2, 42, 39, 795900), datetime.datetime(2025, 4, 10, 2, 46, 23, 542700), datetime.datetime(2025, 4, 10, 2, 45, 58, 385900), datetime.datetime(2025, 4, 10, 2, 47, 59, 195500), datetime.datetime(2025, 4, 10, 2, 47, 33, 86600), datetime.datetime(2025, 4, 10, 2, 48, 21, 300), datetime.datetime(2025, 4, 10, 2, 49, 16, 585400), datetime.datetime(2025, 4, 10, 2, 49, 46, 417700), datetime.datetime(2025, 4, 10, 2, 49, 55, 650000), datetime.datetime(2025, 4, 10, 2, 50, 40, 668200), datetime.datetime(2025, 4, 10, 2, 51, 43, 400100), datetime.datetime(2025, 4, 10, 2, 51, 46, 173300), datetime.datetime(2025, 4, 10, 2, 52, 55, 878900), datetime.datetime(2025, 4, 10, 2, 53, 12, 197800), datetime.datetime(2025, 4, 10, 2, 56, 45, 438200), datetime.datetime(2025, 4, 10, 2, 57, 47, 973400), datetime.datetime(2025, 4, 10, 2, 58, 49, 430100), datetime.datetime(2025, 4, 10, 2, 59, 17, 634800), datetime.datetime(2025, 4, 10, 3, 5, 16, 737100), datetime.datetime(2025, 4, 10, 3, 3, 46, 501100), datetime.datetime(2025, 4, 10, 3, 4, 36, 439900), datetime.datetime(2025, 4, 10, 3, 5, 18, 713600), datetime.datetime(2025, 4, 10, 3, 7, 49, 454000), datetime.datetime(2025, 4, 10, 3, 10, 15, 621900), datetime.datetime(2025, 4, 10, 3, 12, 32, 359600), datetime.datetime(2025, 4, 10, 3, 11, 29, 850300), datetime.datetime(2025, 4, 10, 3, 12, 5, 320100), datetime.datetime(2025, 4, 10, 3, 14, 38, 653100), datetime.datetime(2025, 4, 10, 3, 16, 38, 210800), datetime.datetime(2025, 4, 10, 3, 18, 36, 644600)]</t>
+        </is>
+      </c>
+      <c r="AE72" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>59</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>67f4c41c98f97634f1260ac7</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>B94NDH</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="n">
+        <v>28</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>4</v>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>No comments</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>45757.1429434395</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA73" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 10, 2, 18, 35, 349500), datetime.datetime(2025, 4, 10, 2, 19, 0, 984100), datetime.datetime(2025, 4, 10, 2, 20, 37, 201000), datetime.datetime(2025, 4, 10, 2, 22, 10, 927400), datetime.datetime(2025, 4, 10, 2, 23, 6, 379500), datetime.datetime(2025, 4, 10, 2, 23, 1, 339100), datetime.datetime(2025, 4, 10, 2, 24, 3, 610000), datetime.datetime(2025, 4, 10, 2, 27, 23, 772100), datetime.datetime(2025, 4, 10, 2, 27, 13, 875200), datetime.datetime(2025, 4, 10, 2, 27, 14, 906000), datetime.datetime(2025, 4, 10, 2, 28, 36, 61700), datetime.datetime(2025, 4, 10, 2, 28, 30, 667500), datetime.datetime(2025, 4, 10, 2, 29, 27, 220800), datetime.datetime(2025, 4, 10, 2, 29, 56, 971600), datetime.datetime(2025, 4, 10, 2, 31, 36, 298900), datetime.datetime(2025, 4, 10, 2, 31, 31, 621800), datetime.datetime(2025, 4, 10, 2, 32, 4, 291200), datetime.datetime(2025, 4, 10, 2, 33, 4, 525000), datetime.datetime(2025, 4, 10, 2, 35, 33, 767400), datetime.datetime(2025, 4, 10, 2, 34, 34, 873300), datetime.datetime(2025, 4, 10, 2, 35, 22, 575200), datetime.datetime(2025, 4, 10, 2, 35, 22, 651900), datetime.datetime(2025, 4, 10, 2, 36, 20, 141400), datetime.datetime(2025, 4, 10, 2, 36, 7, 442300), datetime.datetime(2025, 4, 10, 2, 37, 20, 258600), datetime.datetime(2025, 4, 10, 2, 37, 15, 664200), datetime.datetime(2025, 4, 10, 2, 38, 5, 406700), datetime.datetime(2025, 4, 10, 2, 38, 17, 162200), datetime.datetime(2025, 4, 10, 2, 39, 59, 907500), datetime.datetime(2025, 4, 10, 2, 41, 1, 336600), datetime.datetime(2025, 4, 10, 2, 41, 42, 719500), datetime.datetime(2025, 4, 10, 2, 41, 44, 225100), datetime.datetime(2025, 4, 10, 2, 43, 36, 776900), datetime.datetime(2025, 4, 10, 2, 44, 59, 531800), datetime.datetime(2025, 4, 10, 2, 44, 44, 991800), datetime.datetime(2025, 4, 10, 2, 46, 6, 161500), datetime.datetime(2025, 4, 10, 2, 47, 55, 875700), datetime.datetime(2025, 4, 10, 2, 47, 15, 533900), datetime.datetime(2025, 4, 10, 2, 47, 31, 211700), datetime.datetime(2025, 4, 10, 2, 47, 47, 924000), datetime.datetime(2025, 4, 10, 2, 48, 23, 818800), datetime.datetime(2025, 4, 10, 2, 52, 56, 900700), datetime.datetime(2025, 4, 10, 2, 52, 56, 900700), datetime.datetime(2025, 4, 10, 2, 55, 47, 375800), datetime.datetime(2025, 4, 10, 2, 56, 23, 458500), datetime.datetime(2025, 4, 10, 2, 57, 5, 971300), datetime.datetime(2025, 4, 10, 2, 57, 24, 127100), datetime.datetime(2025, 4, 10, 2, 58, 40, 664100), datetime.datetime(2025, 4, 10, 2, 59, 37, 66900), datetime.datetime(2025, 4, 10, 3, 0, 12, 749000), datetime.datetime(2025, 4, 10, 2, 59, 58, 505300), datetime.datetime(2025, 4, 10, 3, 0, 14, 658000), datetime.datetime(2025, 4, 10, 3, 0, 47, 831100), datetime.datetime(2025, 4, 10, 3, 1, 56, 177600), datetime.datetime(2025, 4, 10, 3, 1, 51, 71500), datetime.datetime(2025, 4, 10, 3, 2, 46, 501800), datetime.datetime(2025, 4, 10, 3, 4, 24, 329100), datetime.datetime(2025, 4, 10, 3, 6, 21, 949500), datetime.datetime(2025, 4, 10, 3, 5, 34, 975700), datetime.datetime(2025, 4, 10, 3, 6, 57, 139900), datetime.datetime(2025, 4, 10, 3, 7, 10, 334900), datetime.datetime(2025, 4, 10, 3, 8, 59, 975500), datetime.datetime(2025, 4, 10, 3, 9, 22, 827300), datetime.datetime(2025, 4, 10, 3, 9, 37, 860800), datetime.datetime(2025, 4, 10, 3, 9, 55, 629000), datetime.datetime(2025, 4, 10, 3, 10, 38, 549000), datetime.datetime(2025, 4, 10, 3, 11, 39, 355300), datetime.datetime(2025, 4, 10, 3, 11, 47, 831700), datetime.datetime(2025, 4, 10, 3, 12, 38, 433900), datetime.datetime(2025, 4, 10, 3, 13, 51, 328400), datetime.datetime(2025, 4, 10, 3, 14, 1, 151500), datetime.datetime(2025, 4, 10, 3, 14, 28, 202900), datetime.datetime(2025, 4, 10, 3, 15, 8, 303200), datetime.datetime(2025, 4, 10, 3, 16, 20, 984800), datetime.datetime(2025, 4, 10, 3, 16, 31, 715300), datetime.datetime(2025, 4, 10, 3, 17, 33, 339600), datetime.datetime(2025, 4, 10, 3, 17, 22, 234200), datetime.datetime(2025, 4, 10, 3, 19, 15, 604900), datetime.datetime(2025, 4, 10, 3, 18, 41, 257200), datetime.datetime(2025, 4, 10, 3, 19, 16, 3000), datetime.datetime(2025, 4, 10, 3, 19, 58, 3500), datetime.datetime(2025, 4, 10, 3, 20, 35, 678700), datetime.datetime(2025, 4, 10, 3, 21, 36, 864400), datetime.datetime(2025, 4, 10, 3, 21, 53, 193900), datetime.datetime(2025, 4, 10, 3, 21, 50, 357100), datetime.datetime(2025, 4, 10, 3, 22, 7, 368800), datetime.datetime(2025, 4, 10, 3, 22, 35, 881200), datetime.datetime(2025, 4, 10, 3, 23, 19, 982200), datetime.datetime(2025, 4, 10, 3, 24, 51, 731900)]</t>
+        </is>
+      </c>
+      <c r="AE73" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>57</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5baa5c962eb8020001f1ed3a</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>FJG1EX</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="n">
+        <v>45757.10861085919</v>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="AA74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 10, 2, 17, 31, 405600), datetime.datetime(2025, 4, 10, 2, 17, 29, 65500), datetime.datetime(2025, 4, 10, 2, 17, 42, 736300), datetime.datetime(2025, 4, 10, 2, 19, 3, 68400), datetime.datetime(2025, 4, 10, 2, 24, 51, 74900), datetime.datetime(2025, 4, 10, 2, 22, 19, 836300), datetime.datetime(2025, 4, 10, 2, 23, 18, 351400), datetime.datetime(2025, 4, 10, 2, 23, 55, 894600), datetime.datetime(2025, 4, 10, 2, 28, 30, 984800), datetime.datetime(2025, 4, 10, 2, 26, 38, 232300), datetime.datetime(2025, 4, 10, 2, 27, 52, 334100), datetime.datetime(2025, 4, 10, 2, 27, 55, 655100), datetime.datetime(2025, 4, 10, 2, 34, 34, 161600), datetime.datetime(2025, 4, 10, 2, 31, 47, 422800), datetime.datetime(2025, 4, 10, 2, 32, 15, 615300), datetime.datetime(2025, 4, 10, 2, 34, 25, 213800), datetime.datetime(2025, 4, 10, 2, 34, 50, 521900), datetime.datetime(2025, 4, 10, 2, 34, 49, 294300), datetime.datetime(2025, 4, 10, 2, 35, 11, 838600), datetime.datetime(2025, 4, 10, 2, 36, 4, 638200), datetime.datetime(2025, 4, 10, 2, 36, 28, 354100)]</t>
+        </is>
+      </c>
+      <c r="AE74" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>57</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>67f588a70bda8704ed309bb2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>D9OF87</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="n">
+        <v>45757.15140523139</v>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>diagnostic test</t>
+        </is>
+      </c>
+      <c r="AA75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 10, 2, 24, 23, 569000), datetime.datetime(2025, 4, 10, 2, 24, 56, 85600), datetime.datetime(2025, 4, 10, 2, 25, 6, 873300), datetime.datetime(2025, 4, 10, 2, 25, 18, 135100), datetime.datetime(2025, 4, 10, 2, 25, 54, 450800), datetime.datetime(2025, 4, 10, 2, 26, 47, 125000), datetime.datetime(2025, 4, 10, 2, 26, 46, 100900), datetime.datetime(2025, 4, 10, 2, 28, 19, 444500), datetime.datetime(2025, 4, 10, 2, 28, 2, 606400), datetime.datetime(2025, 4, 10, 2, 30, 15, 585300), datetime.datetime(2025, 4, 10, 2, 45, 49, 565000), datetime.datetime(2025, 4, 10, 2, 43, 13, 77400), datetime.datetime(2025, 4, 10, 2, 44, 15, 46700), datetime.datetime(2025, 4, 10, 2, 44, 6, 123600), datetime.datetime(2025, 4, 10, 2, 48, 51, 407300), datetime.datetime(2025, 4, 10, 2, 50, 1, 832900), datetime.datetime(2025, 4, 10, 2, 48, 28, 629500), datetime.datetime(2025, 4, 10, 2, 50, 21, 223200), datetime.datetime(2025, 4, 10, 2, 50, 20, 799000), datetime.datetime(2025, 4, 10, 2, 50, 58, 677100), datetime.datetime(2025, 4, 10, 2, 50, 58, 344600), datetime.datetime(2025, 4, 10, 2, 51, 24, 116900), datetime.datetime(2025, 4, 10, 2, 51, 25, 81800), datetime.datetime(2025, 4, 10, 2, 58, 40, 614100), datetime.datetime(2025, 4, 10, 2, 56, 21, 580800), datetime.datetime(2025, 4, 10, 2, 59, 40, 824600), datetime.datetime(2025, 4, 10, 3, 0, 42, 725400), datetime.datetime(2025, 4, 10, 3, 1, 34, 731800), datetime.datetime(2025, 4, 10, 3, 2, 38, 372200), datetime.datetime(2025, 4, 10, 3, 4, 7, 487600), datetime.datetime(2025, 4, 10, 3, 4, 16, 823800), datetime.datetime(2025, 4, 10, 3, 5, 43, 55000), datetime.datetime(2025, 4, 10, 3, 5, 59, 185200), datetime.datetime(2025, 4, 10, 3, 6, 44, 330100), datetime.datetime(2025, 4, 10, 3, 8, 2, 692900), datetime.datetime(2025, 4, 10, 3, 8, 15, 54700), datetime.datetime(2025, 4, 10, 3, 10, 23, 18900), datetime.datetime(2025, 4, 10, 3, 9, 56, 754400), datetime.datetime(2025, 4, 10, 3, 11, 31, 463900), datetime.datetime(2025, 4, 10, 3, 11, 6, 969200), datetime.datetime(2025, 4, 10, 3, 13, 32, 979000), datetime.datetime(2025, 4, 10, 3, 12, 56, 363900), datetime.datetime(2025, 4, 10, 3, 12, 53, 605800), datetime.datetime(2025, 4, 10, 3, 13, 20, 947000), datetime.datetime(2025, 4, 10, 3, 13, 25, 778200), datetime.datetime(2025, 4, 10, 3, 19, 46, 800300), datetime.datetime(2025, 4, 10, 3, 19, 46, 800300), datetime.datetime(2025, 4, 10, 3, 22, 17, 621900), datetime.datetime(2025, 4, 10, 3, 24, 5, 573500), datetime.datetime(2025, 4, 10, 3, 23, 51, 563900), datetime.datetime(2025, 4, 10, 3, 25, 42, 224200), datetime.datetime(2025, 4, 10, 3, 28, 3, 503100), datetime.datetime(2025, 4, 10, 3, 28, 25, 271000), datetime.datetime(2025, 4, 10, 3, 28, 21, 742800), datetime.datetime(2025, 4, 10, 3, 30, 55, 342500), datetime.datetime(2025, 4, 10, 3, 31, 10, 227500), datetime.datetime(2025, 4, 10, 3, 31, 30, 198800), datetime.datetime(2025, 4, 10, 3, 31, 34, 268500), datetime.datetime(2025, 4, 10, 3, 32, 55, 861700), datetime.datetime(2025, 4, 10, 3, 34, 35, 254300), datetime.datetime(2025, 4, 10, 3, 34, 26, 526100), datetime.datetime(2025, 4, 10, 3, 34, 40, 816000), datetime.datetime(2025, 4, 10, 3, 35, 19, 608200), datetime.datetime(2025, 4, 10, 3, 37, 24, 900300), datetime.datetime(2025, 4, 10, 3, 37, 19, 449300), datetime.datetime(2025, 4, 10, 3, 38, 20, 599700)]</t>
+        </is>
+      </c>
+      <c r="AE75" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>58</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>67f447e2165a120fa551a9de</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>M2XTJ8</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>post practice</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="n">
+        <v>45757.12125449545</v>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="AA76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>59</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>67f437b7797e833603cd854e</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>3FR07C</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>45</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>4</v>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="n">
+        <v>45757.15628823656</v>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA77" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 10, 2, 28, 20, 47200), datetime.datetime(2025, 4, 10, 2, 26, 42, 926900), datetime.datetime(2025, 4, 10, 2, 28, 32, 507900), datetime.datetime(2025, 4, 10, 2, 28, 54, 97100), datetime.datetime(2025, 4, 10, 2, 41, 15, 772200), datetime.datetime(2025, 4, 10, 2, 35, 26, 81400), datetime.datetime(2025, 4, 10, 2, 36, 42, 336000), datetime.datetime(2025, 4, 10, 2, 36, 46, 890800), datetime.datetime(2025, 4, 10, 2, 37, 45, 999900), datetime.datetime(2025, 4, 10, 2, 37, 46, 846000), datetime.datetime(2025, 4, 10, 2, 38, 9, 827000), datetime.datetime(2025, 4, 10, 2, 39, 4, 509700), datetime.datetime(2025, 4, 10, 2, 39, 15, 213100), datetime.datetime(2025, 4, 10, 2, 39, 42, 711400), datetime.datetime(2025, 4, 10, 2, 54, 27, 859200), datetime.datetime(2025, 4, 10, 2, 47, 43, 831500), datetime.datetime(2025, 4, 10, 2, 48, 25, 599600), datetime.datetime(2025, 4, 10, 2, 48, 38, 570700), datetime.datetime(2025, 4, 10, 2, 49, 32, 361300), datetime.datetime(2025, 4, 10, 2, 49, 21, 2400), datetime.datetime(2025, 4, 10, 2, 52, 17, 829000), datetime.datetime(2025, 4, 10, 2, 51, 23, 769700), datetime.datetime(2025, 4, 10, 2, 51, 46, 363800), datetime.datetime(2025, 4, 10, 2, 53, 14, 255300), datetime.datetime(2025, 4, 10, 2, 52, 41, 991900), datetime.datetime(2025, 4, 10, 2, 53, 0, 912700), datetime.datetime(2025, 4, 10, 2, 55, 22, 299900), datetime.datetime(2025, 4, 10, 2, 54, 50, 399000), datetime.datetime(2025, 4, 10, 2, 58, 55, 526900), datetime.datetime(2025, 4, 10, 2, 57, 24, 650600), datetime.datetime(2025, 4, 10, 2, 57, 36, 145800), datetime.datetime(2025, 4, 10, 2, 57, 44, 784900), datetime.datetime(2025, 4, 10, 2, 57, 59, 364600), datetime.datetime(2025, 4, 10, 2, 58, 16, 764700), datetime.datetime(2025, 4, 10, 2, 59, 21, 830000), datetime.datetime(2025, 4, 10, 2, 59, 21, 200800), datetime.datetime(2025, 4, 10, 2, 59, 38, 194700), datetime.datetime(2025, 4, 10, 3, 0, 1, 163200), datetime.datetime(2025, 4, 10, 3, 13, 53, 819500), datetime.datetime(2025, 4, 10, 3, 7, 23, 134000), datetime.datetime(2025, 4, 10, 3, 7, 34, 743100), datetime.datetime(2025, 4, 10, 3, 10, 30, 605000), datetime.datetime(2025, 4, 10, 3, 9, 28, 612100), datetime.datetime(2025, 4, 10, 3, 11, 39, 288000), datetime.datetime(2025, 4, 10, 3, 10, 57, 262900), datetime.datetime(2025, 4, 10, 3, 13, 30, 688400), datetime.datetime(2025, 4, 10, 3, 12, 38, 866000), datetime.datetime(2025, 4, 10, 3, 12, 49, 884100), datetime.datetime(2025, 4, 10, 3, 13, 20, 604800), datetime.datetime(2025, 4, 10, 3, 13, 37, 505100), datetime.datetime(2025, 4, 10, 3, 16, 25, 17800), datetime.datetime(2025, 4, 10, 3, 16, 25, 17800), datetime.datetime(2025, 4, 10, 3, 25, 35, 890200), datetime.datetime(2025, 4, 10, 3, 21, 44, 390700), datetime.datetime(2025, 4, 10, 3, 22, 24, 573900), datetime.datetime(2025, 4, 10, 3, 28, 43, 470800), datetime.datetime(2025, 4, 10, 3, 25, 54, 701900), datetime.datetime(2025, 4, 10, 3, 26, 33, 778300), datetime.datetime(2025, 4, 10, 3, 26, 43, 787000), datetime.datetime(2025, 4, 10, 3, 31, 4, 661600), datetime.datetime(2025, 4, 10, 3, 29, 22, 140700), datetime.datetime(2025, 4, 10, 3, 30, 8, 15700), datetime.datetime(2025, 4, 10, 3, 30, 21, 313900), datetime.datetime(2025, 4, 10, 3, 30, 59, 439400), datetime.datetime(2025, 4, 10, 3, 35, 41, 971000), datetime.datetime(2025, 4, 10, 3, 33, 47, 860600), datetime.datetime(2025, 4, 10, 3, 34, 31, 696200), datetime.datetime(2025, 4, 10, 3, 34, 27, 435500), datetime.datetime(2025, 4, 10, 3, 35, 28, 7100), datetime.datetime(2025, 4, 10, 3, 36, 5, 305000), datetime.datetime(2025, 4, 10, 3, 36, 45, 505700), datetime.datetime(2025, 4, 10, 3, 38, 33, 954400), datetime.datetime(2025, 4, 10, 3, 38, 2, 296400), datetime.datetime(2025, 4, 10, 3, 39, 53, 748300), datetime.datetime(2025, 4, 10, 3, 39, 27, 166800), datetime.datetime(2025, 4, 10, 3, 40, 13, 236500), datetime.datetime(2025, 4, 10, 3, 40, 48, 559100), datetime.datetime(2025, 4, 10, 3, 41, 30, 481500), datetime.datetime(2025, 4, 10, 3, 41, 50, 870700), datetime.datetime(2025, 4, 10, 3, 42, 24, 662100), datetime.datetime(2025, 4, 10, 3, 42, 21, 445500), datetime.datetime(2025, 4, 10, 3, 42, 37, 933700), datetime.datetime(2025, 4, 10, 3, 43, 13, 938100), datetime.datetime(2025, 4, 10, 3, 43, 30, 741700), datetime.datetime(2025, 4, 10, 3, 44, 53, 581100)]</t>
+        </is>
+      </c>
+      <c r="AE77" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>58</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>67ceb35b4792192fccbb19c9</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>SOTJJ9</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>removed_due_to_inactivity</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="n">
+        <v>45757.15335900303</v>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="AA78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 10, 2, 29, 51, 677600), datetime.datetime(2025, 4, 10, 2, 29, 31, 281800), datetime.datetime(2025, 4, 10, 2, 30, 7, 282900), datetime.datetime(2025, 4, 10, 2, 32, 14, 519900), datetime.datetime(2025, 4, 10, 2, 36, 28, 193500), datetime.datetime(2025, 4, 10, 2, 35, 3, 700000), datetime.datetime(2025, 4, 10, 2, 36, 17, 582000), datetime.datetime(2025, 4, 10, 2, 36, 33, 658300), datetime.datetime(2025, 4, 10, 2, 37, 7, 865900), datetime.datetime(2025, 4, 10, 2, 41, 59, 866700), datetime.datetime(2025, 4, 10, 2, 40, 24, 497400), datetime.datetime(2025, 4, 10, 2, 40, 41, 846800), datetime.datetime(2025, 4, 10, 2, 41, 7, 304000), datetime.datetime(2025, 4, 10, 2, 48, 8, 307700), datetime.datetime(2025, 4, 10, 2, 44, 57, 650200), datetime.datetime(2025, 4, 10, 2, 45, 38, 609100), datetime.datetime(2025, 4, 10, 2, 45, 51, 348400), datetime.datetime(2025, 4, 10, 2, 51, 7, 998800), datetime.datetime(2025, 4, 10, 2, 49, 0, 241500), datetime.datetime(2025, 4, 10, 2, 49, 13, 571100), datetime.datetime(2025, 4, 10, 2, 49, 41, 790800), datetime.datetime(2025, 4, 10, 2, 50, 2, 3000), datetime.datetime(2025, 4, 10, 2, 54, 23, 415200), datetime.datetime(2025, 4, 10, 2, 52, 49, 153000), datetime.datetime(2025, 4, 10, 2, 54, 59, 644800), datetime.datetime(2025, 4, 10, 2, 54, 27, 111100), datetime.datetime(2025, 4, 10, 2, 54, 55, 313000), datetime.datetime(2025, 4, 10, 2, 55, 15, 303300), datetime.datetime(2025, 4, 10, 2, 55, 26, 371100), datetime.datetime(2025, 4, 10, 2, 55, 44, 271700), datetime.datetime(2025, 4, 10, 3, 11, 44, 658600), datetime.datetime(2025, 4, 10, 3, 4, 14, 18800), datetime.datetime(2025, 4, 10, 3, 4, 35, 716500), datetime.datetime(2025, 4, 10, 3, 9, 51, 640900), datetime.datetime(2025, 4, 10, 3, 7, 37, 630700), datetime.datetime(2025, 4, 10, 3, 7, 51, 961500), datetime.datetime(2025, 4, 10, 3, 8, 15, 338400), datetime.datetime(2025, 4, 10, 3, 8, 56, 208500), datetime.datetime(2025, 4, 10, 3, 11, 36, 424300), datetime.datetime(2025, 4, 10, 3, 11, 36, 424300), datetime.datetime(2025, 4, 10, 4, 6, 20, 546600), datetime.datetime(2025, 4, 10, 4, 6, 20, 546600)]</t>
+        </is>
+      </c>
+      <c r="AE78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>59</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>at-sb</t>
         </is>
       </c>
     </row>

--- a/simple_game_test/filtered_users.xlsx
+++ b/simple_game_test/filtered_users.xlsx
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -3736,16 +3736,8 @@
           <t>34</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>joint_belief</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>sb-at</t>
-        </is>
-      </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3845,16 +3837,8 @@
           <t>34</t>
         </is>
       </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>joint_belief</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>sb-at</t>
-        </is>
-      </c>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4347,16 +4331,8 @@
           <t>45</t>
         </is>
       </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>individual_belief_high</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>at-sb</t>
-        </is>
-      </c>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4464,7 +4440,7 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -4593,7 +4569,7 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -4722,7 +4698,7 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -5291,7 +5267,7 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -5406,7 +5382,7 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5513,16 +5489,8 @@
           <t>48</t>
         </is>
       </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>joint_belief</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>sb-at</t>
-        </is>
-      </c>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5630,7 +5598,7 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -6702,7 +6670,7 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -6831,7 +6799,7 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -7041,7 +7009,7 @@
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -7170,7 +7138,7 @@
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -7414,7 +7382,7 @@
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -7543,7 +7511,7 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
@@ -7658,7 +7626,7 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
@@ -8501,16 +8469,8 @@
           <t>56</t>
         </is>
       </c>
-      <c r="AL68" t="inlineStr">
-        <is>
-          <t>joint_belief</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>sb-at</t>
-        </is>
-      </c>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8610,16 +8570,8 @@
           <t>60</t>
         </is>
       </c>
-      <c r="AL69" t="inlineStr">
-        <is>
-          <t>joint_belief</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>sb-at</t>
-        </is>
-      </c>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8727,7 +8679,7 @@
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -8856,7 +8808,7 @@
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -9100,7 +9052,7 @@
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -9215,7 +9167,7 @@
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
@@ -9330,7 +9282,7 @@
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -9574,7 +9526,7 @@
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">

--- a/simple_game_test/filtered_users.xlsx
+++ b/simple_game_test/filtered_users.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM78"/>
+  <dimension ref="A1:AM101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9650,6 +9650,2515 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>673c8683b1c8a4c8a79d02d8</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>10OYIR</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>sandbox_2</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="n">
+        <v>45763.80001119861</v>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>634d7250a9dbe47b2b1d110f</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>T8C3N0</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>domain_1</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="n">
+        <v>45763.80200236606</v>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>diagnostic feedback</t>
+        </is>
+      </c>
+      <c r="AA80" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 16, 19, 38, 37, 467100), datetime.datetime(2025, 4, 16, 19, 38, 11, 272200), datetime.datetime(2025, 4, 16, 19, 38, 20, 180800), datetime.datetime(2025, 4, 16, 19, 38, 37, 514700), datetime.datetime(2025, 4, 16, 19, 38, 57, 895400)]</t>
+        </is>
+      </c>
+      <c r="AE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>78</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>67ff7d17df0e7d9724518538</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>QSQZU0</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>domain_1</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="n">
+        <v>45763.81152367481</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>diagnostic test</t>
+        </is>
+      </c>
+      <c r="AA81" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 16, 19, 43, 24, 856900), datetime.datetime(2025, 4, 16, 19, 42, 27, 773100), datetime.datetime(2025, 4, 16, 19, 43, 21, 793800), datetime.datetime(2025, 4, 16, 19, 43, 33, 192800)]</t>
+        </is>
+      </c>
+      <c r="AE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>78</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>67e4f246f492b6719c066a0c</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>NMYFRJ</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>domain_1</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="n">
+        <v>45763.81498643304</v>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="AA82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>78</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>67f585364b27a832a4e25ab0</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>XK2YNW</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>domain_1</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="n">
+        <v>45763.81612519736</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>diagnostic feedback</t>
+        </is>
+      </c>
+      <c r="AA83" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 16, 19, 57, 10, 188500), datetime.datetime(2025, 4, 16, 19, 55, 34, 206700), datetime.datetime(2025, 4, 16, 19, 56, 45, 150800), datetime.datetime(2025, 4, 16, 19, 56, 51, 555900)]</t>
+        </is>
+      </c>
+      <c r="AE83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>79</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5de434b622383642a58d86a2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>V5I1GF</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>domain_1</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="n">
+        <v>45764.01016859274</v>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>diagnostic feedback</t>
+        </is>
+      </c>
+      <c r="AA84" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 0, 31, 43, 299400), datetime.datetime(2025, 4, 17, 0, 31, 16, 223000), datetime.datetime(2025, 4, 17, 0, 32, 4, 930900), datetime.datetime(2025, 4, 17, 0, 33, 38, 870600), datetime.datetime(2025, 4, 17, 0, 33, 28, 851200), datetime.datetime(2025, 4, 17, 0, 35, 43, 211500)]</t>
+        </is>
+      </c>
+      <c r="AE84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>86</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>62b354926116305375200028</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>VER231</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="n">
+        <v>45764.03702031422</v>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>diagnostic feedback</t>
+        </is>
+      </c>
+      <c r="AA85" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 0, 30, 48, 616300), datetime.datetime(2025, 4, 17, 0, 30, 21, 371600), datetime.datetime(2025, 4, 17, 0, 30, 18, 621000), datetime.datetime(2025, 4, 17, 0, 30, 48, 56900), datetime.datetime(2025, 4, 17, 0, 31, 20, 732200), datetime.datetime(2025, 4, 17, 0, 31, 30, 990800), datetime.datetime(2025, 4, 17, 0, 31, 46, 343800), datetime.datetime(2025, 4, 17, 0, 31, 56, 695100), datetime.datetime(2025, 4, 17, 0, 32, 3, 407300), datetime.datetime(2025, 4, 17, 0, 32, 26, 724800), datetime.datetime(2025, 4, 17, 0, 32, 26, 724800), datetime.datetime(2025, 4, 17, 0, 32, 26, 724800), datetime.datetime(2025, 4, 17, 0, 32, 26, 724800)]</t>
+        </is>
+      </c>
+      <c r="AE85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>86</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>67f5a6a3215b47356e0afded</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>04GGWE</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="n">
+        <v>38</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>5</v>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>the game requires full attention</t>
+        </is>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="n">
+        <v>45764.1171745465</v>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA86" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 1, 12, 11, 808300), datetime.datetime(2025, 4, 17, 1, 10, 29, 447200), datetime.datetime(2025, 4, 17, 1, 12, 0, 589700), datetime.datetime(2025, 4, 17, 1, 12, 39, 242400), datetime.datetime(2025, 4, 17, 1, 13, 27, 18000), datetime.datetime(2025, 4, 17, 1, 13, 20, 359200), datetime.datetime(2025, 4, 17, 1, 14, 5, 401300), datetime.datetime(2025, 4, 17, 1, 14, 18, 935500), datetime.datetime(2025, 4, 17, 1, 15, 15, 554000), datetime.datetime(2025, 4, 17, 1, 15, 21, 318500), datetime.datetime(2025, 4, 17, 1, 20, 54, 965600), datetime.datetime(2025, 4, 17, 1, 18, 56, 150900), datetime.datetime(2025, 4, 17, 1, 19, 35, 869200), datetime.datetime(2025, 4, 17, 1, 19, 42, 180800), datetime.datetime(2025, 4, 17, 1, 20, 5, 749100), datetime.datetime(2025, 4, 17, 1, 20, 19, 863000), datetime.datetime(2025, 4, 17, 1, 23, 43, 577000), datetime.datetime(2025, 4, 17, 1, 22, 42, 793400), datetime.datetime(2025, 4, 17, 1, 23, 28, 237100), datetime.datetime(2025, 4, 17, 1, 23, 20, 543000), datetime.datetime(2025, 4, 17, 1, 24, 34, 593300), datetime.datetime(2025, 4, 17, 1, 24, 23, 172800), datetime.datetime(2025, 4, 17, 1, 25, 26, 916400), datetime.datetime(2025, 4, 17, 1, 25, 8, 273400), datetime.datetime(2025, 4, 17, 1, 26, 17, 725900), datetime.datetime(2025, 4, 17, 1, 26, 7, 290200), datetime.datetime(2025, 4, 17, 1, 26, 24, 369700), datetime.datetime(2025, 4, 17, 1, 26, 33, 187400), datetime.datetime(2025, 4, 17, 1, 38, 46, 36900), datetime.datetime(2025, 4, 17, 1, 33, 2, 325400), datetime.datetime(2025, 4, 17, 1, 33, 43, 981000), datetime.datetime(2025, 4, 17, 1, 33, 42, 453500), datetime.datetime(2025, 4, 17, 1, 34, 13, 346100), datetime.datetime(2025, 4, 17, 1, 36, 13, 208200), datetime.datetime(2025, 4, 17, 1, 35, 36, 90100), datetime.datetime(2025, 4, 17, 1, 36, 5, 463800), datetime.datetime(2025, 4, 17, 1, 36, 17, 945400), datetime.datetime(2025, 4, 17, 1, 45, 42, 335300), datetime.datetime(2025, 4, 17, 1, 42, 12, 329800), datetime.datetime(2025, 4, 17, 1, 42, 47, 23300), datetime.datetime(2025, 4, 17, 1, 43, 0, 160400), datetime.datetime(2025, 4, 17, 1, 42, 57, 299900), datetime.datetime(2025, 4, 17, 1, 50, 30, 599600), datetime.datetime(2025, 4, 17, 1, 47, 15, 770800), datetime.datetime(2025, 4, 17, 1, 50, 21, 997700), datetime.datetime(2025, 4, 17, 1, 49, 14, 883100), datetime.datetime(2025, 4, 17, 1, 49, 31, 436700), datetime.datetime(2025, 4, 17, 1, 49, 42, 836600), datetime.datetime(2025, 4, 17, 1, 49, 58, 466600), datetime.datetime(2025, 4, 17, 1, 52, 27, 439000), datetime.datetime(2025, 4, 17, 1, 52, 27, 439000), datetime.datetime(2025, 4, 17, 2, 2, 27, 137600), datetime.datetime(2025, 4, 17, 1, 59, 31, 924100), datetime.datetime(2025, 4, 17, 1, 59, 58, 416600), datetime.datetime(2025, 4, 17, 2, 0, 12, 466700), datetime.datetime(2025, 4, 17, 2, 0, 38, 846200), datetime.datetime(2025, 4, 17, 2, 6, 25, 266500), datetime.datetime(2025, 4, 17, 2, 3, 57, 760200), datetime.datetime(2025, 4, 17, 2, 4, 3, 996600), datetime.datetime(2025, 4, 17, 2, 4, 26, 189000), datetime.datetime(2025, 4, 17, 2, 4, 50, 217600), datetime.datetime(2025, 4, 17, 2, 7, 38, 439600), datetime.datetime(2025, 4, 17, 2, 6, 36, 930000), datetime.datetime(2025, 4, 17, 2, 6, 53, 534400), datetime.datetime(2025, 4, 17, 2, 7, 3, 9400), datetime.datetime(2025, 4, 17, 2, 7, 19, 880800), datetime.datetime(2025, 4, 17, 2, 14, 47, 371200), datetime.datetime(2025, 4, 17, 2, 12, 4, 928900), datetime.datetime(2025, 4, 17, 2, 12, 14, 214700), datetime.datetime(2025, 4, 17, 2, 13, 26, 63300), datetime.datetime(2025, 4, 17, 2, 13, 4, 599300), datetime.datetime(2025, 4, 17, 2, 13, 59, 85700), datetime.datetime(2025, 4, 17, 2, 13, 59, 604600), datetime.datetime(2025, 4, 17, 2, 18, 32, 37200), datetime.datetime(2025, 4, 17, 2, 16, 53, 762300), datetime.datetime(2025, 4, 17, 2, 17, 18, 908500), datetime.datetime(2025, 4, 17, 2, 17, 31, 611700), datetime.datetime(2025, 4, 17, 2, 17, 54, 85000), datetime.datetime(2025, 4, 17, 2, 17, 56, 150800), datetime.datetime(2025, 4, 17, 2, 18, 14, 90900), datetime.datetime(2025, 4, 17, 2, 18, 32, 155100), datetime.datetime(2025, 4, 17, 2, 18, 48, 365100), datetime.datetime(2025, 4, 17, 2, 19, 39, 815500), datetime.datetime(2025, 4, 17, 2, 19, 27, 332900), datetime.datetime(2025, 4, 17, 2, 26, 4, 602700), datetime.datetime(2025, 4, 17, 2, 23, 25, 987500), datetime.datetime(2025, 4, 17, 2, 23, 35, 582700), datetime.datetime(2025, 4, 17, 2, 23, 52, 495000), datetime.datetime(2025, 4, 17, 2, 23, 59, 600700), datetime.datetime(2025, 4, 17, 2, 24, 11, 170900), datetime.datetime(2025, 4, 17, 2, 24, 28, 263700), datetime.datetime(2025, 4, 17, 2, 24, 39, 873900), datetime.datetime(2025, 4, 17, 2, 25, 7, 140500), datetime.datetime(2025, 4, 17, 2, 25, 6, 494600), datetime.datetime(2025, 4, 17, 2, 25, 28, 326300), datetime.datetime(2025, 4, 17, 2, 31, 39, 943400), datetime.datetime(2025, 4, 17, 2, 28, 55, 337200), datetime.datetime(2025, 4, 17, 2, 29, 5, 295200), datetime.datetime(2025, 4, 17, 2, 29, 35, 447100), datetime.datetime(2025, 4, 17, 2, 29, 59, 570300), datetime.datetime(2025, 4, 17, 2, 30, 4, 372100), datetime.datetime(2025, 4, 17, 2, 30, 43, 636400), datetime.datetime(2025, 4, 17, 2, 30, 48, 649100), datetime.datetime(2025, 4, 17, 2, 31, 3, 867800), datetime.datetime(2025, 4, 17, 2, 40, 40, 425400), datetime.datetime(2025, 4, 17, 2, 36, 18, 225500), datetime.datetime(2025, 4, 17, 2, 36, 32, 33300), datetime.datetime(2025, 4, 17, 2, 36, 48, 804100), datetime.datetime(2025, 4, 17, 2, 37, 10, 61800), datetime.datetime(2025, 4, 17, 2, 37, 23, 828800), datetime.datetime(2025, 4, 17, 2, 37, 31, 376000), datetime.datetime(2025, 4, 17, 2, 37, 48, 400), datetime.datetime(2025, 4, 17, 2, 38, 9, 676100), datetime.datetime(2025, 4, 17, 2, 39, 3, 530900), datetime.datetime(2025, 4, 17, 2, 38, 53, 86600), datetime.datetime(2025, 4, 17, 2, 42, 40, 706300), datetime.datetime(2025, 4, 17, 2, 41, 18, 823700), datetime.datetime(2025, 4, 17, 2, 41, 22, 504800), datetime.datetime(2025, 4, 17, 2, 41, 45, 706900), datetime.datetime(2025, 4, 17, 2, 42, 1, 111700), datetime.datetime(2025, 4, 17, 2, 43, 16, 364400)]</t>
+        </is>
+      </c>
+      <c r="AE86" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>87</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>67fa59acbd52188eee1c3be0</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>4S9DRF</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>domain_1</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="n">
+        <v>45764.01852973425</v>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>diagnostic feedback</t>
+        </is>
+      </c>
+      <c r="AA87" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 0, 31, 4, 57900), datetime.datetime(2025, 4, 17, 0, 30, 28, 948300), datetime.datetime(2025, 4, 17, 0, 31, 19, 747800), datetime.datetime(2025, 4, 17, 0, 32, 10, 817900), datetime.datetime(2025, 4, 17, 0, 32, 37, 720700)]</t>
+        </is>
+      </c>
+      <c r="AE87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>86</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ87" t="inlineStr"/>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>67f51164ef33ac5cd77e3191</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>LNJUSH</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>sandbox_2</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="n">
+        <v>45764.0211531686</v>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>67ef0684a2f656a31c042fbb</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2YJ7FC</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="n">
+        <v>45764.02171330118</v>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr"/>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>60b96835d5cbb2261c7fd22c</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>XGI9X3</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>removed_due_to_inactivity</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="n">
+        <v>45764.05842079555</v>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="AA90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 1, 8, 56, 355300), datetime.datetime(2025, 4, 17, 1, 7, 52, 340300), datetime.datetime(2025, 4, 17, 1, 8, 51, 281900), datetime.datetime(2025, 4, 17, 1, 9, 12, 244100), datetime.datetime(2025, 4, 17, 1, 18, 36, 677500), datetime.datetime(2025, 4, 17, 1, 14, 45, 5000), datetime.datetime(2025, 4, 17, 1, 16, 11, 909800), datetime.datetime(2025, 4, 17, 1, 16, 24, 817100), datetime.datetime(2025, 4, 17, 1, 17, 25, 322600), datetime.datetime(2025, 4, 17, 1, 18, 56, 240200), datetime.datetime(2025, 4, 17, 1, 18, 47, 950700), datetime.datetime(2025, 4, 17, 1, 20, 19, 320600), datetime.datetime(2025, 4, 17, 1, 20, 3, 535100), datetime.datetime(2025, 4, 17, 1, 20, 48, 366400), datetime.datetime(2025, 4, 17, 1, 24, 0, 407300), datetime.datetime(2025, 4, 17, 1, 24, 0, 407300)]</t>
+        </is>
+      </c>
+      <c r="AE90" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>87</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr"/>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>67fb593695667474dd6d2b89</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>HKTQ0H</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="n">
+        <v>45764.05294403684</v>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr"/>
+      <c r="AK91" t="inlineStr"/>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>67fe179372649a73a391369d</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>KJZ54V</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>25</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>4</v>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="n">
+        <v>45764.09927296991</v>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA92" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'ArrowRight', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 1, 43, 43, 702100), datetime.datetime(2025, 4, 17, 1, 43, 17, 223700), datetime.datetime(2025, 4, 17, 1, 45, 5, 202900), datetime.datetime(2025, 4, 17, 1, 44, 41, 842400), datetime.datetime(2025, 4, 17, 1, 44, 50, 266900), datetime.datetime(2025, 4, 17, 1, 45, 11, 509700), datetime.datetime(2025, 4, 17, 1, 45, 45, 783400), datetime.datetime(2025, 4, 17, 1, 45, 42, 781700), datetime.datetime(2025, 4, 17, 1, 46, 23, 115400), datetime.datetime(2025, 4, 17, 1, 46, 21, 859700), datetime.datetime(2025, 4, 17, 1, 46, 29, 134000), datetime.datetime(2025, 4, 17, 1, 52, 38, 165100), datetime.datetime(2025, 4, 17, 1, 50, 8, 853200), datetime.datetime(2025, 4, 17, 1, 50, 46, 717600), datetime.datetime(2025, 4, 17, 1, 51, 4, 93700), datetime.datetime(2025, 4, 17, 1, 51, 30, 109300), datetime.datetime(2025, 4, 17, 1, 51, 23, 395400), datetime.datetime(2025, 4, 17, 1, 51, 38, 857500), datetime.datetime(2025, 4, 17, 1, 51, 56, 315900), datetime.datetime(2025, 4, 17, 1, 52, 10, 860700), datetime.datetime(2025, 4, 17, 1, 52, 22, 728300), datetime.datetime(2025, 4, 17, 1, 56, 4, 719700), datetime.datetime(2025, 4, 17, 1, 54, 24, 883100), datetime.datetime(2025, 4, 17, 1, 55, 21, 698700), datetime.datetime(2025, 4, 17, 1, 55, 12, 86700), datetime.datetime(2025, 4, 17, 1, 55, 21, 827000), datetime.datetime(2025, 4, 17, 1, 55, 48, 688200), datetime.datetime(2025, 4, 17, 1, 56, 34, 618200), datetime.datetime(2025, 4, 17, 1, 56, 27, 255100), datetime.datetime(2025, 4, 17, 1, 56, 45, 146300), datetime.datetime(2025, 4, 17, 1, 57, 9, 854600), datetime.datetime(2025, 4, 17, 1, 57, 11, 893400), datetime.datetime(2025, 4, 17, 1, 58, 7, 426400), datetime.datetime(2025, 4, 17, 1, 58, 13, 164700), datetime.datetime(2025, 4, 17, 1, 58, 22, 446100), datetime.datetime(2025, 4, 17, 1, 58, 30, 972900), datetime.datetime(2025, 4, 17, 1, 58, 54, 833200), datetime.datetime(2025, 4, 17, 1, 59, 53, 205800), datetime.datetime(2025, 4, 17, 1, 59, 37, 825800), datetime.datetime(2025, 4, 17, 1, 59, 55, 350400), datetime.datetime(2025, 4, 17, 2, 0, 0, 823700), datetime.datetime(2025, 4, 17, 2, 0, 8, 792300), datetime.datetime(2025, 4, 17, 2, 1, 57, 929300), datetime.datetime(2025, 4, 17, 2, 2, 12, 326300), datetime.datetime(2025, 4, 17, 2, 1, 59, 745800), datetime.datetime(2025, 4, 17, 2, 2, 20, 695000), datetime.datetime(2025, 4, 17, 2, 2, 24, 55800), datetime.datetime(2025, 4, 17, 2, 3, 15, 153200), datetime.datetime(2025, 4, 17, 2, 3, 42, 113000), datetime.datetime(2025, 4, 17, 2, 5, 51, 562700), datetime.datetime(2025, 4, 17, 2, 4, 53, 306200), datetime.datetime(2025, 4, 17, 2, 5, 2, 152300), datetime.datetime(2025, 4, 17, 2, 5, 21, 805100), datetime.datetime(2025, 4, 17, 2, 5, 46, 932500), datetime.datetime(2025, 4, 17, 2, 5, 58, 600), datetime.datetime(2025, 4, 17, 2, 6, 25, 891900), datetime.datetime(2025, 4, 17, 2, 7, 47, 432300), datetime.datetime(2025, 4, 17, 2, 7, 21, 95000), datetime.datetime(2025, 4, 17, 2, 7, 40, 165700), datetime.datetime(2025, 4, 17, 2, 7, 55, 590000), datetime.datetime(2025, 4, 17, 2, 8, 17, 358600), datetime.datetime(2025, 4, 17, 2, 8, 20, 454200), datetime.datetime(2025, 4, 17, 2, 8, 40, 76600), datetime.datetime(2025, 4, 17, 2, 9, 20, 501700), datetime.datetime(2025, 4, 17, 2, 9, 20, 943600), datetime.datetime(2025, 4, 17, 2, 9, 21, 870300), datetime.datetime(2025, 4, 17, 2, 9, 39, 549600), datetime.datetime(2025, 4, 17, 2, 10, 5, 199900), datetime.datetime(2025, 4, 17, 2, 10, 26, 235700), datetime.datetime(2025, 4, 17, 2, 11, 17, 502000), datetime.datetime(2025, 4, 17, 2, 11, 3, 392000), datetime.datetime(2025, 4, 17, 2, 11, 24, 630600), datetime.datetime(2025, 4, 17, 2, 11, 40, 703100), datetime.datetime(2025, 4, 17, 2, 11, 44, 629800), datetime.datetime(2025, 4, 17, 2, 14, 4, 69600), datetime.datetime(2025, 4, 17, 2, 14, 4, 69600), datetime.datetime(2025, 4, 17, 2, 18, 33, 600900), datetime.datetime(2025, 4, 17, 2, 16, 23, 848500), datetime.datetime(2025, 4, 17, 2, 17, 46, 34700), datetime.datetime(2025, 4, 17, 2, 17, 58, 958200), datetime.datetime(2025, 4, 17, 2, 17, 53, 685300), datetime.datetime(2025, 4, 17, 2, 18, 18, 506600), datetime.datetime(2025, 4, 17, 2, 18, 23, 777100), datetime.datetime(2025, 4, 17, 2, 19, 48, 774100), datetime.datetime(2025, 4, 17, 2, 19, 39, 415700), datetime.datetime(2025, 4, 17, 2, 20, 27, 525200), datetime.datetime(2025, 4, 17, 2, 20, 17, 675600), datetime.datetime(2025, 4, 17, 2, 20, 29, 917000), datetime.datetime(2025, 4, 17, 2, 21, 2, 215000), datetime.datetime(2025, 4, 17, 2, 21, 9, 977100), datetime.datetime(2025, 4, 17, 2, 22, 42, 132000)]</t>
+        </is>
+      </c>
+      <c r="AE92" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>88</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>67e9875c5b9b26c19a3bdf88</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>8XC1BI</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>51</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>6</v>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>domain_2</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="n">
+        <v>45764.04387980628</v>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA93" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB93" t="inlineStr"/>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', ' ', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'Control', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 1, 7, 24, 615800), datetime.datetime(2025, 4, 17, 1, 6, 54, 190400), datetime.datetime(2025, 4, 17, 1, 8, 1, 287600), datetime.datetime(2025, 4, 17, 1, 8, 54, 97900), datetime.datetime(2025, 4, 17, 1, 8, 54, 97900), datetime.datetime(2025, 4, 17, 1, 17, 24, 212200), datetime.datetime(2025, 4, 17, 1, 13, 35, 556400), datetime.datetime(2025, 4, 17, 1, 15, 51, 437600), datetime.datetime(2025, 4, 17, 1, 15, 25, 789700), datetime.datetime(2025, 4, 17, 1, 16, 2, 726400), datetime.datetime(2025, 4, 17, 1, 16, 2, 726400), datetime.datetime(2025, 4, 17, 1, 16, 2, 726400), datetime.datetime(2025, 4, 17, 1, 19, 12, 650800), datetime.datetime(2025, 4, 17, 1, 20, 3, 425300), datetime.datetime(2025, 4, 17, 1, 20, 19, 214900), datetime.datetime(2025, 4, 17, 1, 20, 26, 848700), datetime.datetime(2025, 4, 17, 1, 21, 14, 257300), datetime.datetime(2025, 4, 17, 1, 22, 18, 286400), datetime.datetime(2025, 4, 17, 1, 22, 15, 321000), datetime.datetime(2025, 4, 17, 1, 22, 43, 250600), datetime.datetime(2025, 4, 17, 1, 23, 7, 634900), datetime.datetime(2025, 4, 17, 1, 23, 30, 191500), datetime.datetime(2025, 4, 17, 1, 28, 33, 277700), datetime.datetime(2025, 4, 17, 1, 27, 11, 485900), datetime.datetime(2025, 4, 17, 1, 27, 11, 485900), datetime.datetime(2025, 4, 17, 1, 31, 57, 374100), datetime.datetime(2025, 4, 17, 1, 30, 51, 321800), datetime.datetime(2025, 4, 17, 1, 31, 22, 921600), datetime.datetime(2025, 4, 17, 1, 32, 14, 531900), datetime.datetime(2025, 4, 17, 1, 32, 20, 734600), datetime.datetime(2025, 4, 17, 1, 32, 20, 734600), datetime.datetime(2025, 4, 17, 1, 34, 6, 843700), datetime.datetime(2025, 4, 17, 1, 33, 58, 427600), datetime.datetime(2025, 4, 17, 1, 34, 33, 119600), datetime.datetime(2025, 4, 17, 1, 34, 30, 845100), datetime.datetime(2025, 4, 17, 1, 34, 30, 845100), datetime.datetime(2025, 4, 17, 1, 40, 11, 627900), datetime.datetime(2025, 4, 17, 1, 38, 32, 731200), datetime.datetime(2025, 4, 17, 1, 39, 16, 653500), datetime.datetime(2025, 4, 17, 1, 39, 32, 942300), datetime.datetime(2025, 4, 17, 1, 40, 15, 812200), datetime.datetime(2025, 4, 17, 1, 40, 58, 264200), datetime.datetime(2025, 4, 17, 1, 40, 58, 304900), datetime.datetime(2025, 4, 17, 1, 41, 25, 333900), datetime.datetime(2025, 4, 17, 1, 44, 15, 725300), datetime.datetime(2025, 4, 17, 1, 44, 15, 725300), datetime.datetime(2025, 4, 17, 1, 48, 46, 719900), datetime.datetime(2025, 4, 17, 1, 48, 5, 241400), datetime.datetime(2025, 4, 17, 1, 48, 32, 930400), datetime.datetime(2025, 4, 17, 1, 50, 26, 788900), datetime.datetime(2025, 4, 17, 1, 50, 8, 125600), datetime.datetime(2025, 4, 17, 1, 51, 32, 732100), datetime.datetime(2025, 4, 17, 1, 51, 40, 387500), datetime.datetime(2025, 4, 17, 1, 52, 23, 45200), datetime.datetime(2025, 4, 17, 2, 2, 47, 705500), datetime.datetime(2025, 4, 17, 2, 2, 47, 705500), datetime.datetime(2025, 4, 17, 1, 59, 32, 791700), datetime.datetime(2025, 4, 17, 2, 1, 8, 512000), datetime.datetime(2025, 4, 17, 2, 2, 10, 783400), datetime.datetime(2025, 4, 17, 2, 2, 39, 467300), datetime.datetime(2025, 4, 17, 2, 3, 25, 226500), datetime.datetime(2025, 4, 17, 2, 4, 17, 302100), datetime.datetime(2025, 4, 17, 2, 5, 28, 799800), datetime.datetime(2025, 4, 17, 2, 5, 10, 292300), datetime.datetime(2025, 4, 17, 2, 6, 17, 19100), datetime.datetime(2025, 4, 17, 2, 6, 25, 137200), datetime.datetime(2025, 4, 17, 2, 7, 30, 140600), datetime.datetime(2025, 4, 17, 2, 8, 40, 825300), datetime.datetime(2025, 4, 17, 2, 10, 7, 475300), datetime.datetime(2025, 4, 17, 2, 10, 42, 45900), datetime.datetime(2025, 4, 17, 2, 12, 10, 436600), datetime.datetime(2025, 4, 17, 2, 11, 48, 838400), datetime.datetime(2025, 4, 17, 2, 12, 23, 387600), datetime.datetime(2025, 4, 17, 2, 13, 22, 179900), datetime.datetime(2025, 4, 17, 2, 13, 32, 298100), datetime.datetime(2025, 4, 17, 2, 15, 32, 11800), datetime.datetime(2025, 4, 17, 2, 17, 51, 303200), datetime.datetime(2025, 4, 17, 2, 16, 42, 300), datetime.datetime(2025, 4, 17, 2, 16, 53, 990400), datetime.datetime(2025, 4, 17, 2, 17, 4, 387700), datetime.datetime(2025, 4, 17, 2, 17, 54, 419200), datetime.datetime(2025, 4, 17, 2, 18, 32, 745300), datetime.datetime(2025, 4, 17, 2, 20, 45, 274500), datetime.datetime(2025, 4, 17, 2, 21, 46, 276800), datetime.datetime(2025, 4, 17, 2, 21, 14, 495000), datetime.datetime(2025, 4, 17, 2, 22, 7, 759100), datetime.datetime(2025, 4, 17, 2, 22, 0, 82500), datetime.datetime(2025, 4, 17, 2, 23, 9, 16700), datetime.datetime(2025, 4, 17, 2, 24, 31, 368200), datetime.datetime(2025, 4, 17, 2, 24, 15, 478800), datetime.datetime(2025, 4, 17, 2, 25, 9, 689600), datetime.datetime(2025, 4, 17, 2, 25, 36, 779700), datetime.datetime(2025, 4, 17, 2, 26, 50, 422500), datetime.datetime(2025, 4, 17, 2, 26, 48, 425400), datetime.datetime(2025, 4, 17, 2, 26, 51, 385000), datetime.datetime(2025, 4, 17, 2, 27, 26, 812100), datetime.datetime(2025, 4, 17, 2, 28, 1, 139900), datetime.datetime(2025, 4, 17, 2, 28, 57, 354900), datetime.datetime(2025, 4, 17, 2, 28, 43, 141300), datetime.datetime(2025, 4, 17, 2, 28, 56, 207800), datetime.datetime(2025, 4, 17, 2, 29, 9, 118100), datetime.datetime(2025, 4, 17, 2, 29, 37, 427700), datetime.datetime(2025, 4, 17, 2, 33, 10, 735000), datetime.datetime(2025, 4, 17, 2, 32, 6, 719300), datetime.datetime(2025, 4, 17, 2, 34, 24, 295900), datetime.datetime(2025, 4, 17, 2, 34, 19, 725400), datetime.datetime(2025, 4, 17, 2, 34, 54, 793100), datetime.datetime(2025, 4, 17, 2, 35, 13, 566400), datetime.datetime(2025, 4, 17, 2, 36, 21, 711300), datetime.datetime(2025, 4, 17, 2, 37, 44, 207800), datetime.datetime(2025, 4, 17, 2, 37, 26, 767500), datetime.datetime(2025, 4, 17, 2, 37, 46, 257700), datetime.datetime(2025, 4, 17, 2, 38, 5, 798400), datetime.datetime(2025, 4, 17, 2, 38, 20, 81400), datetime.datetime(2025, 4, 17, 2, 38, 33, 210700), datetime.datetime(2025, 4, 17, 2, 39, 2, 500), datetime.datetime(2025, 4, 17, 2, 39, 18, 359800), datetime.datetime(2025, 4, 17, 2, 39, 42, 998300), datetime.datetime(2025, 4, 17, 2, 39, 50, 289500), datetime.datetime(2025, 4, 17, 2, 40, 30, 517400), datetime.datetime(2025, 4, 17, 2, 41, 14, 327000), datetime.datetime(2025, 4, 17, 2, 41, 15, 403500), datetime.datetime(2025, 4, 17, 2, 41, 33, 846900), datetime.datetime(2025, 4, 17, 2, 42, 12, 488100), datetime.datetime(2025, 4, 17, 2, 43, 15, 927300)]</t>
+        </is>
+      </c>
+      <c r="AE93" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>87</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ93" t="inlineStr"/>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>67f15c3a8fc8c9e4819d340d</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>1P0JMB</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="n">
+        <v>83</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>5</v>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="n">
+        <v>45764.09919267525</v>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA94" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 1, 34, 41, 761800), datetime.datetime(2025, 4, 17, 1, 34, 20, 651200), datetime.datetime(2025, 4, 17, 1, 34, 53, 877700), datetime.datetime(2025, 4, 17, 1, 35, 55, 631600), datetime.datetime(2025, 4, 17, 1, 36, 22, 96600), datetime.datetime(2025, 4, 17, 1, 55, 15, 574900), datetime.datetime(2025, 4, 17, 1, 46, 8, 468900), datetime.datetime(2025, 4, 17, 1, 46, 32, 935000), datetime.datetime(2025, 4, 17, 1, 47, 19, 933200), datetime.datetime(2025, 4, 17, 1, 47, 45, 738700), datetime.datetime(2025, 4, 17, 1, 48, 19, 576100), datetime.datetime(2025, 4, 17, 1, 48, 56, 967600), datetime.datetime(2025, 4, 17, 1, 49, 25, 471000), datetime.datetime(2025, 4, 17, 1, 50, 5, 72300), datetime.datetime(2025, 4, 17, 1, 50, 19, 250100), datetime.datetime(2025, 4, 17, 1, 52, 31, 609800), datetime.datetime(2025, 4, 17, 1, 52, 10, 930900), datetime.datetime(2025, 4, 17, 1, 53, 2, 766100), datetime.datetime(2025, 4, 17, 1, 53, 53, 145900), datetime.datetime(2025, 4, 17, 1, 53, 38, 881900), datetime.datetime(2025, 4, 17, 1, 54, 44, 223100), datetime.datetime(2025, 4, 17, 1, 54, 42, 395000), datetime.datetime(2025, 4, 17, 1, 55, 19, 657300), datetime.datetime(2025, 4, 17, 1, 55, 20, 753400), datetime.datetime(2025, 4, 17, 1, 57, 16, 908900), datetime.datetime(2025, 4, 17, 1, 56, 53, 814100), datetime.datetime(2025, 4, 17, 1, 57, 10, 281100), datetime.datetime(2025, 4, 17, 1, 57, 13, 815800), datetime.datetime(2025, 4, 17, 1, 58, 1, 145600), datetime.datetime(2025, 4, 17, 1, 58, 3, 963600), datetime.datetime(2025, 4, 17, 1, 58, 14, 294400), datetime.datetime(2025, 4, 17, 1, 59, 22, 11100), datetime.datetime(2025, 4, 17, 1, 59, 46, 404600), datetime.datetime(2025, 4, 17, 1, 59, 59, 44100), datetime.datetime(2025, 4, 17, 2, 0, 42, 256100), datetime.datetime(2025, 4, 17, 2, 0, 41, 49800), datetime.datetime(2025, 4, 17, 2, 1, 37, 271900), datetime.datetime(2025, 4, 17, 2, 1, 23, 542500), datetime.datetime(2025, 4, 17, 2, 2, 0, 247200), datetime.datetime(2025, 4, 17, 2, 2, 50, 285300), datetime.datetime(2025, 4, 17, 2, 2, 52, 303800), datetime.datetime(2025, 4, 17, 2, 3, 34, 442400), datetime.datetime(2025, 4, 17, 2, 3, 39, 534500), datetime.datetime(2025, 4, 17, 2, 3, 52, 766200), datetime.datetime(2025, 4, 17, 2, 5, 28, 569400), datetime.datetime(2025, 4, 17, 2, 4, 59, 246000), datetime.datetime(2025, 4, 17, 2, 5, 44, 273800), datetime.datetime(2025, 4, 17, 2, 5, 58, 865000), datetime.datetime(2025, 4, 17, 2, 6, 27, 879300), datetime.datetime(2025, 4, 17, 2, 6, 46, 615400), datetime.datetime(2025, 4, 17, 2, 7, 22, 330500), datetime.datetime(2025, 4, 17, 2, 7, 15, 871200), datetime.datetime(2025, 4, 17, 2, 7, 27, 494100), datetime.datetime(2025, 4, 17, 2, 7, 52, 182000), datetime.datetime(2025, 4, 17, 2, 8, 1, 728000), datetime.datetime(2025, 4, 17, 2, 8, 18, 96000), datetime.datetime(2025, 4, 17, 2, 9, 46, 412700), datetime.datetime(2025, 4, 17, 2, 9, 20, 285100), datetime.datetime(2025, 4, 17, 2, 9, 29, 19100), datetime.datetime(2025, 4, 17, 2, 9, 41, 537500), datetime.datetime(2025, 4, 17, 2, 10, 3, 24600), datetime.datetime(2025, 4, 17, 2, 10, 46, 153900), datetime.datetime(2025, 4, 17, 2, 11, 16, 33700), datetime.datetime(2025, 4, 17, 2, 11, 9, 975900), datetime.datetime(2025, 4, 17, 2, 11, 21, 893900), datetime.datetime(2025, 4, 17, 2, 11, 41, 265400), datetime.datetime(2025, 4, 17, 2, 11, 55, 93700), datetime.datetime(2025, 4, 17, 2, 13, 43, 302200), datetime.datetime(2025, 4, 17, 2, 13, 43, 302200), datetime.datetime(2025, 4, 17, 2, 15, 41, 525500), datetime.datetime(2025, 4, 17, 2, 15, 39, 170700), datetime.datetime(2025, 4, 17, 2, 16, 8, 31200), datetime.datetime(2025, 4, 17, 2, 19, 13, 211000), datetime.datetime(2025, 4, 17, 2, 17, 55, 313000), datetime.datetime(2025, 4, 17, 2, 18, 26, 827400), datetime.datetime(2025, 4, 17, 2, 18, 31, 667500), datetime.datetime(2025, 4, 17, 2, 19, 48, 473700), datetime.datetime(2025, 4, 17, 2, 19, 47, 531200), datetime.datetime(2025, 4, 17, 2, 20, 25, 784700), datetime.datetime(2025, 4, 17, 2, 20, 20, 436300), datetime.datetime(2025, 4, 17, 2, 20, 35, 162400), datetime.datetime(2025, 4, 17, 2, 20, 54, 833000), datetime.datetime(2025, 4, 17, 2, 21, 20, 377100), datetime.datetime(2025, 4, 17, 2, 22, 24, 143500)]</t>
+        </is>
+      </c>
+      <c r="AE94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>88</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>67fd0c0a107af6bb4266f8b1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>K6ZU5R</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>removed_due_to_inactivity</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="n">
+        <v>45764.0815857136</v>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>diagnostic test</t>
+        </is>
+      </c>
+      <c r="AA95" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'CapsLock']</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 1, 52, 10, 646300), datetime.datetime(2025, 4, 17, 1, 52, 2, 797600), datetime.datetime(2025, 4, 17, 1, 52, 57, 531100), datetime.datetime(2025, 4, 17, 1, 54, 24, 766100), datetime.datetime(2025, 4, 17, 1, 53, 57, 516500), datetime.datetime(2025, 4, 17, 1, 56, 38, 837900)]</t>
+        </is>
+      </c>
+      <c r="AE95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>89</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>67e459796c2c8859a302aa12</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>WPVPER</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>sandbox_2</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="n">
+        <v>45764.06014524739</v>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr"/>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr"/>
+      <c r="AL96" t="inlineStr"/>
+      <c r="AM96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>659e05126d0cca72846d4b06</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Y52Z3V</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>45</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>2</v>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>was interesting to do thanks</t>
+        </is>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="n">
+        <v>45764.1133683904</v>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA97" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 1, 51, 53, 853800), datetime.datetime(2025, 4, 17, 1, 51, 25, 803200), datetime.datetime(2025, 4, 17, 1, 52, 0, 358700), datetime.datetime(2025, 4, 17, 1, 54, 36, 708100), datetime.datetime(2025, 4, 17, 1, 53, 44, 117100), datetime.datetime(2025, 4, 17, 1, 54, 48, 939700), datetime.datetime(2025, 4, 17, 1, 54, 58, 958100), datetime.datetime(2025, 4, 17, 1, 55, 47, 436300), datetime.datetime(2025, 4, 17, 1, 55, 57, 435900), datetime.datetime(2025, 4, 17, 2, 0, 44, 107200), datetime.datetime(2025, 4, 17, 1, 58, 53, 2200), datetime.datetime(2025, 4, 17, 1, 59, 39, 469600), datetime.datetime(2025, 4, 17, 1, 59, 33, 784900), datetime.datetime(2025, 4, 17, 2, 0, 9, 334200), datetime.datetime(2025, 4, 17, 2, 2, 4, 468700), datetime.datetime(2025, 4, 17, 2, 3, 41, 985600), datetime.datetime(2025, 4, 17, 2, 3, 3, 173300), datetime.datetime(2025, 4, 17, 2, 3, 34, 732600), datetime.datetime(2025, 4, 17, 2, 3, 47, 103000), datetime.datetime(2025, 4, 17, 2, 4, 28, 181100), datetime.datetime(2025, 4, 17, 2, 4, 23, 196400), datetime.datetime(2025, 4, 17, 2, 4, 46, 751600), datetime.datetime(2025, 4, 17, 2, 5, 5, 106700), datetime.datetime(2025, 4, 17, 2, 5, 13, 751000), datetime.datetime(2025, 4, 17, 2, 6, 42, 438100), datetime.datetime(2025, 4, 17, 2, 6, 17, 763100), datetime.datetime(2025, 4, 17, 2, 6, 40, 302100), datetime.datetime(2025, 4, 17, 2, 6, 51, 920100), datetime.datetime(2025, 4, 17, 2, 9, 46, 233100), datetime.datetime(2025, 4, 17, 2, 8, 32, 621400), datetime.datetime(2025, 4, 17, 2, 9, 0, 451000), datetime.datetime(2025, 4, 17, 2, 9, 21, 468200), datetime.datetime(2025, 4, 17, 2, 10, 25, 125000), datetime.datetime(2025, 4, 17, 2, 10, 49, 531300), datetime.datetime(2025, 4, 17, 2, 10, 53, 714200), datetime.datetime(2025, 4, 17, 2, 12, 41, 434400), datetime.datetime(2025, 4, 17, 2, 12, 24, 572400), datetime.datetime(2025, 4, 17, 2, 12, 46, 167300), datetime.datetime(2025, 4, 17, 2, 12, 55, 849800), datetime.datetime(2025, 4, 17, 2, 13, 54, 631700), datetime.datetime(2025, 4, 17, 2, 14, 0, 567000), datetime.datetime(2025, 4, 17, 2, 14, 19, 882100), datetime.datetime(2025, 4, 17, 2, 15, 26, 215400), datetime.datetime(2025, 4, 17, 2, 16, 58, 868800), datetime.datetime(2025, 4, 17, 2, 16, 28, 502000), datetime.datetime(2025, 4, 17, 2, 17, 12, 929600), datetime.datetime(2025, 4, 17, 2, 17, 42, 331700), datetime.datetime(2025, 4, 17, 2, 17, 42, 413900), datetime.datetime(2025, 4, 17, 2, 17, 51, 666100), datetime.datetime(2025, 4, 17, 2, 18, 11, 265300), datetime.datetime(2025, 4, 17, 2, 18, 25, 258200), datetime.datetime(2025, 4, 17, 2, 19, 56, 81400), datetime.datetime(2025, 4, 17, 2, 19, 56, 81400), datetime.datetime(2025, 4, 17, 2, 21, 48, 331500), datetime.datetime(2025, 4, 17, 2, 21, 50, 346900), datetime.datetime(2025, 4, 17, 2, 22, 9, 529500), datetime.datetime(2025, 4, 17, 2, 22, 22, 467300), datetime.datetime(2025, 4, 17, 2, 22, 33, 214800), datetime.datetime(2025, 4, 17, 2, 24, 33, 333500), datetime.datetime(2025, 4, 17, 2, 24, 1, 83900), datetime.datetime(2025, 4, 17, 2, 24, 14, 483400), datetime.datetime(2025, 4, 17, 2, 24, 23, 535700), datetime.datetime(2025, 4, 17, 2, 25, 25, 111500), datetime.datetime(2025, 4, 17, 2, 25, 46, 625500), datetime.datetime(2025, 4, 17, 2, 25, 53, 993000), datetime.datetime(2025, 4, 17, 2, 26, 9, 562400), datetime.datetime(2025, 4, 17, 2, 26, 53, 831300), datetime.datetime(2025, 4, 17, 2, 27, 0, 327400), datetime.datetime(2025, 4, 17, 2, 27, 21, 917100), datetime.datetime(2025, 4, 17, 2, 27, 26, 593200), datetime.datetime(2025, 4, 17, 2, 29, 20, 449000), datetime.datetime(2025, 4, 17, 2, 28, 45, 231000), datetime.datetime(2025, 4, 17, 2, 29, 36, 96700), datetime.datetime(2025, 4, 17, 2, 29, 43, 727800), datetime.datetime(2025, 4, 17, 2, 30, 16, 399000), datetime.datetime(2025, 4, 17, 2, 31, 5, 597700), datetime.datetime(2025, 4, 17, 2, 30, 56, 715200), datetime.datetime(2025, 4, 17, 2, 31, 33, 395100), datetime.datetime(2025, 4, 17, 2, 32, 2, 429700), datetime.datetime(2025, 4, 17, 2, 33, 7, 414600), datetime.datetime(2025, 4, 17, 2, 33, 35, 178400), datetime.datetime(2025, 4, 17, 2, 33, 32, 700400), datetime.datetime(2025, 4, 17, 2, 33, 54, 268400), datetime.datetime(2025, 4, 17, 2, 34, 10, 48900), datetime.datetime(2025, 4, 17, 2, 34, 46, 62100), datetime.datetime(2025, 4, 17, 2, 34, 47, 101300), datetime.datetime(2025, 4, 17, 2, 36, 26, 995700), datetime.datetime(2025, 4, 17, 2, 35, 49, 564300), datetime.datetime(2025, 4, 17, 2, 36, 1, 793600), datetime.datetime(2025, 4, 17, 2, 36, 18, 411700), datetime.datetime(2025, 4, 17, 2, 37, 8, 207400), datetime.datetime(2025, 4, 17, 2, 37, 16, 443200), datetime.datetime(2025, 4, 17, 2, 37, 34, 94100), datetime.datetime(2025, 4, 17, 2, 37, 42, 242100), datetime.datetime(2025, 4, 17, 2, 39, 21, 810000), datetime.datetime(2025, 4, 17, 2, 39, 5, 592200), datetime.datetime(2025, 4, 17, 2, 39, 17, 655900), datetime.datetime(2025, 4, 17, 2, 39, 29, 809500), datetime.datetime(2025, 4, 17, 2, 39, 38, 424300), datetime.datetime(2025, 4, 17, 2, 39, 52, 192700), datetime.datetime(2025, 4, 17, 2, 40, 23, 292000), datetime.datetime(2025, 4, 17, 2, 41, 1, 407600), datetime.datetime(2025, 4, 17, 2, 40, 46, 308100), datetime.datetime(2025, 4, 17, 2, 40, 56, 446200), datetime.datetime(2025, 4, 17, 2, 41, 15, 211200), datetime.datetime(2025, 4, 17, 2, 41, 54, 739500), datetime.datetime(2025, 4, 17, 2, 42, 48, 805900)]</t>
+        </is>
+      </c>
+      <c r="AE97" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>89</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ97" t="inlineStr"/>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5eaac1b48d712102356b170f</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2MXW4T</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>26</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>4</v>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="n">
+        <v>45764.09988031594</v>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA98" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 1, 34, 25, 912900), datetime.datetime(2025, 4, 17, 1, 34, 22, 436700), datetime.datetime(2025, 4, 17, 1, 34, 44, 190100), datetime.datetime(2025, 4, 17, 1, 35, 7, 226100), datetime.datetime(2025, 4, 17, 1, 35, 25, 296300), datetime.datetime(2025, 4, 17, 1, 56, 0, 544800), datetime.datetime(2025, 4, 17, 1, 46, 0, 585100), datetime.datetime(2025, 4, 17, 1, 46, 27, 153400), datetime.datetime(2025, 4, 17, 1, 46, 39, 216100), datetime.datetime(2025, 4, 17, 1, 47, 1, 843400), datetime.datetime(2025, 4, 17, 1, 48, 44, 324900), datetime.datetime(2025, 4, 17, 1, 48, 8, 614700), datetime.datetime(2025, 4, 17, 1, 48, 23, 127200), datetime.datetime(2025, 4, 17, 1, 54, 11, 713700), datetime.datetime(2025, 4, 17, 1, 51, 36, 722100), datetime.datetime(2025, 4, 17, 1, 52, 1, 552100), datetime.datetime(2025, 4, 17, 1, 52, 3, 967900), datetime.datetime(2025, 4, 17, 1, 52, 15, 879400), datetime.datetime(2025, 4, 17, 1, 52, 21, 685100), datetime.datetime(2025, 4, 17, 1, 55, 46, 875100), datetime.datetime(2025, 4, 17, 1, 54, 22, 859100), datetime.datetime(2025, 4, 17, 1, 54, 53, 741500), datetime.datetime(2025, 4, 17, 1, 55, 2, 447200), datetime.datetime(2025, 4, 17, 1, 55, 28, 285900), datetime.datetime(2025, 4, 17, 1, 55, 47, 345400), datetime.datetime(2025, 4, 17, 1, 56, 59, 514600), datetime.datetime(2025, 4, 17, 1, 56, 44, 899500), datetime.datetime(2025, 4, 17, 1, 56, 58, 822500), datetime.datetime(2025, 4, 17, 1, 57, 2, 787800), datetime.datetime(2025, 4, 17, 1, 58, 33, 888100), datetime.datetime(2025, 4, 17, 1, 58, 1, 163300), datetime.datetime(2025, 4, 17, 1, 58, 12, 878400), datetime.datetime(2025, 4, 17, 1, 58, 15, 958500), datetime.datetime(2025, 4, 17, 2, 0, 21, 400000), datetime.datetime(2025, 4, 17, 1, 59, 43, 316900), datetime.datetime(2025, 4, 17, 1, 59, 59, 364500), datetime.datetime(2025, 4, 17, 1, 59, 57, 348000), datetime.datetime(2025, 4, 17, 2, 2, 35, 454000), datetime.datetime(2025, 4, 17, 2, 1, 32, 937200), datetime.datetime(2025, 4, 17, 2, 2, 8, 439900), datetime.datetime(2025, 4, 17, 2, 2, 27, 40400), datetime.datetime(2025, 4, 17, 2, 2, 46, 891100), datetime.datetime(2025, 4, 17, 2, 3, 11, 615400), datetime.datetime(2025, 4, 17, 2, 3, 34, 236700), datetime.datetime(2025, 4, 17, 2, 4, 54, 250400), datetime.datetime(2025, 4, 17, 2, 5, 25, 926700), datetime.datetime(2025, 4, 17, 2, 5, 5, 241200), datetime.datetime(2025, 4, 17, 2, 5, 26, 38900), datetime.datetime(2025, 4, 17, 2, 6, 18, 249700), datetime.datetime(2025, 4, 17, 2, 6, 18, 239900), datetime.datetime(2025, 4, 17, 2, 6, 35, 888900), datetime.datetime(2025, 4, 17, 2, 6, 38, 861900), datetime.datetime(2025, 4, 17, 2, 7, 29, 9800), datetime.datetime(2025, 4, 17, 2, 7, 14, 715200), datetime.datetime(2025, 4, 17, 2, 7, 25, 742900), datetime.datetime(2025, 4, 17, 2, 7, 45, 733700), datetime.datetime(2025, 4, 17, 2, 8, 1, 946300), datetime.datetime(2025, 4, 17, 2, 8, 10, 444000), datetime.datetime(2025, 4, 17, 2, 10, 1, 635800), datetime.datetime(2025, 4, 17, 2, 9, 14, 9500), datetime.datetime(2025, 4, 17, 2, 9, 29, 17700), datetime.datetime(2025, 4, 17, 2, 9, 46, 11100), datetime.datetime(2025, 4, 17, 2, 9, 56, 683500), datetime.datetime(2025, 4, 17, 2, 9, 58, 345700), datetime.datetime(2025, 4, 17, 2, 12, 20, 130100), datetime.datetime(2025, 4, 17, 2, 11, 26, 130600), datetime.datetime(2025, 4, 17, 2, 11, 29, 76000), datetime.datetime(2025, 4, 17, 2, 11, 47, 334700), datetime.datetime(2025, 4, 17, 2, 12, 5, 657400), datetime.datetime(2025, 4, 17, 2, 13, 2, 704600), datetime.datetime(2025, 4, 17, 2, 13, 2, 704600), datetime.datetime(2025, 4, 17, 2, 16, 11, 573100), datetime.datetime(2025, 4, 17, 2, 16, 12, 104100), datetime.datetime(2025, 4, 17, 2, 16, 28, 871300), datetime.datetime(2025, 4, 17, 2, 19, 31, 45400), datetime.datetime(2025, 4, 17, 2, 18, 17, 733800), datetime.datetime(2025, 4, 17, 2, 18, 29, 884200), datetime.datetime(2025, 4, 17, 2, 18, 49, 818800), datetime.datetime(2025, 4, 17, 2, 19, 49, 905500), datetime.datetime(2025, 4, 17, 2, 19, 43, 354500), datetime.datetime(2025, 4, 17, 2, 20, 41, 604100), datetime.datetime(2025, 4, 17, 2, 20, 38, 367500), datetime.datetime(2025, 4, 17, 2, 21, 1, 790000), datetime.datetime(2025, 4, 17, 2, 21, 49, 402300), datetime.datetime(2025, 4, 17, 2, 22, 0, 857600), datetime.datetime(2025, 4, 17, 2, 23, 11, 401300)]</t>
+        </is>
+      </c>
+      <c r="AE98" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>88</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ98" t="inlineStr"/>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>65a97afe116a650acc588c5b</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>J1VLQ0</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" t="n">
+        <v>23</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>[3]</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>2</v>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>study_completed</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="n">
+        <v>45764.11285833514</v>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="AA99" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>['mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse', 'mouse']</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>[datetime.datetime(2025, 4, 17, 1, 50, 41, 275800), datetime.datetime(2025, 4, 17, 1, 50, 16, 553500), datetime.datetime(2025, 4, 17, 1, 50, 50, 611700), datetime.datetime(2025, 4, 17, 1, 50, 58, 997500), datetime.datetime(2025, 4, 17, 1, 55, 2, 925500), datetime.datetime(2025, 4, 17, 1, 53, 17, 83000), datetime.datetime(2025, 4, 17, 1, 53, 48, 27400), datetime.datetime(2025, 4, 17, 1, 53, 57, 700700), datetime.datetime(2025, 4, 17, 1, 54, 19, 548800), datetime.datetime(2025, 4, 17, 2, 3, 11, 421300), datetime.datetime(2025, 4, 17, 1, 59, 48, 860200), datetime.datetime(2025, 4, 17, 1, 59, 59, 298800), datetime.datetime(2025, 4, 17, 2, 0, 4, 118400), datetime.datetime(2025, 4, 17, 2, 0, 23, 446500), datetime.datetime(2025, 4, 17, 2, 0, 25, 390600), datetime.datetime(2025, 4, 17, 2, 1, 18, 70500), datetime.datetime(2025, 4, 17, 2, 1, 11, 482800), datetime.datetime(2025, 4, 17, 2, 1, 52, 744300), datetime.datetime(2025, 4, 17, 2, 1, 43, 910500), datetime.datetime(2025, 4, 17, 2, 2, 18, 916900), datetime.datetime(2025, 4, 17, 2, 2, 14, 294700), datetime.datetime(2025, 4, 17, 2, 5, 53, 846500), datetime.datetime(2025, 4, 17, 2, 4, 24, 454100), datetime.datetime(2025, 4, 17, 2, 4, 57, 912700), datetime.datetime(2025, 4, 17, 2, 5, 1, 509800), datetime.datetime(2025, 4, 17, 2, 5, 20, 900500), datetime.datetime(2025, 4, 17, 2, 5, 41, 354400), datetime.datetime(2025, 4, 17, 2, 6, 5, 866400), datetime.datetime(2025, 4, 17, 2, 6, 43, 966300), datetime.datetime(2025, 4, 17, 2, 6, 50, 899800), datetime.datetime(2025, 4, 17, 2, 7, 16, 360500), datetime.datetime(2025, 4, 17, 2, 7, 28, 878200), datetime.datetime(2025, 4, 17, 2, 8, 14, 373500), datetime.datetime(2025, 4, 17, 2, 9, 0, 964100), datetime.datetime(2025, 4, 17, 2, 8, 52, 303300), datetime.datetime(2025, 4, 17, 2, 9, 19, 301500), datetime.datetime(2025, 4, 17, 2, 9, 30, 255500), datetime.datetime(2025, 4, 17, 2, 9, 40, 660400), datetime.datetime(2025, 4, 17, 2, 9, 47, 19400), datetime.datetime(2025, 4, 17, 2, 11, 35, 711800), datetime.datetime(2025, 4, 17, 2, 11, 25, 591600), datetime.datetime(2025, 4, 17, 2, 11, 17, 733500), datetime.datetime(2025, 4, 17, 2, 12, 14, 693700), datetime.datetime(2025, 4, 17, 2, 12, 11, 873300), datetime.datetime(2025, 4, 17, 2, 12, 18, 931600), datetime.datetime(2025, 4, 17, 2, 14, 23, 205400), datetime.datetime(2025, 4, 17, 2, 13, 55, 419400), datetime.datetime(2025, 4, 17, 2, 14, 17, 695900), datetime.datetime(2025, 4, 17, 2, 17, 49, 796000), datetime.datetime(2025, 4, 17, 2, 16, 19, 175300), datetime.datetime(2025, 4, 17, 2, 16, 28, 97700), datetime.datetime(2025, 4, 17, 2, 17, 54, 425000), datetime.datetime(2025, 4, 17, 2, 17, 49, 463500), datetime.datetime(2025, 4, 17, 2, 17, 57, 357700), datetime.datetime(2025, 4, 17, 2, 18, 2, 669800), datetime.datetime(2025, 4, 17, 2, 18, 15, 821300), datetime.datetime(2025, 4, 17, 2, 19, 25, 317600), datetime.datetime(2025, 4, 17, 2, 19, 25, 317600), datetime.datetime(2025, 4, 17, 2, 23, 21, 293300), datetime.datetime(2025, 4, 17, 2, 22, 37, 54500), datetime.datetime(2025, 4, 17, 2, 22, 31, 846200), datetime.datetime(2025, 4, 17, 2, 22, 52, 403000), datetime.datetime(2025, 4, 17, 2, 22, 58, 375200), datetime.datetime(2025, 4, 17, 2, 23, 21, 336300), datetime.datetime(2025, 4, 17, 2, 24, 23, 480500), datetime.datetime(2025, 4, 17, 2, 24, 7, 317300), datetime.datetime(2025, 4, 17, 2, 24, 14, 895000), datetime.datetime(2025, 4, 17, 2, 24, 21, 816500), datetime.datetime(2025, 4, 17, 2, 24, 33, 89300), datetime.datetime(2025, 4, 17, 2, 25, 24, 350400), datetime.datetime(2025, 4, 17, 2, 25, 23, 143300), datetime.datetime(2025, 4, 17, 2, 25, 45, 396600), datetime.datetime(2025, 4, 17, 2, 25, 51, 170400), datetime.datetime(2025, 4, 17, 2, 27, 15, 346300), datetime.datetime(2025, 4, 17, 2, 26, 52, 110700), datetime.datetime(2025, 4, 17, 2, 27, 12, 974600), datetime.datetime(2025, 4, 17, 2, 27, 14, 624700), datetime.datetime(2025, 4, 17, 2, 29, 19, 920300), datetime.datetime(2025, 4, 17, 2, 28, 31, 412100), datetime.datetime(2025, 4, 17, 2, 28, 41, 256600), datetime.datetime(2025, 4, 17, 2, 28, 48, 730700), datetime.datetime(2025, 4, 17, 2, 29, 25, 942300), datetime.datetime(2025, 4, 17, 2, 29, 36, 351000), datetime.datetime(2025, 4, 17, 2, 29, 40, 110900), datetime.datetime(2025, 4, 17, 2, 29, 57, 170100), datetime.datetime(2025, 4, 17, 2, 34, 57, 288600), datetime.datetime(2025, 4, 17, 2, 32, 41, 856300), datetime.datetime(2025, 4, 17, 2, 33, 6, 545900), datetime.datetime(2025, 4, 17, 2, 33, 26, 210600), datetime.datetime(2025, 4, 17, 2, 33, 51, 618100), datetime.datetime(2025, 4, 17, 2, 34, 0, 78700), datetime.datetime(2025, 4, 17, 2, 37, 18, 289700), datetime.datetime(2025, 4, 17, 2, 36, 6, 242400), datetime.datetime(2025, 4, 17, 2, 36, 45, 392000), datetime.datetime(2025, 4, 17, 2, 36, 42, 74200), datetime.datetime(2025, 4, 17, 2, 36, 49, 852300), datetime.datetime(2025, 4, 17, 2, 37, 4, 2300), datetime.datetime(2025, 4, 17, 2, 37, 55, 297800), datetime.datetime(2025, 4, 17, 2, 37, 43, 810200), datetime.datetime(2025, 4, 17, 2, 39, 9, 843500), datetime.datetime(2025, 4, 17, 2, 38, 58, 422200), datetime.datetime(2025, 4, 17, 2, 38, 54, 244100), datetime.datetime(2025, 4, 17, 2, 39, 7, 141800), datetime.datetime(2025, 4, 17, 2, 39, 45, 861600), datetime.datetime(2025, 4, 17, 2, 39, 50, 479400), datetime.datetime(2025, 4, 17, 2, 41, 19, 893000), datetime.datetime(2025, 4, 17, 2, 41, 2, 75100), datetime.datetime(2025, 4, 17, 2, 41, 11, 137400), datetime.datetime(2025, 4, 17, 2, 41, 14, 297100), datetime.datetime(2025, 4, 17, 2, 41, 29, 681500), datetime.datetime(2025, 4, 17, 2, 42, 6, 272000)]</t>
+        </is>
+      </c>
+      <c r="AE99" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>89</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>67fe0992fb0768fdc5720187</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>FFPTE7</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="n">
+        <v>45764.08020157751</v>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="inlineStr"/>
+      <c r="AK100" t="inlineStr"/>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>67ddb06bc7175d8f155fe2bf</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2UZ7GF</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>left_study_or_got_disconnected</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="n">
+        <v>45764.19133317126</v>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr"/>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
